--- a/Glassdoor_Jobs_2026-04-28.xlsx
+++ b/Glassdoor_Jobs_2026-04-28.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Executive Director</t>
+          <t>Bioinformatics Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$70K - $80K(Employer provided)</t>
+          <t>$80K - $85K(Employer provided)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
+          <t>https://www.glassdoor.com/job-listing/bioinformatics-analyst-agendia-JV_KO0,22_KE23,30.htm?jl=1010110968052</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Executive Assistant to the CEO</t>
+          <t>Gen AI Engineering Analyst - Vice President</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -505,17 +505,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$55K(Employer provided)</t>
+          <t>$114K - $171K(Employer provided)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
+          <t>https://www.glassdoor.com/job-listing/gen-ai-engineering-analyst-vice-president-citi-JV_IC1154093_KO0,41_KE42,46.htm?jl=1010114737667</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$350K - $500K(Employer provided)</t>
+          <t>$163K - $173K(Employer provided)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-hunter-michaels-JV_KO0,3_KE4,19.htm?jl=1010066292543</t>
+          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-brooksource-JV_IC1152672_KO0,21_KE22,33.htm?jl=1010114706169</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CEO in Training (CIT), Executive Director</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,17 +569,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$46K - $84K(Glassdoor est.)</t>
+          <t>$50.00 - $55.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1128031_KO0,38_KE39,52.htm?jl=1010100454520</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-brooksource-JV_IC1154170_KO0,14_KE15,26.htm?jl=1010114754582</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CEO - Interior Design Company</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$250K - $350K(Employer provided)</t>
+          <t>$122K - $160K(Employer provided)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-interior-design-company-redford-hearth-executive-search-healthcare-JV_IC1132348_KO0,27_KE28,70.htm?jl=1010077281914</t>
+          <t>https://www.glassdoor.com/job-listing/machine-learning-engineer-ii-glidewell-dental-JV_IC1146798_KO0,28_KE29,45.htm?jl=1009940212594</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Aircraft Performance Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -633,17 +633,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$175K - $225K(Employer provided)</t>
+          <t>$75K(Employer provided)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
+          <t>https://www.glassdoor.com/job-listing/aircraft-performance-engineer-i-rocketroute-JV_IC1164306_KO0,31_KE32,43.htm?jl=1010103160521</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Associate Director, Data Science - Market Access</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$170K - $175K(Employer provided)</t>
+          <t>$149K - $215K(Employer provided)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
+          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-market-access-sanofi-JV_IC1154545_KO0,45_KE46,52.htm?jl=1010050421211</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Co-founder</t>
+          <t>Sr. Exploitation Specialist/Data Scientist (TS/SCI)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -695,15 +695,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>$117K - $195K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/co-founder-veganbase-JV_KO0,10_KE11,20.htm?jl=1010096856397</t>
+          <t>https://www.glassdoor.com/job-listing/sr-exploitation-specialist-data-scientist-ts-sci-culmen-international-JV_IC1154170_KO0,48_KE49,69.htm?jl=1010041116784</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -715,7 +719,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cofounder (CEO/CTO/CSO for Autumn 2021 Cohort)</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -723,15 +727,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>$70K - $80K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/cofounder-ceo-cto-cso-for-autumn-2021-cohort-counterfactual-ventures-JV_KO0,44_KE45,68.htm?jl=1010096854974</t>
+          <t>https://www.glassdoor.com/job-listing/ai-developer-mifab-JV_IC1128808_KO0,12_KE13,18.htm?jl=1010103162764</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -743,7 +751,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Trust &amp; Safety Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -751,15 +759,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>$138K - $275K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-granite-county-medical-center-JV_IC1135305_KO0,3_KE4,33.htm?jl=1010062632144</t>
+          <t>https://www.glassdoor.com/job-listing/trust-safety-machine-learning-engineer-zoom-JV_IC1147436_KO0,38_KE39,43.htm?jl=1010103395317</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -771,7 +783,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Lab Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -779,15 +791,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>$75K - $80K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-la-pizza-loca-JV_IC1163767_KO0,9_KE10,23.htm?jl=1009284779217</t>
+          <t>https://www.glassdoor.com/job-listing/lab-data-scientist-geveko-markings-usa-JV_IC1155838_KO0,18_KE19,38.htm?jl=1010104506793</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -799,7 +815,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chief Executive Officer (CEO)</t>
+          <t>Senior Data Product Lead</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -809,17 +825,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$210K - $345K(Employer provided)</t>
+          <t>$100K - $139K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-ceo-mendocino-community-health-clinic-JV_IC1147597_KO0,27_KE28,61.htm?jl=1010076472683</t>
+          <t>https://www.glassdoor.com/job-listing/senior-data-product-lead-mariner-finance-JV_IC1151049_KO0,24_KE25,40.htm?jl=1010081192082</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -831,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Data Scientist / Generative AI Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -839,15 +855,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>$85K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-morongo-band-of-mission-indians-JV_IC1147053_KO0,23_KE24,55.htm?jl=1010104655090</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-generative-ai-data-engineer-specialized-staffing-solutions-JV_IC1145261_KO0,42_KE43,73.htm?jl=1010101551039</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -859,7 +879,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -867,15 +887,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>$160K - $185K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-appjaxx-JV_KO0,23_KE24,31.htm?jl=1010053135563</t>
+          <t>https://www.glassdoor.com/job-listing/ai-engineer-friant-associates-JV_IC1147404_KO0,11_KE12,29.htm?jl=1010037044723</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -887,7 +911,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>ML/AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -895,15 +919,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>$80K - $120K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-jonas-software-JV_KO0,9_KE10,24.htm?jl=1010076386564</t>
+          <t>https://www.glassdoor.com/job-listing/ml-ai-engineer-midwest-machine-llc-JV_IC1139740_KO0,14_KE15,34.htm?jl=1010109262064</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -915,7 +943,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Director, Commercial Data Science - Hampton, NJ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -923,15 +951,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>$177K - $229K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-jonas-software-JV_KO0,9_KE10,24.htm?jl=1010083936061</t>
+          <t>https://www.glassdoor.com/job-listing/director-commercial-data-science-hampton-nj-celldex-JV_IC1126790_KO0,43_KE44,51.htm?jl=1010072517837</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -943,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>President - Property Systems PMS</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -951,15 +983,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>$124K - $165K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-property-systems-pms-jonas-software-JV_KO0,30_KE31,45.htm?jl=1010093058178</t>
+          <t>https://www.glassdoor.com/job-listing/sr-data-scientist-the-hershey-company-JV_IC1139977_KO0,17_KE18,37.htm?jl=1009569149385</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -971,7 +1007,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CEO In Training</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -981,17 +1017,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$41K - $72K(Glassdoor est.)</t>
+          <t>$80K - $90K(Employer provided)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-quorum-services-JV_IC1140171_KO0,15_KE16,31.htm?jl=1010061603989</t>
+          <t>https://www.glassdoor.com/job-listing/computer-science-teacher-kūlia-academy-JV_IC1140656_KO0,24_KE25,38.htm?jl=1009966984742</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1003,7 +1039,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chief Executive Officer (CEO)</t>
+          <t>Data Scientist - AI Trainer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1011,15 +1047,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>$50.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-ceo-greeley-county-health-services-JV_IC1150926_KO0,27_KE28,58.htm?jl=1010079234942</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-ai-trainer-dataannotation-JV_IC1165356_KO0,25_KE26,40.htm?jl=1010111066792</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1031,7 +1071,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Technical target analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1039,15 +1079,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>$70K - $185K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-mid-south-transportation-JV_IC1144463_KO0,23_KE24,48.htm?jl=1009799948862</t>
+          <t>https://www.glassdoor.com/job-listing/technical-target-analyst-cia-JV_IC1138213_KO0,24_KE25,28.htm?jl=1009964046918</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1059,7 +1103,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CEO Communications Strategist</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1069,17 +1113,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$114K - $140K(Employer provided)</t>
+          <t>$48K - $80K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-communications-strategist-project-management-institute-JV_KO0,29_KE30,58.htm?jl=1010076119027</t>
+          <t>https://www.glassdoor.com/job-listing/ai-specialist-medpro-group-JV_IC1144939_KO0,13_KE14,26.htm?jl=1010112183170</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1091,7 +1135,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1099,15 +1143,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>$71K - $123K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-chief-executive-officer-goodwill-JV_IC1144380_KO0,33_KE34,42.htm?jl=1010071741435</t>
+          <t>https://www.glassdoor.com/job-listing/ai-specialist-commonwealth-equipment-corp-JV_IC1165586_KO0,13_KE14,41.htm?jl=1010101947687</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1119,7 +1167,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Lead Developer, Finance Technology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1127,15 +1175,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>$98K - $152K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-adams-keegan-JV_IC1144463_KO0,3_KE4,16.htm?jl=1010101043925</t>
+          <t>https://www.glassdoor.com/job-listing/lead-developer-finance-technology-the-jm-smucker-co-JV_IC1146360_KO0,33_KE34,51.htm?jl=1010097676555</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1147,7 +1199,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>President, Southwest</t>
+          <t>Data Scientist (In Person - Austin, TX)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1157,17 +1209,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$200K - $215K(Employer provided)</t>
+          <t>$135K - $170K(Employer provided)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-southwest-renova-one-JV_IC1139977_KO0,19_KE20,30.htm?jl=1010076478484</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-in-person-austin-tx-tommbo-com-JV_IC1139761_KO0,34_KE35,45.htm?jl=1010046625687</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1179,7 +1231,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Clinical Data Scientist - AI Trainer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1189,17 +1241,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$165K - $180K(Employer provided)</t>
+          <t>$40.00 - $60.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-kinston-JV_IC1138852_KO0,12_KE13,28.htm?jl=1010093428970</t>
+          <t>https://www.glassdoor.com/job-listing/clinical-data-scientist-ai-trainer-dataannotation-JV_IC1154703_KO0,34_KE35,49.htm?jl=1010080150976</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1211,7 +1263,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>President, Dragons Academy</t>
+          <t>MRM Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1221,17 +1273,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$100K - $160K(Employer provided)</t>
+          <t>$152K - $186K(Employer provided)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-dragons-academy-black-dragon-capital-JV_KO0,25_KE26,46.htm?jl=1010076639291</t>
+          <t>https://www.glassdoor.com/job-listing/mrm-senior-data-scientist-pacific-life-JV_IC1146837_KO0,25_KE26,38.htm?jl=1010094536797</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1243,7 +1295,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Executive Director</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1251,15 +1303,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>$75K - $157K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-black-dragon-capital-JV_KO0,18_KE19,39.htm?jl=1010006370188</t>
+          <t>https://www.glassdoor.com/job-listing/data-engineer-cia-JV_IC1138213_KO0,13_KE14,17.htm?jl=1009964042992</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1271,7 +1327,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1281,17 +1337,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$203K - $282K(Employer provided)</t>
+          <t>$162K - $260K(Employer provided)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-roanoke-chowan-community-health-center-JV_IC1138391_KO0,23_KE24,62.htm?jl=1010097179493</t>
+          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-takeda-pharmaceuticals-JV_IC1154532_KO0,21_KE22,44.htm?jl=1010080328224</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1303,7 +1359,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Executive Assistant to CEO</t>
+          <t>Associate Director, Registry Data Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1313,17 +1369,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$86K - $108K(Employer provided)</t>
+          <t>$159K - $183K(Employer provided)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-ceo-earnest-JV_KO0,26_KE27,34.htm?jl=1010109327574</t>
+          <t>https://www.glassdoor.com/job-listing/associate-director-registry-data-analytics-american-academy-of-dermatology-JV_IC1158097_KO0,42_KE43,74.htm?jl=1010115120315</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1335,7 +1391,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1345,17 +1401,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$243K - $389K(Employer provided)</t>
+          <t>$130K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-unity-care-nw-JV_IC1150256_KO0,23_KE24,37.htm?jl=1010033656460</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-the-judge-group-JV_IC1140494_KO0,14_KE15,30.htm?jl=1010106793793</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">

--- a/Glassdoor_Jobs_2026-04-28.xlsx
+++ b/Glassdoor_Jobs_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bioinformatics Analyst</t>
+          <t>Behavior Analyst (BCBA)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$80K - $85K(Employer provided)</t>
+          <t>$81K - $104K(Employer provided)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/bioinformatics-analyst-agendia-JV_KO0,22_KE23,30.htm?jl=1010110968052</t>
+          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1164305_KO0,21_KE22,40.htm?jl=1010038441282</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Engineering Analyst - Vice President</t>
+          <t>Behavior Analyst (BCBA)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -505,17 +505,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$114K - $171K(Employer provided)</t>
+          <t>$81K - $104K(Employer provided)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/gen-ai-engineering-analyst-vice-president-citi-JV_IC1154093_KO0,41_KE42,46.htm?jl=1010114737667</t>
+          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1148170_KO0,21_KE22,40.htm?jl=1010100922250</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Hybrid Behavior Analyst (BCBA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$163K - $173K(Employer provided)</t>
+          <t>$81K - $104K(Employer provided)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-brooksource-JV_IC1152672_KO0,21_KE22,33.htm?jl=1010114706169</t>
+          <t>https://www.glassdoor.com/job-listing/hybrid-behavior-analyst-bcba-soar-autism-center-JV_KO0,28_KE29,47.htm?jl=1010054630392</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Business Analyst 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,17 +569,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$50.00 - $55.00Per Hour(Employer provided)</t>
+          <t>$34.66 - $36.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-brooksource-JV_IC1154170_KO0,14_KE15,26.htm?jl=1010114754582</t>
+          <t>https://www.glassdoor.com/job-listing/business-analyst-1-insync-staffing-JV_IC1151576_KO0,18_KE19,34.htm?jl=1010114536750</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>HRIS Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -599,19 +599,15 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>$122K - $160K(Employer provided)</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/machine-learning-engineer-ii-glidewell-dental-JV_IC1146798_KO0,28_KE29,45.htm?jl=1009940212594</t>
+          <t>https://www.glassdoor.com/job-listing/hris-analyst-beusa-energy-JV_IC1140171_KO0,12_KE13,25.htm?jl=1010106990644</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aircraft Performance Engineer I</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -633,17 +629,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$75K(Employer provided)</t>
+          <t>$105K - $115K(Employer provided)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/aircraft-performance-engineer-i-rocketroute-JV_IC1164306_KO0,31_KE32,43.htm?jl=1010103160521</t>
+          <t>https://www.glassdoor.com/job-listing/business-analyst-12-elements-consulting-JV_IC1139790_KO0,16_KE17,39.htm?jl=1010053067441</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,7 +651,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Director, Data Science - Market Access</t>
+          <t>Junior Financial Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -665,17 +661,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$149K - $215K(Employer provided)</t>
+          <t>$70K - $75K(Employer provided)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-market-access-sanofi-JV_IC1154545_KO0,45_KE46,52.htm?jl=1010050421211</t>
+          <t>https://www.glassdoor.com/job-listing/junior-financial-analyst-gl-staffing-services-JV_IC1154160_KO0,24_KE25,45.htm?jl=1010115041405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,7 +683,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Exploitation Specialist/Data Scientist (TS/SCI)</t>
+          <t>Senior Population Health Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -697,17 +693,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$117K - $195K(Glassdoor est.)</t>
+          <t>$44.10 - $68.53Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sr-exploitation-specialist-data-scientist-ts-sci-culmen-international-JV_IC1154170_KO0,48_KE49,69.htm?jl=1010041116784</t>
+          <t>https://www.glassdoor.com/job-listing/senior-population-health-data-analyst-torrance-memorial-medical-center-JV_IC1146894_KO0,37_KE38,70.htm?jl=1010093309288</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,7 +715,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Lead Quantitative Analyst (Charlotte, NC (Hybrid) or Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,17 +725,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$70K - $80K(Employer provided)</t>
+          <t>$160K - $210K(Employer provided)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-developer-mifab-JV_IC1128808_KO0,12_KE13,18.htm?jl=1010103162764</t>
+          <t>https://www.glassdoor.com/job-listing/lead-quantitative-analyst-charlotte-nc-hybrid-or-remote-brighthouse-financial-JV_IC1138644_KO0,55_KE56,77.htm?jl=1010114527699</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -751,7 +747,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety Machine Learning Engineer</t>
+          <t>Financial Analyst III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,17 +757,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$138K - $275K(Employer provided)</t>
+          <t>$106K - $130K(Employer provided)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/trust-safety-machine-learning-engineer-zoom-JV_IC1147436_KO0,38_KE39,43.htm?jl=1010103395317</t>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-iii-greenheck-group-JV_IC1142551_KO0,21_KE22,37.htm?jl=1010038412231</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -783,7 +779,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lab Data Scientist</t>
+          <t>IT FinOps Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -793,17 +789,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$75K - $80K(Employer provided)</t>
+          <t>$104K - $141K(Employer provided)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/lab-data-scientist-geveko-markings-usa-JV_IC1155838_KO0,18_KE19,38.htm?jl=1010104506793</t>
+          <t>https://www.glassdoor.com/job-listing/it-finops-analyst-atlas-air-worldwide-JV_IC1132464_KO0,17_KE18,37.htm?jl=1010082614845</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -815,7 +811,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Product Lead</t>
+          <t>National Account Sales Analyst - Retail</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -825,17 +821,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$100K - $139K(Glassdoor est.)</t>
+          <t>$50K - $60K(Employer provided)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-data-product-lead-mariner-finance-JV_IC1151049_KO0,24_KE25,40.htm?jl=1010081192082</t>
+          <t>https://www.glassdoor.com/job-listing/national-account-sales-analyst-retail-enerco-JV_IC1145778_KO0,37_KE38,44.htm?jl=1010114768785</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,7 +843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist / Generative AI Data Engineer</t>
+          <t>Laboratory Analyst - Afternoon Shift (Seattle, WA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -857,17 +853,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$85K(Employer provided)</t>
+          <t>$22.00 - $24.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-generative-ai-data-engineer-specialized-staffing-solutions-JV_IC1145261_KO0,42_KE43,73.htm?jl=1010101551039</t>
+          <t>https://www.glassdoor.com/job-listing/laboratory-analyst-afternoon-shift-seattle-wa-ieh-laboratories-consulting-group-JV_IC1150505_KO0,45_KE46,79.htm?jl=1010115098281</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,7 +875,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Job Cost Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -889,17 +885,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$160K - $185K(Employer provided)</t>
+          <t>$57K - $82K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-engineer-friant-associates-JV_IC1147404_KO0,11_KE12,29.htm?jl=1010037044723</t>
+          <t>https://www.glassdoor.com/job-listing/job-cost-analyst-vee-jay-cement-contracting-JV_IC1131270_KO0,16_KE17,43.htm?jl=1010114961842</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,7 +907,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ML/AI Engineer</t>
+          <t>Corporate Financial Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -921,17 +917,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$80K - $120K(Employer provided)</t>
+          <t>$65K - $85K(Employer provided)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ml-ai-engineer-midwest-machine-llc-JV_IC1139740_KO0,14_KE15,34.htm?jl=1010109262064</t>
+          <t>https://www.glassdoor.com/job-listing/corporate-financial-analyst-centro-iowa-JV_IC1149335_KO0,27_KE28,39.htm?jl=1010061590757</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -943,7 +939,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Director, Commercial Data Science - Hampton, NJ</t>
+          <t>Chemical Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -953,17 +949,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$177K - $229K(Employer provided)</t>
+          <t>$53K - $70K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/director-commercial-data-science-hampton-nj-celldex-JV_IC1126790_KO0,43_KE44,51.htm?jl=1010072517837</t>
+          <t>https://www.glassdoor.com/job-listing/chemical-analyst-materion-JV_IC1145796_KO0,16_KE17,25.htm?jl=1010114458569</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -975,7 +971,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Loan Origination Systems Support Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -985,17 +981,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$124K - $165K(Glassdoor est.)</t>
+          <t>$50K - $71K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sr-data-scientist-the-hershey-company-JV_IC1139977_KO0,17_KE18,37.htm?jl=1009569149385</t>
+          <t>https://www.glassdoor.com/job-listing/loan-origination-systems-support-analyst-oakstar-bank-JV_IC1131348_KO0,40_KE41,53.htm?jl=1010111062272</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,7 +1003,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Senior Sales Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1017,17 +1013,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$80K - $90K(Employer provided)</t>
+          <t>$68K - $99K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/computer-science-teacher-kūlia-academy-JV_IC1140656_KO0,24_KE25,38.htm?jl=1009966984742</t>
+          <t>https://www.glassdoor.com/job-listing/senior-sales-analyst-breakthru-beverage-group-JV_IC1155147_KO0,20_KE21,45.htm?jl=1010114667197</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,7 +1035,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist - AI Trainer</t>
+          <t>Analyst / Associate, Infrastructure and Energy Debt Advisory</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1049,17 +1045,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$50.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$110K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-ai-trainer-dataannotation-JV_IC1165356_KO0,25_KE26,40.htm?jl=1010111066792</t>
+          <t>https://www.glassdoor.com/job-listing/analyst-associate-infrastructure-and-energy-debt-advisory-macquarie-group-JV_IC1132348_KO0,57_KE58,73.htm?jl=1010114916735</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,7 +1067,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Technical target analyst</t>
+          <t>IT Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1081,17 +1077,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$70K - $185K(Employer provided)</t>
+          <t>$65K - $75K(Employer provided)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/technical-target-analyst-cia-JV_IC1138213_KO0,24_KE25,28.htm?jl=1009964046918</t>
+          <t>https://www.glassdoor.com/job-listing/it-analyst-great-lakes-castings-JV_IC1134383_KO0,10_KE11,31.htm?jl=1010111083685</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,7 +1099,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Analyst II - Product System Configuration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1113,17 +1109,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$48K - $80K(Glassdoor est.)</t>
+          <t>$80K - $106K(Employer provided)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-specialist-medpro-group-JV_IC1144939_KO0,13_KE14,26.htm?jl=1010112183170</t>
+          <t>https://www.glassdoor.com/job-listing/analyst-ii-product-system-configuration-inland-empire-health-plan-JV_IC1147132_KO0,39_KE40,65.htm?jl=1009813420167</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,7 +1131,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Investment Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1145,17 +1141,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$71K - $123K(Glassdoor est.)</t>
+          <t>$110K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-specialist-commonwealth-equipment-corp-JV_IC1165586_KO0,13_KE14,41.htm?jl=1010101947687</t>
+          <t>https://www.glassdoor.com/job-listing/investment-analyst-terreno-realty-corporation-JV_IC1150442_KO0,18_KE19,45.htm?jl=1010064278960</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,7 +1163,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lead Developer, Finance Technology</t>
+          <t>Import Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1177,17 +1173,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$98K - $152K(Glassdoor est.)</t>
+          <t>$55K - $70K(Employer provided)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/lead-developer-finance-technology-the-jm-smucker-co-JV_IC1146360_KO0,33_KE34,51.htm?jl=1010097676555</t>
+          <t>https://www.glassdoor.com/job-listing/import-analyst-dillard-s-JV_KO0,14_KE15,24.htm?jl=1010100715804</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,7 +1195,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist (In Person - Austin, TX)</t>
+          <t>Process Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1209,17 +1205,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$135K - $170K(Employer provided)</t>
+          <t>$60K(Employer provided)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-in-person-austin-tx-tommbo-com-JV_IC1139761_KO0,34_KE35,45.htm?jl=1010046625687</t>
+          <t>https://www.glassdoor.com/job-listing/process-analyst-komico-hillsboro-JV_IC1151603_KO0,15_KE16,32.htm?jl=1010109685799</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,7 +1227,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clinical Data Scientist - AI Trainer</t>
+          <t>Financial Systems Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1241,17 +1237,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$40.00 - $60.00Per Hour(Employer provided)</t>
+          <t>$66K - $94K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/clinical-data-scientist-ai-trainer-dataannotation-JV_IC1154703_KO0,34_KE35,49.htm?jl=1010080150976</t>
+          <t>https://www.glassdoor.com/job-listing/financial-systems-analyst-pappas-restaurants-JV_IC1140171_KO0,25_KE26,44.htm?jl=1010088757112</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,7 +1259,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MRM Senior Data Scientist</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1273,17 +1269,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$152K - $186K(Employer provided)</t>
+          <t>$120K - $160K(Employer provided)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/mrm-senior-data-scientist-pacific-life-JV_IC1146837_KO0,25_KE26,38.htm?jl=1010094536797</t>
+          <t>https://www.glassdoor.com/job-listing/senior-business-analyst-genesis-capital-ca-JV_IC1146875_KO0,23_KE24,42.htm?jl=1009971786272</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,7 +1291,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Support Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1305,17 +1301,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$75K - $157K(Employer provided)</t>
+          <t>$44K - $59K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-engineer-cia-JV_IC1138213_KO0,13_KE14,17.htm?jl=1009964042992</t>
+          <t>https://www.glassdoor.com/job-listing/it-support-analyst-van-andel-research-institute-JV_IC1134796_KO0,18_KE19,47.htm?jl=1010110029456</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,7 +1323,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Business Analyst - In Person</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1337,17 +1333,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$162K - $260K(Employer provided)</t>
+          <t>$70K - $80K(Employer provided)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-takeda-pharmaceuticals-JV_IC1154532_KO0,21_KE22,44.htm?jl=1010080328224</t>
+          <t>https://www.glassdoor.com/job-listing/business-analyst-in-person-the-boat-house-JV_IC1135926_KO0,26_KE27,41.htm?jl=1010091637363</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,7 +1355,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Director, Registry Data Analytics</t>
+          <t>Business Analyst - Healthcare</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1369,17 +1365,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$159K - $183K(Employer provided)</t>
+          <t>$59K - $86K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-director-registry-data-analytics-american-academy-of-dermatology-JV_IC1158097_KO0,42_KE43,74.htm?jl=1010115120315</t>
+          <t>https://www.glassdoor.com/job-listing/business-analyst-healthcare-retina-group-of-florida-JV_IC1154154_KO0,27_KE28,51.htm?jl=1010106778321</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,30 +1387,2890 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>$80K - $100K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-columbus-downtown-development-corporation-JV_IC1145845_KO0,17_KE18,59.htm?jl=1010078938074</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>$81K - $136K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/director-northwestern-mutual-JV_IC1133579_KO0,8_KE9,28.htm?jl=1010112720343</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Investment Banking Consultant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>$68K - $206K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/investment-banking-consultant-accenture-JV_IC1154170_KO0,29_KE30,39.htm?jl=1010000045025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Credit Portfolio Group - Research - Vice President</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>$200K - $275K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/credit-portfolio-group-research-vice-president-jpmorgan-chase-co-JV_IC1132348_KO0,46_KE47,64.htm?jl=1010021310234</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Credit Portfolio Group - Research - Associate</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>$135K - $200K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/credit-portfolio-group-research-associate-jpmorgan-chase-co-JV_IC1132348_KO0,41_KE42,59.htm?jl=1010073216090</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Equity Research - REITs - Associate</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>$150K - $200K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/equity-research-reits-associate-jpmorgan-chase-co-JV_IC1132348_KO0,31_KE32,49.htm?jl=1010070497398</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Equity Research - Specialty &amp; Consumer Finance - Associate</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>$150K - $200K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/equity-research-specialty-consumer-finance-associate-jpmorgan-chase-co-JV_KO0,52_KE53,70.htm?jl=1010098630208</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Equity Research - Utilities - Associate</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>$150K - $200K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/equity-research-utilities-associate-jpmorgan-chase-co-JV_KO0,35_KE36,53.htm?jl=1010106989954</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Investment Banking - Investment Grade Finance - Associate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>$175K - $225K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/investment-banking-investment-grade-finance-associate-jpmorgan-chase-co-JV_IC1132348_KO0,53_KE54,71.htm?jl=1010073215917</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AIS Analyst</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>$85K - $100K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ais-analyst-abrdn-JV_KO0,11_KE12,17.htm?jl=1010056425121</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Operations Analyst, Renewable Energy Procurement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>$82K - $126K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/operations-analyst-renewable-energy-procurement-tesla-JV_IC1139761_KO0,47_KE48,53.htm?jl=1010033677027</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Investment Analyst</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>$47.50 - $71.25Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-investment-analyst-atrium-health-JV_IC1128935_KO0,25_KE26,39.htm?jl=1010101093398</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Strategic Investor Communications Lead</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>$189K - $284K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/strategic-investor-communications-lead-ge-healthcare-JV_IC1128808_KO0,38_KE39,52.htm?jl=1010045621776</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Collections Specialist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>$65K - $126K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/collections-specialist-gallagher-JV_IC1128962_KO0,22_KE23,32.htm?jl=1009960182119</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Investment Specialist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>$134K - $269K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/investment-specialist-rsm-JV_KO0,21_KE22,25.htm?jl=1010071186146</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Alternatives Data Analyst</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>$68.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-alternatives-data-analyst-mercer-JV_IC1154532_KO0,32_KE33,39.htm?jl=1010063137206</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VP, Mortgage &amp; Structured Credit</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>$105K - $228K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/vp-mortgage-structured-credit-guy-carpenter-JV_IC1152672_KO0,29_KE30,43.htm?jl=1010092092965</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Product Manager</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>$120K - $204K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-product-manager-edward-jones-JV_IC1133917_KO0,22_KE23,35.htm?jl=1010061670684</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Occupational Math Tutor</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>$45.00 - $75.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/occupational-math-tutor-x-ai-JV_IC1147434_KO0,23_KE24,28.htm?jl=1010082573712</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Finance Expert - Risk</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-risk-x-ai-JV_IC1147434_KO0,19_KE20,24.htm?jl=1010082573766</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Finance Expert - Portfolio Management</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-portfolio-management-x-ai-JV_IC1147434_KO0,35_KE36,40.htm?jl=1010082573727</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Finance Expert - Corporate Finance</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-corporate-finance-x-ai-JV_IC1147434_KO0,32_KE33,37.htm?jl=1010082573838</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Investment Banking Expert - ECM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/investment-banking-expert-ecm-x-ai-JV_IC1147434_KO0,29_KE30,34.htm?jl=1010082573672</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Finance Expert - Quant</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-quant-x-ai-JV_IC1147434_KO0,20_KE21,25.htm?jl=1010082573554</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Finance Expert - Quantitative Trading</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-quantitative-trading-x-ai-JV_IC1147434_KO0,35_KE36,40.htm?jl=1010082573792</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Finance Expert - Fixed Income</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-fixed-income-x-ai-JV_KO0,27_KE28,32.htm?jl=1010111363064</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Tutor - Crypto</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-tutor-crypto-x-ai-JV_IC1147434_KO0,15_KE16,20.htm?jl=1010082573789</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Finance Expert - Credit Analyst</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-credit-analyst-x-ai-JV_IC1147434_KO0,29_KE30,34.htm?jl=1010082573764</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Finance Expert - Private Credit</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-private-credit-x-ai-JV_IC1147434_KO0,29_KE30,34.htm?jl=1010082573783</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Finance Expert - Real Estate Investment</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-real-estate-investment-x-ai-JV_IC1147434_KO0,37_KE38,42.htm?jl=1010082573771</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Finance Expert - Structured Finance</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-structured-finance-x-ai-JV_IC1147434_KO0,33_KE34,38.htm?jl=1010082573774</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>CFA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>$70K - $80K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Executive Assistant to the CEO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>$55K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>President ANC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>$318K - $406K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-anc-alutiiq-JV_IC1134201_KO0,13_KE14,21.htm?jl=1010071156640</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>$320K - $350K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-ceo-the-moran-company-JV_IC1154062_KO0,13_KE14,31.htm?jl=1010108349638</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>$170K - $175K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer - CEO</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>$145K - $160K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-ceo-ymca-JV_IC1150604_KO0,27_KE28,32.htm?jl=1010112946443</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Chief of Staff to CEO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>$220K - $275K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-of-staff-to-ceo-iterative-health-JV_IC1154545_KO0,21_KE22,38.htm?jl=1009970363828</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-anson-regional-medical-service-JV_IC1138675_KO0,23_KE24,54.htm?jl=1010104525348</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>$300K - $450K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-northwestern-medical-center-JV_IC1141798_KO0,23_KE24,51.htm?jl=1010086464392</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>$275K - $280K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1136950_KO0,23_KE24,41.htm?jl=1010097248172</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>$175K - $225K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>$140K - $150K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/executive-director-the-moran-company-JV_IC1136440_KO0,18_KE19,36.htm?jl=1010108424026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>President and CEO - Oklahoma Manufacturing Alliance</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-and-ceo-oklahoma-manufacturing-alliance-schnake-turnbo-frank-JV_IC1137055_KO0,49_KE50,70.htm?jl=1010109776782</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>President &amp; Chief Commercial Officer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>$150K - $185K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-chief-commercial-officer-check-my-policy-JV_IC1140171_KO0,34_KE35,50.htm?jl=1010094178300</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>$150K - $175K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1126720_KO0,23_KE24,41.htm?jl=1010091874998</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>City Manager</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>$200K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-marathon-JV_IC1154115_KO0,12_KE13,29.htm?jl=1010103355662</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>$150K - $220K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-lng-holding-JV_IC1128793_KO0,23_KE24,35.htm?jl=1010006337770</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>President and Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>$275K - $325K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-and-chief-executive-officer-confidential-JV_KO0,37_KE38,50.htm?jl=1010043379708</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CEO in Training (CIT), Executive Director</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>$42K - $76K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133685_KO0,38_KE39,52.htm?jl=1010088747434</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>$175K - $200K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-scion-staffing-JV_IC1150480_KO0,23_KE24,38.htm?jl=1010092080553</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CEO in Training (CIT), Executive Director</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>$46K - $84K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133406_KO0,38_KE39,52.htm?jl=1010112336554</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Regional Executive Director - Chicagoland | World Relief</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>$120K - $130K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/regional-executive-director-chicagoland-world-relief-vanderbloemen-search-group-JV_IC1128808_KO0,52_KE53,79.htm?jl=1010104739908</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Louisiana Healthcare Connections Plan President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/louisiana-healthcare-connections-plan-president-ceo-centene-JV_IC1150013_KO0,51_KE52,59.htm?jl=1010112808854</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Director, CEO Communications</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>$90K - $150K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/director-ceo-communications-ochsner-health-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010105292126</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>City Manager</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>$180K - $210K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-arvin-ca-JV_IC1146556_KO0,12_KE13,29.htm?jl=1010112565997</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>City Manager</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>$275K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/city-manager-sausalito-art-festival-JV_IC1147411_KO0,12_KE13,35.htm?jl=1010015848250</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>City Manager - Annapolis, MD</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>$250K - $294K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/city-manager-annapolis-md-annapolis-market-house-md-JV_IC1153523_KO0,25_KE26,51.htm?jl=1010023329394</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>City Manager</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>$274K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/city-manager-county-of-sonoma-JV_IC1147520_KO0,12_KE13,29.htm?jl=1010107011390</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>President and General Manager, WPVI-TV</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>$412K - $553K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-and-general-manager-wpvi-tv-walt-disney-company-JV_IC1152672_KO0,37_KE38,57.htm?jl=1009865634435</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>President - BVCI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/president-bvci-black-veatch-JV_IC1151049_KO0,14_KE15,27.htm?jl=1010009377310</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Bioinformatics Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>$80K - $85K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/bioinformatics-analyst-agendia-JV_KO0,22_KE23,30.htm?jl=1010110968052</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>$50.00 - $55.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-brooksource-JV_IC1154170_KO0,14_KE15,26.htm?jl=1010114754582</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Scientist / Generative AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>$85K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-generative-ai-data-engineer-specialized-staffing-solutions-JV_IC1145261_KO0,42_KE43,73.htm?jl=1010101551039</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>$70K - $80K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-developer-mifab-JV_IC1128808_KO0,12_KE13,18.htm?jl=1010103162764</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>$138K - $275K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/trust-safety-machine-learning-engineer-zoom-JV_IC1147436_KO0,38_KE39,43.htm?jl=1010103395317</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>$163K - $173K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-brooksource-JV_IC1152672_KO0,21_KE22,33.htm?jl=1010114706169</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>$80K - $90K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/computer-science-teacher-kūlia-academy-JV_IC1140656_KO0,24_KE25,38.htm?jl=1009966984742</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Associate Director, Data Science - Market Access</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>$149K - $215K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-market-access-sanofi-JV_IC1154545_KO0,45_KE46,52.htm?jl=1010050421211</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ML/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>$80K - $120K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ml-ai-engineer-midwest-machine-llc-JV_IC1139740_KO0,14_KE15,34.htm?jl=1010109262064</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Director, Commercial Data Science - Hampton, NJ</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>$177K - $229K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/director-commercial-data-science-hampton-nj-celldex-JV_IC1126790_KO0,43_KE44,51.htm?jl=1010072517837</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Applied AI/Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>$150K - $200K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/applied-ai-machine-learning-engineer-oddball-JV_IC1158535_KO0,36_KE37,44.htm?jl=1010075983886</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Scientist - AI Trainer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>$40.00 - $60.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-ai-trainer-dataannotation-JV_IC1148112_KO0,25_KE26,40.htm?jl=1010080136077</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Scientist (In Person - Austin, TX)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>$135K - $170K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-in-person-austin-tx-tommbo-com-JV_IC1139761_KO0,34_KE35,45.htm?jl=1010046625687</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>$124K - $165K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/sr-data-scientist-the-hershey-company-JV_IC1139977_KO0,17_KE18,37.htm?jl=1009569149385</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Specialist</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>$71K - $123K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-specialist-commonwealth-equipment-corp-JV_IC1165586_KO0,13_KE14,41.htm?jl=1010101947687</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Lab Data Scientist</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>$75K - $80K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/lab-data-scientist-geveko-markings-usa-JV_IC1155838_KO0,18_KE19,38.htm?jl=1010104506793</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Data Product Lead</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>$100K - $139K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-data-product-lead-mariner-finance-JV_IC1151049_KO0,24_KE25,40.htm?jl=1010081192082</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sr. Exploitation Specialist/Data Scientist (TS/SCI)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>$117K - $195K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/sr-exploitation-specialist-data-scientist-ts-sci-culmen-international-JV_IC1154170_KO0,48_KE49,69.htm?jl=1010041116784</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; Network Analyst</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/infrastructure-network-analyst-outerlink-global-solutions-JV_IC1150108_KO0,30_KE31,57.htm?jl=1010109233580</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI and Automation Engineer (Business Analysis, Senior Analyst)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>$100K - $115K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-and-automation-engineer-business-analysis-senior-analyst-the-mil-corporation-JV_IC1155074_KO0,59_KE60,79.htm?jl=1010101966087</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Director, Enterprise Data Architecture and Analytics</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>$174K - $216K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-director-enterprise-data-architecture-and-analytics-pattern-energy-group-JV_IC1147401_KO0,58_KE59,79.htm?jl=1009990778925</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Artificial Intelligence (AI) Developer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>$68K - $114K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-artificial-intelligence-ai-developer-amtelco-JV_IC3740374_KO0,43_KE44,51.htm?jl=1010109218562</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Applied Research Mathematician / Generative AI</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>$133K - $197K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/applied-research-mathematician-generative-ai-national-security-agency-JV_IC1165756_KO0,44_KE45,69.htm?jl=1010108944998</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Software Engineer, Agentic Systems</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>$160K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/software-engineer-agentic-systems-incommodities-JV_IC1139761_KO0,33_KE34,47.htm?jl=1010084207208</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Gen AI Engineering Analyst - Vice President</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>$114K - $171K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/gen-ai-engineering-analyst-vice-president-citi-JV_IC1154093_KO0,41_KE42,46.htm?jl=1010114737667</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Technical target analyst</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>$70K - $185K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/technical-target-analyst-cia-JV_IC1138213_KO0,24_KE25,28.htm?jl=1009964046918</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>$130K - $150K(Employer provided)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>https://www.glassdoor.com/job-listing/data-scientist-the-judge-group-JV_IC1140494_KO0,14_KE15,30.htm?jl=1010106793793</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>Data Science</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>AI Innovation Engineer | Bridging Craftsmanship and the Future</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>$80K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-innovation-engineer-bridging-craftsmanship-and-the-future-miami-prestige-interiors-JV_IC1154170_KO0,60_KE61,85.htm?jl=1010105305197</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>$160K - $185K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-engineer-friant-associates-JV_IC1147404_KO0,11_KE12,29.htm?jl=1010037044723</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (SWE-3)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>$108K - $195K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-ai-engineer-swe-3-leidos-JV_IC1153599_KO0,24_KE25,31.htm?jl=1010062832518</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/Glassdoor_Jobs_2026-04-28.xlsx
+++ b/Glassdoor_Jobs_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$81K - $104K(Employer provided)</t>
+          <t>$86K - $114K(Employer provided)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1164305_KO0,21_KE22,40.htm?jl=1010038441282</t>
+          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1133911_KO0,21_KE22,40.htm?jl=1010038425988</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1148170_KO0,21_KE22,40.htm?jl=1010100922250</t>
+          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1148170_KO0,21_KE22,40.htm?jl=1010038451649</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hybrid Behavior Analyst (BCBA)</t>
+          <t>Behavior Analyst (BCBA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/hybrid-behavior-analyst-bcba-soar-autism-center-JV_KO0,28_KE29,47.htm?jl=1010054630392</t>
+          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1148170_KO0,21_KE22,40.htm?jl=1010100922250</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Business Analyst 1</t>
+          <t>Senior Sales Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,12 +569,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$34.66 - $36.00Per Hour(Employer provided)</t>
+          <t>$68K - $99K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/business-analyst-1-insync-staffing-JV_IC1151576_KO0,18_KE19,34.htm?jl=1010114536750</t>
+          <t>https://www.glassdoor.com/job-listing/senior-sales-analyst-breakthru-beverage-group-JV_IC1155147_KO0,20_KE21,45.htm?jl=1010114667197</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HRIS Analyst</t>
+          <t>Program Cost and Schedule Control Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -599,10 +599,14 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>$125.93Per Hour(Employer provided)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/hris-analyst-beusa-energy-JV_IC1140171_KO0,12_KE13,25.htm?jl=1010106990644</t>
+          <t>https://www.glassdoor.com/job-listing/program-cost-and-schedule-control-analyst-apr-consulting-JV_IC1147311_KO0,41_KE42,56.htm?jl=1010112675047</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -619,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Business Analyst I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -629,12 +633,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$105K - $115K(Employer provided)</t>
+          <t>$53K - $70K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/business-analyst-12-elements-consulting-JV_IC1139790_KO0,16_KE17,39.htm?jl=1010053067441</t>
+          <t>https://www.glassdoor.com/job-listing/business-analyst-i-php-agency-JV_IC1139977_KO0,18_KE19,29.htm?jl=1010115251725</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -651,7 +655,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Financial Analyst</t>
+          <t>Financial Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -661,12 +665,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$70K - $75K(Employer provided)</t>
+          <t>$75K - $106K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/junior-financial-analyst-gl-staffing-services-JV_IC1154160_KO0,24_KE25,45.htm?jl=1010115041405</t>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-selby-jennings-JV_IC1154532_KO0,17_KE18,32.htm?jl=1010114539700</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -683,7 +687,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Population Health Data Analyst</t>
+          <t>Job Cost Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -693,12 +697,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$44.10 - $68.53Per Hour(Employer provided)</t>
+          <t>$57K - $82K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-population-health-data-analyst-torrance-memorial-medical-center-JV_IC1146894_KO0,37_KE38,70.htm?jl=1010093309288</t>
+          <t>https://www.glassdoor.com/job-listing/job-cost-analyst-vee-jay-cement-contracting-JV_IC1131270_KO0,16_KE17,43.htm?jl=1010114961842</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -747,7 +751,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Financial Analyst III</t>
+          <t>Sr. Financial Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -757,12 +761,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$106K - $130K(Employer provided)</t>
+          <t>$70K - $87K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/financial-analyst-iii-greenheck-group-JV_IC1142551_KO0,21_KE22,37.htm?jl=1010038412231</t>
+          <t>https://www.glassdoor.com/job-listing/sr-financial-analyst-safecor-health-JV_IC1145845_KO0,20_KE21,35.htm?jl=1010093412811</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -779,7 +783,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT FinOps Analyst</t>
+          <t>Cost Engineer / Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -789,12 +793,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$104K - $141K(Employer provided)</t>
+          <t>$65.00 - $80.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/it-finops-analyst-atlas-air-worldwide-JV_IC1132464_KO0,17_KE18,37.htm?jl=1010082614845</t>
+          <t>https://www.glassdoor.com/job-listing/cost-engineer-analyst-innovative-turnaround-controls-JV_IC1152640_KO0,21_KE22,52.htm?jl=1010007520522</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -811,7 +815,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>National Account Sales Analyst - Retail</t>
+          <t>Financial Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -821,12 +825,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$50K - $60K(Employer provided)</t>
+          <t>$63K - $96K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/national-account-sales-analyst-retail-enerco-JV_IC1145778_KO0,37_KE38,44.htm?jl=1010114768785</t>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-hydro-JV_IC1146170_KO0,17_KE18,23.htm?jl=1010108517953</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -843,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Laboratory Analyst - Afternoon Shift (Seattle, WA)</t>
+          <t>Sales Commission Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -851,14 +855,10 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>$22.00 - $24.00Per Hour(Employer provided)</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/laboratory-analyst-afternoon-shift-seattle-wa-ieh-laboratories-consulting-group-JV_IC1150505_KO0,45_KE46,79.htm?jl=1010115098281</t>
+          <t>https://www.glassdoor.com/job-listing/sales-commission-analyst-adobe-JV_IC1128238_KO0,24_KE25,30.htm?jl=1010107209881</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Job Cost Analyst</t>
+          <t>Chemical Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$57K - $82K(Glassdoor est.)</t>
+          <t>$53K - $70K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/job-cost-analyst-vee-jay-cement-contracting-JV_IC1131270_KO0,16_KE17,43.htm?jl=1010114961842</t>
+          <t>https://www.glassdoor.com/job-listing/chemical-analyst-materion-JV_IC1145796_KO0,16_KE17,25.htm?jl=1010114458569</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -907,7 +907,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Corporate Financial Analyst</t>
+          <t>Analyst / Associate, Infrastructure and Energy Debt Advisory</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$65K - $85K(Employer provided)</t>
+          <t>$110K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/corporate-financial-analyst-centro-iowa-JV_IC1149335_KO0,27_KE28,39.htm?jl=1010061590757</t>
+          <t>https://www.glassdoor.com/job-listing/analyst-associate-infrastructure-and-energy-debt-advisory-macquarie-group-JV_IC1132348_KO0,57_KE58,73.htm?jl=1010114916735</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chemical Analyst</t>
+          <t>Accounting Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$53K - $70K(Glassdoor est.)</t>
+          <t>$28.00 - $32.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chemical-analyst-materion-JV_IC1145796_KO0,16_KE17,25.htm?jl=1010114458569</t>
+          <t>https://www.glassdoor.com/job-listing/accounting-analyst-talentburst-JV_IC1138922_KO0,18_KE19,30.htm?jl=1010114789828</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Loan Origination Systems Support Analyst</t>
+          <t>Sales Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$50K - $71K(Glassdoor est.)</t>
+          <t>$57K - $86K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/loan-origination-systems-support-analyst-oakstar-bank-JV_IC1131348_KO0,40_KE41,53.htm?jl=1010111062272</t>
+          <t>https://www.glassdoor.com/job-listing/sales-analyst-victaulic-JV_IC1151932_KO0,13_KE14,23.htm?jl=1010083969774</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Sales Analyst</t>
+          <t>Senior Acquisitions Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$68K - $99K(Glassdoor est.)</t>
+          <t>$80K - $100K(Employer provided)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-sales-analyst-breakthru-beverage-group-JV_IC1155147_KO0,20_KE21,45.htm?jl=1010114667197</t>
+          <t>https://www.glassdoor.com/job-listing/senior-acquisitions-analyst-marquette-management-JV_IC1128808_KO0,27_KE28,48.htm?jl=1010109648829</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analyst / Associate, Infrastructure and Energy Debt Advisory</t>
+          <t>Junior Financial Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$110K - $200K(Employer provided)</t>
+          <t>$70K - $75K(Employer provided)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/analyst-associate-infrastructure-and-energy-debt-advisory-macquarie-group-JV_IC1132348_KO0,57_KE58,73.htm?jl=1010114916735</t>
+          <t>https://www.glassdoor.com/job-listing/junior-financial-analyst-gl-staffing-services-JV_IC1154160_KO0,24_KE25,45.htm?jl=1010115041405</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT Analyst</t>
+          <t>QA Lab Analyst- Analytical</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$65K - $75K(Employer provided)</t>
+          <t>$20.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/it-analyst-great-lakes-castings-JV_IC1134383_KO0,10_KE11,31.htm?jl=1010111083685</t>
+          <t>https://www.glassdoor.com/job-listing/qa-lab-analyst-analytical-mayer-brothers-JV_IC1158943_KO0,25_KE26,40.htm?jl=1010108261024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analyst II - Product System Configuration</t>
+          <t>Quality Improvement Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$80K - $106K(Employer provided)</t>
+          <t>$58K - $93K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/analyst-ii-product-system-configuration-inland-empire-health-plan-JV_IC1147132_KO0,39_KE40,65.htm?jl=1009813420167</t>
+          <t>https://www.glassdoor.com/job-listing/quality-improvement-analyst-true-rx-management-services-JV_IC1145353_KO0,27_KE28,55.htm?jl=1010095460719</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Investment Analyst</t>
+          <t>Sales Operations Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$110K - $150K(Employer provided)</t>
+          <t>$65K - $85K(Employer provided)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-analyst-terreno-realty-corporation-JV_IC1150442_KO0,18_KE19,45.htm?jl=1010064278960</t>
+          <t>https://www.glassdoor.com/job-listing/sales-operations-analyst-visa-lighting-an-oldenburg-group-company-JV_IC1133579_KO0,24_KE25,65.htm?jl=1010074838658</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1163,7 +1163,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Import Analyst</t>
+          <t>Investment Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$55K - $70K(Employer provided)</t>
+          <t>$110K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/import-analyst-dillard-s-JV_KO0,14_KE15,24.htm?jl=1010100715804</t>
+          <t>https://www.glassdoor.com/job-listing/investment-analyst-terreno-realty-corporation-JV_IC1150442_KO0,18_KE19,45.htm?jl=1010064278960</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Process Analyst</t>
+          <t>Benefits Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$60K(Employer provided)</t>
+          <t>$58K - $74K(Employer provided)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/process-analyst-komico-hillsboro-JV_IC1151603_KO0,15_KE16,32.htm?jl=1010109685799</t>
+          <t>https://www.glassdoor.com/job-listing/benefits-analyst-brookdale-senior-living-JV_IC1144496_KO0,16_KE17,40.htm?jl=1010115089470</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Financial Systems Analyst</t>
+          <t>Sales and Marketing Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$66K - $94K(Glassdoor est.)</t>
+          <t>$60K - $70K(Employer provided)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/financial-systems-analyst-pappas-restaurants-JV_IC1140171_KO0,25_KE26,44.htm?jl=1010088757112</t>
+          <t>https://www.glassdoor.com/job-listing/sales-and-marketing-analyst-gsc-enterprises-JV_IC1140540_KO0,27_KE28,43.htm?jl=1010109888516</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Business Analyst</t>
+          <t>Client Support Center Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$120K - $160K(Employer provided)</t>
+          <t>$33K - $55K(Employer provided)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-business-analyst-genesis-capital-ca-JV_IC1146875_KO0,23_KE24,42.htm?jl=1009971786272</t>
+          <t>https://www.glassdoor.com/job-listing/client-support-center-analyst-athenahealth-JV_IC1135503_KO0,29_KE30,42.htm?jl=1010100458393</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Support Analyst</t>
+          <t>Sales Tax Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$44K - $59K(Glassdoor est.)</t>
+          <t>$51K - $68K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/it-support-analyst-van-andel-research-institute-JV_IC1134796_KO0,18_KE19,47.htm?jl=1010110029456</t>
+          <t>https://www.glassdoor.com/job-listing/sales-tax-analyst-pleasant-valley-corporation-JV_IC1145799_KO0,17_KE18,45.htm?jl=1010073039141</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Business Analyst - In Person</t>
+          <t>Intelligence Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$70K - $80K(Employer provided)</t>
+          <t>$59K - $107K(Employer provided)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/business-analyst-in-person-the-boat-house-JV_IC1135926_KO0,26_KE27,41.htm?jl=1010091637363</t>
+          <t>https://www.glassdoor.com/job-listing/intelligence-analyst-leidos-JV_IC1147652_KO0,20_KE21,27.htm?jl=1010114963762</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Business Analyst - Healthcare</t>
+          <t>Service &amp; Sales Operations Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$59K - $86K(Glassdoor est.)</t>
+          <t>$57K - $81K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/business-analyst-healthcare-retina-group-of-florida-JV_IC1154154_KO0,27_KE28,51.htm?jl=1010106778321</t>
+          <t>https://www.glassdoor.com/job-listing/service-sales-operations-analyst-pitco-nh-JV_IC1147785_KO0,32_KE33,41.htm?jl=1010063149721</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>ServiceNow Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$80K - $100K(Employer provided)</t>
+          <t>$46.50 - $62.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/financial-analyst-columbus-downtown-development-corporation-JV_IC1145845_KO0,17_KE18,59.htm?jl=1010078938074</t>
+          <t>https://www.glassdoor.com/job-listing/servicenow-analyst-compucom-JV_IC1155583_KO0,18_KE19,27.htm?jl=1010114685532</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>$82K - $126K(Glassdoor est.)</t>
+          <t>$82K - $127K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Strategic Investor Communications Lead</t>
+          <t>Principal, Energy Infrastructure Investments</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>$189K - $284K(Employer provided)</t>
+          <t>$246K - $306K(Employer provided)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/strategic-investor-communications-lead-ge-healthcare-JV_IC1128808_KO0,38_KE39,52.htm?jl=1010045621776</t>
+          <t>https://www.glassdoor.com/job-listing/principal-energy-infrastructure-investments-meta-JV_IC1132348_KO0,43_KE44,48.htm?jl=1010112675924</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1803,7 +1803,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Collections Specialist</t>
+          <t>Strategic Investor Communications Lead</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1813,12 +1813,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>$65K - $126K(Employer provided)</t>
+          <t>$189K - $284K(Employer provided)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/collections-specialist-gallagher-JV_IC1128962_KO0,22_KE23,32.htm?jl=1009960182119</t>
+          <t>https://www.glassdoor.com/job-listing/strategic-investor-communications-lead-ge-healthcare-JV_IC1128808_KO0,38_KE39,52.htm?jl=1010045621776</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Investment Specialist</t>
+          <t>Collections Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$134K - $269K(Employer provided)</t>
+          <t>$65K - $126K(Employer provided)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-specialist-rsm-JV_KO0,21_KE22,25.htm?jl=1010071186146</t>
+          <t>https://www.glassdoor.com/job-listing/collections-specialist-gallagher-JV_IC1128962_KO0,22_KE23,32.htm?jl=1009960182119</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1867,7 +1867,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Alternatives Data Analyst</t>
+          <t>Investment Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>$68.00Per Hour(Employer provided)</t>
+          <t>$134K - $269K(Employer provided)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-alternatives-data-analyst-mercer-JV_IC1154532_KO0,32_KE33,39.htm?jl=1010063137206</t>
+          <t>https://www.glassdoor.com/job-listing/investment-specialist-rsm-JV_KO0,21_KE22,25.htm?jl=1010071186146</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VP, Mortgage &amp; Structured Credit</t>
+          <t>Senior Alternatives Data Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>$105K - $228K(Employer provided)</t>
+          <t>$68.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/vp-mortgage-structured-credit-guy-carpenter-JV_IC1152672_KO0,29_KE30,43.htm?jl=1010092092965</t>
+          <t>https://www.glassdoor.com/job-listing/senior-alternatives-data-analyst-mercer-JV_IC1154532_KO0,32_KE33,39.htm?jl=1010063137206</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Occupational Math Tutor</t>
+          <t>Finance Expert - Fixed Income</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$45.00 - $75.00Per Hour(Employer provided)</t>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/occupational-math-tutor-x-ai-JV_IC1147434_KO0,23_KE24,28.htm?jl=1010082573712</t>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-fixed-income-x-ai-JV_KO0,27_KE28,32.htm?jl=1010111363064</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Finance Expert - Risk</t>
+          <t>FX Treasury Manager</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$119K - $191K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-risk-x-ai-JV_IC1147434_KO0,19_KE20,24.htm?jl=1010082573766</t>
+          <t>https://www.glassdoor.com/job-listing/fx-treasury-manager-salesforce-JV_IC1155583_KO0,19_KE20,30.htm?jl=1010091996431</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2027,7 +2027,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Finance Expert - Portfolio Management</t>
+          <t>Securities &amp; Commodities Specialist - Freelance AI Trainer Project</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$8.00 - $65.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-portfolio-management-x-ai-JV_IC1147434_KO0,35_KE36,40.htm?jl=1010082573727</t>
+          <t>https://www.glassdoor.com/job-listing/securities-commodities-specialist-freelance-ai-trainer-project-invisible-technologies-JV_IC1139977_KO0,62_KE63,85.htm?jl=1010082625711</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Finance Expert - Corporate Finance</t>
+          <t>VP, AI Risk Manager</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$159K - $271K(Employer provided)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-corporate-finance-x-ai-JV_IC1147434_KO0,32_KE33,37.htm?jl=1010082573838</t>
+          <t>https://www.glassdoor.com/job-listing/vp-ai-risk-manager-chubb-JV_IC1127046_KO0,18_KE19,24.htm?jl=1010005026857</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Investment Banking Expert - ECM</t>
+          <t>Sr. Program Manager</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$40.00 - $60.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-banking-expert-ecm-x-ai-JV_IC1147434_KO0,29_KE30,34.htm?jl=1010082573672</t>
+          <t>https://www.glassdoor.com/job-listing/sr-program-manager-cedent-JV_KO0,18_KE19,25.htm?jl=1009382584851</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2123,7 +2123,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Finance Expert - Quant</t>
+          <t>Equity Strategist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$145K - $173K(Employer provided)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-quant-x-ai-JV_IC1147434_KO0,20_KE21,25.htm?jl=1010082573554</t>
+          <t>https://www.glassdoor.com/job-listing/equity-strategist-ubs-JV_KO0,17_KE18,21.htm?jl=1010109601778</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Finance Expert - Quantitative Trading</t>
+          <t>AVP, Advisory Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$104K - $173K(Employer provided)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-quantitative-trading-x-ai-JV_IC1147434_KO0,35_KE36,40.htm?jl=1010082573792</t>
+          <t>https://www.glassdoor.com/job-listing/avp-advisory-consultant-lpl-financial-JV_IC1155108_KO0,23_KE24,37.htm?jl=1010094647514</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2187,7 +2187,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Finance Expert - Fixed Income</t>
+          <t>VP, Alternative Investments Platform Management</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$145K - $241K(Employer provided)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-fixed-income-x-ai-JV_KO0,27_KE28,32.htm?jl=1010111363064</t>
+          <t>https://www.glassdoor.com/job-listing/vp-alternative-investments-platform-management-lpl-financial-JV_IC1155108_KO0,46_KE47,60.htm?jl=1010102268301</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Tutor - Crypto</t>
+          <t>Regulatory Reporting QA Vice President</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$140K - $185K(Employer provided)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-tutor-crypto-x-ai-JV_IC1147434_KO0,15_KE16,20.htm?jl=1010082573789</t>
+          <t>https://www.glassdoor.com/job-listing/regulatory-reporting-qa-vice-president-sumitomo-pharma-JV_IC1126819_KO0,38_KE39,54.htm?jl=1010084228891</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Finance Expert - Credit Analyst</t>
+          <t>Net Asset Value (NAV), Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$110K - $125K(Employer provided)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-credit-analyst-x-ai-JV_IC1147434_KO0,29_KE30,34.htm?jl=1010082573764</t>
+          <t>https://www.glassdoor.com/job-listing/net-asset-value-nav-analyst-sumitomo-pharma-JV_KO0,27_KE28,43.htm?jl=1010106784232</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Finance Expert - Private Credit</t>
+          <t>Distribution Risk Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$143K - $185K(Employer provided)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-private-credit-x-ai-JV_IC1147434_KO0,29_KE30,34.htm?jl=1010082573783</t>
+          <t>https://www.glassdoor.com/job-listing/distribution-risk-specialist-sumitomo-pharma-JV_KO0,28_KE29,44.htm?jl=1010091955697</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2315,7 +2315,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Finance Expert - Real Estate Investment</t>
+          <t>Product Analyst Custom Indices- Enterprise Data</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$110K - $225K(Employer provided)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-real-estate-investment-x-ai-JV_IC1147434_KO0,37_KE38,42.htm?jl=1010082573771</t>
+          <t>https://www.glassdoor.com/job-listing/product-analyst-custom-indices-enterprise-data-bloomberg-JV_IC1132348_KO0,46_KE47,56.htm?jl=1010065219020</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Finance Expert - Structured Finance</t>
+          <t>Bloomberg Intelligence, Thematic Strategist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$215K - $285K(Employer provided)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-structured-finance-x-ai-JV_IC1147434_KO0,33_KE34,38.htm?jl=1010082573774</t>
+          <t>https://www.glassdoor.com/job-listing/bloomberg-intelligence-thematic-strategist-bloomberg-JV_IC1132348_KO0,42_KE43,52.htm?jl=1010072907857</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2371,1906 +2371,6 @@
         </is>
       </c>
       <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Executive Director</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>$70K - $80K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Executive Assistant to the CEO</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>$55K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>President ANC</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>$318K - $406K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-anc-alutiiq-JV_IC1134201_KO0,13_KE14,21.htm?jl=1010071156640</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>President &amp; CEO</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>$320K - $350K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-ceo-the-moran-company-JV_IC1154062_KO0,13_KE14,31.htm?jl=1010108349638</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>$170K - $175K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer - CEO</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>$145K - $160K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-ceo-ymca-JV_IC1150604_KO0,27_KE28,32.htm?jl=1010112946443</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Chief of Staff to CEO</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>$220K - $275K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-of-staff-to-ceo-iterative-health-JV_IC1154545_KO0,21_KE22,38.htm?jl=1009970363828</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-anson-regional-medical-service-JV_IC1138675_KO0,23_KE24,54.htm?jl=1010104525348</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>$300K - $450K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-northwestern-medical-center-JV_IC1141798_KO0,23_KE24,51.htm?jl=1010086464392</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>$275K - $280K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1136950_KO0,23_KE24,41.htm?jl=1010097248172</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>$175K - $225K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Executive Director</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>$140K - $150K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-the-moran-company-JV_IC1136440_KO0,18_KE19,36.htm?jl=1010108424026</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>President and CEO - Oklahoma Manufacturing Alliance</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-ceo-oklahoma-manufacturing-alliance-schnake-turnbo-frank-JV_IC1137055_KO0,49_KE50,70.htm?jl=1010109776782</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>President &amp; Chief Commercial Officer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>$150K - $185K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-chief-commercial-officer-check-my-policy-JV_IC1140171_KO0,34_KE35,50.htm?jl=1010094178300</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>$150K - $175K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1126720_KO0,23_KE24,41.htm?jl=1010091874998</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>City Manager</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>$200K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-marathon-JV_IC1154115_KO0,12_KE13,29.htm?jl=1010103355662</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>$150K - $220K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-lng-holding-JV_IC1128793_KO0,23_KE24,35.htm?jl=1010006337770</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>President and Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>$275K - $325K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-chief-executive-officer-confidential-JV_KO0,37_KE38,50.htm?jl=1010043379708</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>CEO in Training (CIT), Executive Director</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>$42K - $76K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133685_KO0,38_KE39,52.htm?jl=1010088747434</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>$175K - $200K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-scion-staffing-JV_IC1150480_KO0,23_KE24,38.htm?jl=1010092080553</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>CEO in Training (CIT), Executive Director</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>$46K - $84K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133406_KO0,38_KE39,52.htm?jl=1010112336554</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Regional Executive Director - Chicagoland | World Relief</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>$120K - $130K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/regional-executive-director-chicagoland-world-relief-vanderbloemen-search-group-JV_IC1128808_KO0,52_KE53,79.htm?jl=1010104739908</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Louisiana Healthcare Connections Plan President &amp; CEO</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/louisiana-healthcare-connections-plan-president-ceo-centene-JV_IC1150013_KO0,51_KE52,59.htm?jl=1010112808854</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Director, CEO Communications</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>$90K - $150K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/director-ceo-communications-ochsner-health-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010105292126</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>City Manager</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>$180K - $210K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-arvin-ca-JV_IC1146556_KO0,12_KE13,29.htm?jl=1010112565997</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>City Manager</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>$275K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-sausalito-art-festival-JV_IC1147411_KO0,12_KE13,35.htm?jl=1010015848250</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>City Manager - Annapolis, MD</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>$250K - $294K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-annapolis-md-annapolis-market-house-md-JV_IC1153523_KO0,25_KE26,51.htm?jl=1010023329394</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>City Manager</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>$274K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-county-of-sonoma-JV_IC1147520_KO0,12_KE13,29.htm?jl=1010107011390</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>President and General Manager, WPVI-TV</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>$412K - $553K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-general-manager-wpvi-tv-walt-disney-company-JV_IC1152672_KO0,37_KE38,57.htm?jl=1009865634435</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>President - BVCI</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/president-bvci-black-veatch-JV_IC1151049_KO0,14_KE15,27.htm?jl=1010009377310</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Bioinformatics Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>$80K - $85K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/bioinformatics-analyst-agendia-JV_KO0,22_KE23,30.htm?jl=1010110968052</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>$50.00 - $55.00Per Hour(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-brooksource-JV_IC1154170_KO0,14_KE15,26.htm?jl=1010114754582</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Scientist / Generative AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>$85K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-generative-ai-data-engineer-specialized-staffing-solutions-JV_IC1145261_KO0,42_KE43,73.htm?jl=1010101551039</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>$70K - $80K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ai-developer-mifab-JV_IC1128808_KO0,12_KE13,18.htm?jl=1010103162764</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>$138K - $275K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/trust-safety-machine-learning-engineer-zoom-JV_IC1147436_KO0,38_KE39,43.htm?jl=1010103395317</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>$163K - $173K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-brooksource-JV_IC1152672_KO0,21_KE22,33.htm?jl=1010114706169</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Computer Science Teacher</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>$80K - $90K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/computer-science-teacher-kūlia-academy-JV_IC1140656_KO0,24_KE25,38.htm?jl=1009966984742</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Associate Director, Data Science - Market Access</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>$149K - $215K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-market-access-sanofi-JV_IC1154545_KO0,45_KE46,52.htm?jl=1010050421211</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>ML/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>$80K - $120K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ml-ai-engineer-midwest-machine-llc-JV_IC1139740_KO0,14_KE15,34.htm?jl=1010109262064</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Director, Commercial Data Science - Hampton, NJ</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>$177K - $229K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/director-commercial-data-science-hampton-nj-celldex-JV_IC1126790_KO0,43_KE44,51.htm?jl=1010072517837</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Applied AI/Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>$150K - $200K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/applied-ai-machine-learning-engineer-oddball-JV_IC1158535_KO0,36_KE37,44.htm?jl=1010075983886</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Scientist - AI Trainer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>$40.00 - $60.00Per Hour(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-ai-trainer-dataannotation-JV_IC1148112_KO0,25_KE26,40.htm?jl=1010080136077</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Data Scientist (In Person - Austin, TX)</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>$135K - $170K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-in-person-austin-tx-tommbo-com-JV_IC1139761_KO0,34_KE35,45.htm?jl=1010046625687</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>$124K - $165K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/sr-data-scientist-the-hershey-company-JV_IC1139977_KO0,17_KE18,37.htm?jl=1009569149385</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>AI Specialist</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>$71K - $123K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ai-specialist-commonwealth-equipment-corp-JV_IC1165586_KO0,13_KE14,41.htm?jl=1010101947687</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Lab Data Scientist</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>$75K - $80K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/lab-data-scientist-geveko-markings-usa-JV_IC1155838_KO0,18_KE19,38.htm?jl=1010104506793</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Data Product Lead</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>$100K - $139K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/senior-data-product-lead-mariner-finance-JV_IC1151049_KO0,24_KE25,40.htm?jl=1010081192082</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr. Exploitation Specialist/Data Scientist (TS/SCI)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>$117K - $195K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/sr-exploitation-specialist-data-scientist-ts-sci-culmen-international-JV_IC1154170_KO0,48_KE49,69.htm?jl=1010041116784</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Infrastructure &amp; Network Analyst</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/infrastructure-network-analyst-outerlink-global-solutions-JV_IC1150108_KO0,30_KE31,57.htm?jl=1010109233580</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>AI and Automation Engineer (Business Analysis, Senior Analyst)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>$100K - $115K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ai-and-automation-engineer-business-analysis-senior-analyst-the-mil-corporation-JV_IC1155074_KO0,59_KE60,79.htm?jl=1010101966087</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Director, Enterprise Data Architecture and Analytics</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>$174K - $216K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/senior-director-enterprise-data-architecture-and-analytics-pattern-energy-group-JV_IC1147401_KO0,58_KE59,79.htm?jl=1009990778925</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Artificial Intelligence (AI) Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>$68K - $114K(Glassdoor est.)</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/senior-artificial-intelligence-ai-developer-amtelco-JV_IC3740374_KO0,43_KE44,51.htm?jl=1010109218562</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Applied Research Mathematician / Generative AI</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>$133K - $197K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/applied-research-mathematician-generative-ai-national-security-agency-JV_IC1165756_KO0,44_KE45,69.htm?jl=1010108944998</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Software Engineer, Agentic Systems</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>$160K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/software-engineer-agentic-systems-incommodities-JV_IC1139761_KO0,33_KE34,47.htm?jl=1010084207208</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Gen AI Engineering Analyst - Vice President</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>$114K - $171K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/gen-ai-engineering-analyst-vice-president-citi-JV_IC1154093_KO0,41_KE42,46.htm?jl=1010114737667</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Technical target analyst</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>$70K - $185K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/technical-target-analyst-cia-JV_IC1138213_KO0,24_KE25,28.htm?jl=1009964046918</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>$130K - $150K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-the-judge-group-JV_IC1140494_KO0,14_KE15,30.htm?jl=1010106793793</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>AI Innovation Engineer | Bridging Craftsmanship and the Future</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>$80K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ai-innovation-engineer-bridging-craftsmanship-and-the-future-miami-prestige-interiors-JV_IC1154170_KO0,60_KE61,85.htm?jl=1010105305197</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>$160K - $185K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/ai-engineer-friant-associates-JV_IC1147404_KO0,11_KE12,29.htm?jl=1010037044723</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer (SWE-3)</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>$108K - $195K(Employer provided)</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>https://www.glassdoor.com/job-listing/senior-ai-engineer-swe-3-leidos-JV_IC1153599_KO0,24_KE25,31.htm?jl=1010062832518</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Data Science</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/Glassdoor_Jobs_2026-04-28.xlsx
+++ b/Glassdoor_Jobs_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Behavior Analyst (BCBA)</t>
+          <t>Portfolio Manager</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$86K - $114K(Employer provided)</t>
+          <t>$250K(Employer provided)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1133911_KO0,21_KE22,40.htm?jl=1010038425988</t>
+          <t>https://www.glassdoor.com/job-listing/portfolio-manager-creative-financial-staffing-JV_IC1154247_KO0,17_KE18,45.htm?jl=1010107182315</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Behavior Analyst (BCBA)</t>
+          <t>Equity Research - REITs - Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -505,17 +505,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$81K - $104K(Employer provided)</t>
+          <t>$150K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1148170_KO0,21_KE22,40.htm?jl=1010038451649</t>
+          <t>https://www.glassdoor.com/job-listing/equity-research-reits-associate-jpmorgan-chase-co-JV_IC1132348_KO0,31_KE32,49.htm?jl=1010070497398</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Behavior Analyst (BCBA)</t>
+          <t>Equity Research - Specialty &amp; Consumer Finance - Associate</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$81K - $104K(Employer provided)</t>
+          <t>$150K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1148170_KO0,21_KE22,40.htm?jl=1010100922250</t>
+          <t>https://www.glassdoor.com/job-listing/equity-research-specialty-consumer-finance-associate-jpmorgan-chase-co-JV_KO0,52_KE53,70.htm?jl=1010098630208</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Sales Analyst</t>
+          <t>Equity Research - Utilities - Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -569,17 +569,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$68K - $99K(Glassdoor est.)</t>
+          <t>$150K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-sales-analyst-breakthru-beverage-group-JV_IC1155147_KO0,20_KE21,45.htm?jl=1010114667197</t>
+          <t>https://www.glassdoor.com/job-listing/equity-research-utilities-associate-jpmorgan-chase-co-JV_KO0,35_KE36,53.htm?jl=1010106989954</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Program Cost and Schedule Control Analyst</t>
+          <t>Portfolio &amp; Performance Analyst - Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -601,17 +601,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$125.93Per Hour(Employer provided)</t>
+          <t>$76K - $105K(Employer provided)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/program-cost-and-schedule-control-analyst-apr-consulting-JV_IC1147311_KO0,41_KE42,56.htm?jl=1010112675047</t>
+          <t>https://www.glassdoor.com/job-listing/portfolio-performance-analyst-associate-jpmorgan-chase-co-JV_IC1132200_KO0,39_KE40,57.htm?jl=1010100043840</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Business Analyst I</t>
+          <t>Asset Management - Hedge Fund Investment Support - Vice President</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -633,17 +633,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$53K - $70K(Glassdoor est.)</t>
+          <t>$170K - $247K(Employer provided)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/business-analyst-i-php-agency-JV_IC1139977_KO0,18_KE19,29.htm?jl=1010115251725</t>
+          <t>https://www.glassdoor.com/job-listing/asset-management-hedge-fund-investment-support-vice-president-jpmorgan-chase-co-JV_IC1132348_KO0,61_KE62,79.htm?jl=1010036207816</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,7 +655,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Operations Analyst, Renewable Energy Procurement</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$75K - $106K(Glassdoor est.)</t>
+          <t>$82K - $127K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/financial-analyst-selby-jennings-JV_IC1154532_KO0,17_KE18,32.htm?jl=1010114539700</t>
+          <t>https://www.glassdoor.com/job-listing/operations-analyst-renewable-energy-procurement-tesla-JV_IC1139761_KO0,47_KE48,53.htm?jl=1010033677027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Job Cost Analyst</t>
+          <t>Senior Investment Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -697,17 +697,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$57K - $82K(Glassdoor est.)</t>
+          <t>$47.50 - $71.25Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/job-cost-analyst-vee-jay-cement-contracting-JV_IC1131270_KO0,16_KE17,43.htm?jl=1010114961842</t>
+          <t>https://www.glassdoor.com/job-listing/senior-investment-analyst-atrium-health-JV_IC1138644_KO0,25_KE26,39.htm?jl=1010101727068</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lead Quantitative Analyst (Charlotte, NC (Hybrid) or Remote)</t>
+          <t>Investment Data Analytics Analyst I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -729,17 +729,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$160K - $210K(Employer provided)</t>
+          <t>$70K - $106K(Employer provided)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/lead-quantitative-analyst-charlotte-nc-hybrid-or-remote-brighthouse-financial-JV_IC1138644_KO0,55_KE56,77.htm?jl=1010114527699</t>
+          <t>https://www.glassdoor.com/job-listing/investment-data-analytics-analyst-i-cleveland-clinic-JV_IC1145766_KO0,35_KE36,52.htm?jl=1010041736959</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Financial Analyst</t>
+          <t>Investment Operations Analyst I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$70K - $87K(Glassdoor est.)</t>
+          <t>$70K - $106K(Employer provided)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sr-financial-analyst-safecor-health-JV_IC1145845_KO0,20_KE21,35.htm?jl=1010093412811</t>
+          <t>https://www.glassdoor.com/job-listing/investment-operations-analyst-i-cleveland-clinic-JV_IC1145766_KO0,31_KE32,48.htm?jl=1010110804434</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cost Engineer / Analyst</t>
+          <t>Principal, Energy Infrastructure Investments</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$65.00 - $80.00Per Hour(Employer provided)</t>
+          <t>$246K - $306K(Employer provided)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/cost-engineer-analyst-innovative-turnaround-controls-JV_IC1152640_KO0,21_KE22,52.htm?jl=1010007520522</t>
+          <t>https://www.glassdoor.com/job-listing/principal-energy-infrastructure-investments-meta-JV_IC1150505_KO0,43_KE44,48.htm?jl=1010112675915</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Financial Analyst</t>
+          <t>Investment Specialist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -825,17 +825,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$63K - $96K(Glassdoor est.)</t>
+          <t>$134K - $269K(Employer provided)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/financial-analyst-hydro-JV_IC1146170_KO0,17_KE18,23.htm?jl=1010108517953</t>
+          <t>https://www.glassdoor.com/job-listing/investment-specialist-rsm-JV_KO0,21_KE22,25.htm?jl=1010071186146</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sales Commission Analyst</t>
+          <t>Senior Product Manager</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -855,15 +855,19 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>$120K - $204K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sales-commission-analyst-adobe-JV_IC1128238_KO0,24_KE25,30.htm?jl=1010107209881</t>
+          <t>https://www.glassdoor.com/job-listing/senior-product-manager-edward-jones-JV_IC1133917_KO0,22_KE23,35.htm?jl=1010061670684</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -875,7 +879,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chemical Analyst</t>
+          <t>Finance Expert - Fixed Income</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -885,17 +889,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$53K - $70K(Glassdoor est.)</t>
+          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chemical-analyst-materion-JV_IC1145796_KO0,16_KE17,25.htm?jl=1010114458569</t>
+          <t>https://www.glassdoor.com/job-listing/finance-expert-fixed-income-x-ai-JV_KO0,27_KE28,32.htm?jl=1010111363064</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -907,7 +911,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analyst / Associate, Infrastructure and Energy Debt Advisory</t>
+          <t>Securities &amp; Commodities Specialist - Freelance AI Trainer Project</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -917,17 +921,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$110K - $200K(Employer provided)</t>
+          <t>$8.00 - $65.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/analyst-associate-infrastructure-and-energy-debt-advisory-macquarie-group-JV_IC1132348_KO0,57_KE58,73.htm?jl=1010114916735</t>
+          <t>https://www.glassdoor.com/job-listing/securities-commodities-specialist-freelance-ai-trainer-project-invisible-technologies-JV_IC1139977_KO0,62_KE63,85.htm?jl=1010082625711</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -939,7 +943,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Accounting Analyst</t>
+          <t>Equity Strategist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -949,17 +953,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$28.00 - $32.00Per Hour(Employer provided)</t>
+          <t>$145K - $173K(Employer provided)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/accounting-analyst-talentburst-JV_IC1138922_KO0,18_KE19,30.htm?jl=1010114789828</t>
+          <t>https://www.glassdoor.com/job-listing/equity-strategist-ubs-JV_KO0,17_KE18,21.htm?jl=1010109601778</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -971,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sales Analyst</t>
+          <t>VP, Alternative Investments Platform Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -981,17 +985,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$57K - $86K(Glassdoor est.)</t>
+          <t>$145K - $241K(Employer provided)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sales-analyst-victaulic-JV_IC1151932_KO0,13_KE14,23.htm?jl=1010083969774</t>
+          <t>https://www.glassdoor.com/job-listing/vp-alternative-investments-platform-management-lpl-financial-JV_IC1155108_KO0,46_KE47,60.htm?jl=1010102268301</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1003,7 +1007,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Acquisitions Analyst</t>
+          <t>Bloomberg Intelligence, Thematic Strategist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1013,17 +1017,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$80K - $100K(Employer provided)</t>
+          <t>$215K - $285K(Employer provided)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-acquisitions-analyst-marquette-management-JV_IC1128808_KO0,27_KE28,48.htm?jl=1010109648829</t>
+          <t>https://www.glassdoor.com/job-listing/bloomberg-intelligence-thematic-strategist-bloomberg-JV_IC1132348_KO0,42_KE43,52.htm?jl=1010072907857</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1035,7 +1039,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Junior Financial Analyst</t>
+          <t>US Biotech/Pharma - Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1045,17 +1049,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$70K - $75K(Employer provided)</t>
+          <t>$135K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/junior-financial-analyst-gl-staffing-services-JV_IC1154160_KO0,24_KE25,45.htm?jl=1010115041405</t>
+          <t>https://www.glassdoor.com/job-listing/us-biotech-pharma-associate-deutsche-bank-JV_IC3735316_KO0,27_KE28,41.htm?jl=1009998379468</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1067,7 +1071,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QA Lab Analyst- Analytical</t>
+          <t>MVRM Valuation Risk Management – Rates - Vice President</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1077,17 +1081,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$20.00Per Hour(Employer provided)</t>
+          <t>$125K - $198K(Employer provided)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/qa-lab-analyst-analytical-mayer-brothers-JV_IC1158943_KO0,25_KE26,40.htm?jl=1010108261024</t>
+          <t>https://www.glassdoor.com/job-listing/mvrm-valuation-risk-management-rates-vice-president-deutsche-bank-JV_IC3735316_KO0,51_KE52,65.htm?jl=1010084578104</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1099,7 +1103,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Quality Improvement Analyst</t>
+          <t>US Aerospace &amp; Defense - Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1109,17 +1113,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$58K - $93K(Glassdoor est.)</t>
+          <t>$110K - $125K(Employer provided)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/quality-improvement-analyst-true-rx-management-services-JV_IC1145353_KO0,27_KE28,55.htm?jl=1010095460719</t>
+          <t>https://www.glassdoor.com/job-listing/us-aerospace-defense-analyst-deutsche-bank-JV_IC3735316_KO0,28_KE29,42.htm?jl=1010016667567</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1131,7 +1135,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sales Operations Analyst</t>
+          <t>Research Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1141,17 +1145,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$65K - $85K(Employer provided)</t>
+          <t>$135K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sales-operations-analyst-visa-lighting-an-oldenburg-group-company-JV_IC1133579_KO0,24_KE25,65.htm?jl=1010074838658</t>
+          <t>https://www.glassdoor.com/job-listing/research-associate-deutsche-bank-JV_IC3735316_KO0,18_KE19,32.htm?jl=1010094143042</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1163,7 +1167,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Investment Analyst</t>
+          <t>Associate, Portfolio Manager / Derivatives Trader – Derivatives SMA (Option Overlays)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1173,17 +1177,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$110K - $150K(Employer provided)</t>
+          <t>$105K - $140K(Employer provided)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-analyst-terreno-realty-corporation-JV_IC1150442_KO0,18_KE19,45.htm?jl=1010064278960</t>
+          <t>https://www.glassdoor.com/job-listing/associate-portfolio-manager-derivatives-trader-derivatives-sma-option-overlays-blackrock-JV_IC1128808_KO0,78_KE79,88.htm?jl=1010053662882</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1195,7 +1199,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Benefits Analyst</t>
+          <t>Associate, US iShares Product Consulting</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1205,17 +1209,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$58K - $74K(Employer provided)</t>
+          <t>$110K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/benefits-analyst-brookdale-senior-living-JV_IC1144496_KO0,16_KE17,40.htm?jl=1010115089470</t>
+          <t>https://www.glassdoor.com/job-listing/associate-us-ishares-product-consulting-blackrock-JV_KO0,39_KE40,49.htm?jl=1010109682353</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1227,7 +1231,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sales and Marketing Analyst</t>
+          <t>Associate - Hedge Fund Investor Relations</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1237,17 +1241,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$60K - $70K(Employer provided)</t>
+          <t>$105K - $138K(Employer provided)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sales-and-marketing-analyst-gsc-enterprises-JV_IC1140540_KO0,27_KE28,43.htm?jl=1010109888516</t>
+          <t>https://www.glassdoor.com/job-listing/associate-hedge-fund-investor-relations-blackrock-JV_KO0,39_KE40,49.htm?jl=1010111513024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1259,7 +1263,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Client Support Center Analyst</t>
+          <t>Associate, Investment Solutions/Portfolio Consulting</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1269,17 +1273,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$33K - $55K(Employer provided)</t>
+          <t>$116K - $155K(Employer provided)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/client-support-center-analyst-athenahealth-JV_IC1135503_KO0,29_KE30,42.htm?jl=1010100458393</t>
+          <t>https://www.glassdoor.com/job-listing/associate-investment-solutions-portfolio-consulting-blackrock-JV_KO0,51_KE52,61.htm?jl=1010109682583</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1291,7 +1295,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sales Tax Analyst</t>
+          <t>DIRECTOR OF INVESTMENTS, Investment Office</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1301,17 +1305,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$51K - $68K(Glassdoor est.)</t>
+          <t>$350K - $750K(Employer provided)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sales-tax-analyst-pleasant-valley-corporation-JV_IC1145799_KO0,17_KE18,45.htm?jl=1010073039141</t>
+          <t>https://www.glassdoor.com/job-listing/director-of-investments-investment-office-boston-university-school-of-law-JV_IC1154532_KO0,41_KE42,73.htm?jl=1010102711412</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1323,7 +1327,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Intelligence Analyst</t>
+          <t>Aladdin Client Transformations, Vice President (Delivery Lead)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1333,17 +1337,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$59K - $107K(Employer provided)</t>
+          <t>$148K - $195K(Employer provided)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/intelligence-analyst-leidos-JV_IC1147652_KO0,20_KE21,27.htm?jl=1010114963762</t>
+          <t>https://www.glassdoor.com/job-listing/aladdin-client-transformations-vice-president-delivery-lead-blackrock-JV_IC1132348_KO0,59_KE60,69.htm?jl=1010052138380</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1355,7 +1359,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Service &amp; Sales Operations Analyst</t>
+          <t>Associate, Private Equity Secondaries, Portfolio Management</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1365,17 +1369,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$57K - $81K(Glassdoor est.)</t>
+          <t>$130K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/service-sales-operations-analyst-pitco-nh-JV_IC1147785_KO0,32_KE33,41.htm?jl=1010063149721</t>
+          <t>https://www.glassdoor.com/job-listing/associate-private-equity-secondaries-portfolio-management-ares-management-JV_KO0,57_KE58,73.htm?jl=1010082981654</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1387,7 +1391,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ServiceNow Analyst</t>
+          <t>Equity Trading Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1395,19 +1399,15 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>$46.50 - $62.00Per Hour(Employer provided)</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/servicenow-analyst-compucom-JV_IC1155583_KO0,18_KE19,27.htm?jl=1010114685532</t>
+          <t>https://www.glassdoor.com/job-listing/equity-trading-analyst-sei-investments-JV_IC1152660_KO0,22_KE23,38.htm?jl=1010077779964</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Executive Director</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$81K - $136K(Glassdoor est.)</t>
+          <t>$70K - $80K(Employer provided)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/director-northwestern-mutual-JV_IC1133579_KO0,8_KE9,28.htm?jl=1010112720343</t>
+          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1451,7 +1451,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Investment Banking Consultant</t>
+          <t>Executive Assistant to the CEO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$68K - $206K(Employer provided)</t>
+          <t>$55K(Employer provided)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-banking-consultant-accenture-JV_IC1154170_KO0,29_KE30,39.htm?jl=1010000045025</t>
+          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Credit Portfolio Group - Research - Vice President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1493,17 +1493,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>$200K - $275K(Employer provided)</t>
+          <t>$170K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/credit-portfolio-group-research-vice-president-jpmorgan-chase-co-JV_IC1132348_KO0,46_KE47,64.htm?jl=1010021310234</t>
+          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Credit Portfolio Group - Research - Associate</t>
+          <t>President ANC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$135K - $200K(Employer provided)</t>
+          <t>$318K - $406K(Employer provided)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/credit-portfolio-group-research-associate-jpmorgan-chase-co-JV_IC1132348_KO0,41_KE42,59.htm?jl=1010073216090</t>
+          <t>https://www.glassdoor.com/job-listing/president-anc-alutiiq-JV_IC1134201_KO0,13_KE14,21.htm?jl=1010071156640</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1547,7 +1547,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Equity Research - REITs - Associate</t>
+          <t>President &amp; CEO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>$150K - $200K(Employer provided)</t>
+          <t>$320K - $350K(Employer provided)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-research-reits-associate-jpmorgan-chase-co-JV_IC1132348_KO0,31_KE32,49.htm?jl=1010070497398</t>
+          <t>https://www.glassdoor.com/job-listing/president-ceo-the-moran-company-JV_IC1154062_KO0,13_KE14,31.htm?jl=1010108349638</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Equity Research - Specialty &amp; Consumer Finance - Associate</t>
+          <t>Chief of Staff to CEO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1589,17 +1589,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>$150K - $200K(Employer provided)</t>
+          <t>$220K - $275K(Employer provided)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-research-specialty-consumer-finance-associate-jpmorgan-chase-co-JV_KO0,52_KE53,70.htm?jl=1010098630208</t>
+          <t>https://www.glassdoor.com/job-listing/chief-of-staff-to-ceo-iterative-health-JV_IC1154545_KO0,21_KE22,38.htm?jl=1009970363828</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Equity Research - Utilities - Associate</t>
+          <t>Pueblo of Pojoaque Corporate Businesses CEO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1621,17 +1621,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>$150K - $200K(Employer provided)</t>
+          <t>$225K(Employer provided)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-research-utilities-associate-jpmorgan-chase-co-JV_KO0,35_KE36,53.htm?jl=1010106989954</t>
+          <t>https://www.glassdoor.com/job-listing/pueblo-of-pojoaque-corporate-businesses-ceo-pueblo-of-pojoaque-corporations-JV_IC1138171_KO0,43_KE44,75.htm?jl=1010074993847</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Investment Banking - Investment Grade Finance - Associate</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>$175K - $225K(Employer provided)</t>
+          <t>$300K - $450K(Employer provided)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-banking-investment-grade-finance-associate-jpmorgan-chase-co-JV_IC1132348_KO0,53_KE54,71.htm?jl=1010073215917</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-northwestern-medical-center-JV_IC1141798_KO0,23_KE24,51.htm?jl=1010086464392</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AIS Analyst</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1683,19 +1683,15 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>$85K - $100K(Employer provided)</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ais-analyst-abrdn-JV_KO0,11_KE12,17.htm?jl=1010056425121</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-anson-regional-medical-service-JV_IC1138675_KO0,23_KE24,54.htm?jl=1010104525348</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1707,7 +1703,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Operations Analyst, Renewable Energy Procurement</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1717,17 +1713,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>$82K - $127K(Glassdoor est.)</t>
+          <t>$275K - $280K(Employer provided)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/operations-analyst-renewable-energy-procurement-tesla-JV_IC1139761_KO0,47_KE48,53.htm?jl=1010033677027</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1136950_KO0,23_KE24,41.htm?jl=1010097248172</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1739,7 +1735,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Investment Analyst</t>
+          <t>President &amp; Chief Commercial Officer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1749,17 +1745,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>$47.50 - $71.25Per Hour(Employer provided)</t>
+          <t>$150K - $185K(Employer provided)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-investment-analyst-atrium-health-JV_IC1128935_KO0,25_KE26,39.htm?jl=1010101093398</t>
+          <t>https://www.glassdoor.com/job-listing/president-chief-commercial-officer-check-my-policy-JV_IC1140171_KO0,34_KE35,50.htm?jl=1010094178300</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1771,7 +1767,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Principal, Energy Infrastructure Investments</t>
+          <t>CEO in Training (CIT), Executive Director</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1781,17 +1777,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>$246K - $306K(Employer provided)</t>
+          <t>$42K - $76K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/principal-energy-infrastructure-investments-meta-JV_IC1132348_KO0,43_KE44,48.htm?jl=1010112675924</t>
+          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133685_KO0,38_KE39,52.htm?jl=1010088747434</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1803,7 +1799,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Strategic Investor Communications Lead</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1813,17 +1809,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>$189K - $284K(Employer provided)</t>
+          <t>$175K - $225K(Employer provided)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/strategic-investor-communications-lead-ge-healthcare-JV_IC1128808_KO0,38_KE39,52.htm?jl=1010045621776</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1835,7 +1831,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Collections Specialist</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1845,17 +1841,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$65K - $126K(Employer provided)</t>
+          <t>$200K(Employer provided)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/collections-specialist-gallagher-JV_IC1128962_KO0,22_KE23,32.htm?jl=1009960182119</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-marathon-JV_IC1154115_KO0,12_KE13,29.htm?jl=1010103355662</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1867,7 +1863,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Investment Specialist</t>
+          <t>President and CEO - Oklahoma Manufacturing Alliance</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1875,19 +1871,15 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>$134K - $269K(Employer provided)</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-specialist-rsm-JV_KO0,21_KE22,25.htm?jl=1010071186146</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-ceo-oklahoma-manufacturing-alliance-schnake-turnbo-frank-JV_IC1137055_KO0,49_KE50,70.htm?jl=1010109776782</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1899,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Alternatives Data Analyst</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1909,17 +1901,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>$68.00Per Hour(Employer provided)</t>
+          <t>$150K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-alternatives-data-analyst-mercer-JV_IC1154532_KO0,32_KE33,39.htm?jl=1010063137206</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1126720_KO0,23_KE24,41.htm?jl=1010091874998</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1931,7 +1923,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Product Manager</t>
+          <t>President and Chief Executive Officer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1941,17 +1933,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>$120K - $204K(Employer provided)</t>
+          <t>$275K - $325K(Employer provided)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-product-manager-edward-jones-JV_IC1133917_KO0,22_KE23,35.htm?jl=1010061670684</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-chief-executive-officer-confidential-JV_KO0,37_KE38,50.htm?jl=1010043379708</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1963,7 +1955,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Finance Expert - Fixed Income</t>
+          <t>Executive Director</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1973,17 +1965,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$140K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-fixed-income-x-ai-JV_KO0,27_KE28,32.htm?jl=1010111363064</t>
+          <t>https://www.glassdoor.com/job-listing/executive-director-the-moran-company-JV_IC1136440_KO0,18_KE19,36.htm?jl=1010108424026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1995,7 +1987,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FX Treasury Manager</t>
+          <t>CEO in Training (CIT), Executive Director</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2005,17 +1997,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$119K - $191K(Glassdoor est.)</t>
+          <t>$46K - $84K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/fx-treasury-manager-salesforce-JV_IC1155583_KO0,19_KE20,30.htm?jl=1010091996431</t>
+          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133406_KO0,38_KE39,52.htm?jl=1010112336554</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2027,7 +2019,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Securities &amp; Commodities Specialist - Freelance AI Trainer Project</t>
+          <t>CEO - Interior Design Company</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2037,17 +2029,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$8.00 - $65.00Per Hour(Employer provided)</t>
+          <t>$250K - $350K(Employer provided)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/securities-commodities-specialist-freelance-ai-trainer-project-invisible-technologies-JV_IC1139977_KO0,62_KE63,85.htm?jl=1010082625711</t>
+          <t>https://www.glassdoor.com/job-listing/ceo-interior-design-company-redford-hearth-executive-search-healthcare-JV_IC1132348_KO0,27_KE28,70.htm?jl=1010077281914</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2059,7 +2051,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>VP, AI Risk Manager</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2069,17 +2061,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$159K - $271K(Employer provided)</t>
+          <t>$150K - $220K(Employer provided)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/vp-ai-risk-manager-chubb-JV_IC1127046_KO0,18_KE19,24.htm?jl=1010005026857</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-lng-holding-JV_IC1128793_KO0,23_KE24,35.htm?jl=1010006337770</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,7 +2083,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Program Manager</t>
+          <t>Louisiana Healthcare Connections Plan President &amp; CEO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2101,17 +2093,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>$40.00 - $60.00Per Hour(Employer provided)</t>
+          <t>$270K - $580K(Employer provided)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sr-program-manager-cedent-JV_KO0,18_KE19,25.htm?jl=1009382584851</t>
+          <t>https://www.glassdoor.com/job-listing/louisiana-healthcare-connections-plan-president-ceo-centene-JV_IC1150013_KO0,51_KE52,59.htm?jl=1010112808854</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2123,7 +2115,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Equity Strategist</t>
+          <t>Director, CEO Communications</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2133,17 +2125,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>$145K - $173K(Employer provided)</t>
+          <t>$90K - $150K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-strategist-ubs-JV_KO0,17_KE18,21.htm?jl=1010109601778</t>
+          <t>https://www.glassdoor.com/job-listing/director-ceo-communications-ochsner-health-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010105292126</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2155,7 +2147,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AVP, Advisory Consultant</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2165,17 +2157,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>$104K - $173K(Employer provided)</t>
+          <t>$180K - $210K(Employer provided)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/avp-advisory-consultant-lpl-financial-JV_IC1155108_KO0,23_KE24,37.htm?jl=1010094647514</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-arvin-ca-JV_IC1146556_KO0,12_KE13,29.htm?jl=1010112565997</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2187,7 +2179,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VP, Alternative Investments Platform Management</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2197,17 +2189,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>$145K - $241K(Employer provided)</t>
+          <t>$220K - $245K(Employer provided)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/vp-alternative-investments-platform-management-lpl-financial-JV_IC1155108_KO0,46_KE47,60.htm?jl=1010102268301</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-tigard-oregon-JV_IC1165048_KO0,12_KE13,34.htm?jl=1010101155714</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2219,7 +2211,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Regulatory Reporting QA Vice President</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2229,17 +2221,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>$140K - $185K(Employer provided)</t>
+          <t>$275K(Employer provided)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/regulatory-reporting-qa-vice-president-sumitomo-pharma-JV_IC1126819_KO0,38_KE39,54.htm?jl=1010084228891</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-sausalito-art-festival-JV_IC1147411_KO0,12_KE13,35.htm?jl=1010015848250</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2251,7 +2243,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Net Asset Value (NAV), Analyst</t>
+          <t>City Manager - Annapolis, MD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2261,17 +2253,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>$110K - $125K(Employer provided)</t>
+          <t>$250K - $294K(Employer provided)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/net-asset-value-nav-analyst-sumitomo-pharma-JV_KO0,27_KE28,43.htm?jl=1010106784232</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-annapolis-md-annapolis-market-house-md-JV_IC1153523_KO0,25_KE26,51.htm?jl=1010023329394</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2283,7 +2275,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Distribution Risk Specialist</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2293,17 +2285,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>$143K - $185K(Employer provided)</t>
+          <t>$274K(Employer provided)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/distribution-risk-specialist-sumitomo-pharma-JV_KO0,28_KE29,44.htm?jl=1010091955697</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-county-of-sonoma-JV_IC1147520_KO0,12_KE13,29.htm?jl=1010107011390</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2315,7 +2307,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Product Analyst Custom Indices- Enterprise Data</t>
+          <t>President and General Manager, WPVI-TV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2325,17 +2317,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>$110K - $225K(Employer provided)</t>
+          <t>$412K - $553K(Employer provided)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/product-analyst-custom-indices-enterprise-data-bloomberg-JV_IC1132348_KO0,46_KE47,56.htm?jl=1010065219020</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-general-manager-wpvi-tv-walt-disney-company-JV_IC1152672_KO0,37_KE38,57.htm?jl=1009865634435</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2347,7 +2339,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bloomberg Intelligence, Thematic Strategist</t>
+          <t>Executive Business Partner, Office of the CEO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2357,20 +2349,968 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>$215K - $285K(Employer provided)</t>
+          <t>$76.96 - $92.53Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/bloomberg-intelligence-thematic-strategist-bloomberg-JV_IC1132348_KO0,42_KE43,52.htm?jl=1010072907857</t>
+          <t>https://www.glassdoor.com/job-listing/executive-business-partner-office-of-the-ceo-roblox-JV_IC1147406_KO0,44_KE45,51.htm?jl=1010090207481</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Financial Analyst III - FP Financial Services</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>$33.37 - $47.97Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-iii-fp-financial-services-unc-health-JV_IC1138696_KO0,43_KE44,54.htm?jl=1010111806078</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Region President</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>$210K - $350K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/region-president-sysco-JV_IC1146959_KO0,16_KE17,22.htm?jl=1010056940373</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Transportation Clerk - SYGMA - FP - US</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>$16.83 - $25.19Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/transportation-clerk-sygma-fp-us-sygma-network-JV_IC1147539_KO0,32_KE33,46.htm?jl=1010076661775</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Construction Quality Director</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>$130K - $241K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/construction-quality-director-aecom-JV_IC1145778_KO0,29_KE30,35.htm?jl=1010002852559</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FP and A Analyst Sr</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>$77K - $118K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/fp-and-a-analyst-sr-engie-JV_IC1140171_KO0,19_KE20,25.htm?jl=1010051644171</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Specialist I, Pricing</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>$42K - $59K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/specialist-i-pricing-qxo-JV_IC1140029_KO0,20_KE21,24.htm?jl=1010076339628</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Scientist, Study Manager</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>$117K - $184K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-scientist-study-manager-merck-JV_IC1147311_KO0,30_KE31,36.htm?jl=1010069167075</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior Clinical Scientist</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>$115K - $181K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-clinical-scientist-merck-JV_IC1147311_KO0,25_KE26,31.htm?jl=1009970109525</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dishwasher FP</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/dishwasher-fp-arcis-golf-JV_KO0,13_KE14,24.htm?jl=1010053677954</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Social Media Manager</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>$100K - $120K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/social-media-manager-paramount-JV_KO0,20_KE21,30.htm?jl=1010111288466</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Royalty Analyst (Peanuts Worldwide)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>$60K - $70K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/royalty-analyst-peanuts-worldwide-sony-electronics-JV_KO0,33_KE34,50.htm?jl=1010086845696</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aseptic Production Training Instructor</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>$46K - $78K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/aseptic-production-training-instructor-novo-nordisk-JV_IC1138946_KO0,38_KE39,51.htm?jl=1010106837668</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Technical Acquisition and Contracts Specialist</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>$151K - $227K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/technical-acquisition-and-contracts-specialist-the-aerospace-corporation-JV_IC1130353_KO0,46_KE47,72.htm?jl=1010079037925</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Maintenance Tech</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>$40K - $56K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/maintenance-tech-planet-fitness-JV_IC1151076_KO0,16_KE17,31.htm?jl=1010087433721</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Planet Fitness Team Member</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>$33K - $47K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-team-member-planet-fitness-JV_IC1146121_KO0,26_KE27,41.htm?jl=1009789931023</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Member Services Representative- St. Joseph, MO, Planet Fitness</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>$36K - $47K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/member-services-representative-st-joseph-mo-planet-fitness-planet-fitness-JV_IC1131187_KO0,58_KE59,73.htm?jl=1009990771575</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Planet Fitness</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140422_KO0,14_KE15,29.htm?jl=1010063289184</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>planet fitness Member Services Representative</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>$38K - $53K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-member-services-representative-planet-fitness-JV_IC1151049_KO0,45_KE46,60.htm?jl=1010106825729</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Planet Fitness</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140320_KO0,14_KE15,29.htm?jl=1010053177095</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CLUB - Overnight Member Services Rep</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>$27K - $33K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/club-overnight-member-services-rep-planet-fitness-JV_IC1140000_KO0,34_KE35,49.htm?jl=1010031133814</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Member Services Representative- Morning Opener</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>$32K - $42K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/member-services-representative-morning-opener-planet-fitness-JV_IC1130886_KO0,45_KE46,60.htm?jl=1010101171715</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Club Manager</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>$40K - $53K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/club-manager-planet-fitness-JV_IC1141333_KO0,12_KE13,27.htm?jl=1010105150250</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Part-Time Member Services Representative</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>$26K - $35K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/part-time-member-services-representative-planet-fitness-JV_IC1143111_KO0,40_KE41,55.htm?jl=1010083348473</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Member Services Representative</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>$27K - $35K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/member-services-representative-planet-fitness-JV_IC1149904_KO0,30_KE31,45.htm?jl=1010093033515</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Overnight Member Services</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>$33K - $44K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/overnight-member-services-planet-fitness-JV_IC1133904_KO0,25_KE26,40.htm?jl=1010074948979</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CLUB - Assistant Club Manager</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>$34K - $47K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/club-assistant-club-manager-planet-fitness-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010052052649</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Overnight Member Service Rep</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>$12.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/overnight-member-service-rep-planet-fitness-JV_IC1139716_KO0,28_KE29,43.htm?jl=1010083348519</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Specialist, Sexual and Reproductive Health and Rights</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>$59K - $107K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/specialist-sexual-and-reproductive-health-and-rights-international-rescue-committee-JV_KO0,52_KE53,83.htm?jl=1010111119629</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Research Analyst III-(IAC)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>$71K - $111K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/research-analyst-iii-iac-people-technology-processes-JV_IC1154429_KO0,24_KE25,52.htm?jl=1009627655799</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Research Scientist-(IAC)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>$111K - $173K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/research-scientist-iac-people-technology-processes-JV_IC1154429_KO0,22_KE23,50.htm?jl=1009627655806</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/Glassdoor_Jobs_2026-04-28.xlsx
+++ b/Glassdoor_Jobs_2026-04-28.xlsx
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Portfolio Manager</t>
+          <t>Executive Director</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Addiction Recovery Coalition of New Hampshire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$250K(Employer provided)</t>
+          <t>$70K - $80K(Employer provided)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/portfolio-manager-creative-financial-staffing-JV_IC1154247_KO0,17_KE18,45.htm?jl=1010107182315</t>
+          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Equity Research - REITs - Associate</t>
+          <t>Executive Assistant to the CEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Automotive Reinsurance Concepts</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$150K - $200K(Employer provided)</t>
+          <t>$55K(Employer provided)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-research-reits-associate-jpmorgan-chase-co-JV_IC1132348_KO0,31_KE32,49.htm?jl=1010070497398</t>
+          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Equity Research - Specialty &amp; Consumer Finance - Associate</t>
+          <t>President ANC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Alutiiq3.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$150K - $200K(Employer provided)</t>
+          <t>$318K - $406K(Employer provided)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-research-specialty-consumer-finance-associate-jpmorgan-chase-co-JV_KO0,52_KE53,70.htm?jl=1010098630208</t>
+          <t>https://www.glassdoor.com/job-listing/president-anc-alutiiq-JV_IC1134201_KO0,13_KE14,21.htm?jl=1010071156640</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Equity Research - Utilities - Associate</t>
+          <t>President &amp; CEO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$150K - $200K(Employer provided)</t>
+          <t>$320K - $350K(Employer provided)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-research-utilities-associate-jpmorgan-chase-co-JV_KO0,35_KE36,53.htm?jl=1010106989954</t>
+          <t>https://www.glassdoor.com/job-listing/president-ceo-the-moran-company-JV_IC1154062_KO0,13_KE14,31.htm?jl=1010108349638</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Portfolio &amp; Performance Analyst - Associate</t>
+          <t>President</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$76K - $105K(Employer provided)</t>
+          <t>$170K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/portfolio-performance-analyst-associate-jpmorgan-chase-co-JV_IC1132200_KO0,39_KE40,57.htm?jl=1010100043840</t>
+          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Asset Management - Hedge Fund Investment Support - Vice President</t>
+          <t>Chief of Staff to CEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Iterative Health4.2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$170K - $247K(Employer provided)</t>
+          <t>$220K - $275K(Employer provided)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/asset-management-hedge-fund-investment-support-vice-president-jpmorgan-chase-co-JV_IC1132348_KO0,61_KE62,79.htm?jl=1010036207816</t>
+          <t>https://www.glassdoor.com/job-listing/chief-of-staff-to-ceo-iterative-health-JV_IC1154545_KO0,21_KE22,38.htm?jl=1009970363828</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Operations Analyst, Renewable Energy Procurement</t>
+          <t>Pueblo of Pojoaque Corporate Businesses CEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pueblo of Pojoaque Corporations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$82K - $127K(Glassdoor est.)</t>
+          <t>$225K(Employer provided)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/operations-analyst-renewable-energy-procurement-tesla-JV_IC1139761_KO0,47_KE48,53.htm?jl=1010033677027</t>
+          <t>https://www.glassdoor.com/job-listing/pueblo-of-pojoaque-corporate-businesses-ceo-pueblo-of-pojoaque-corporations-JV_IC1138171_KO0,43_KE44,75.htm?jl=1010074993847</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Investment Analyst</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$47.50 - $71.25Per Hour(Employer provided)</t>
+          <t>$275K - $280K(Employer provided)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-investment-analyst-atrium-health-JV_IC1138644_KO0,25_KE26,39.htm?jl=1010101727068</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1136950_KO0,23_KE24,41.htm?jl=1010097248172</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,27 +719,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Investment Data Analytics Analyst I</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>$70K - $106K(Employer provided)</t>
-        </is>
-      </c>
+          <t>Anson Regional Medical Service</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-data-analytics-analyst-i-cleveland-clinic-JV_IC1145766_KO0,35_KE36,52.htm?jl=1010041736959</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-anson-regional-medical-service-JV_IC1138675_KO0,23_KE24,54.htm?jl=1010104525348</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -751,27 +747,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Investment Operations Analyst I</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Northwestern Medical Center3.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$70K - $106K(Employer provided)</t>
+          <t>$300K - $450K(Employer provided)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-operations-analyst-i-cleveland-clinic-JV_IC1145766_KO0,31_KE32,48.htm?jl=1010110804434</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-northwestern-medical-center-JV_IC1141798_KO0,23_KE24,51.htm?jl=1010086464392</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -783,27 +779,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Principal, Energy Infrastructure Investments</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pennsylvania Coalition of Public Charter Schools</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$246K - $306K(Employer provided)</t>
+          <t>$175K - $225K(Employer provided)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/principal-energy-infrastructure-investments-meta-JV_IC1150505_KO0,43_KE44,48.htm?jl=1010112675915</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -815,27 +811,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Investment Specialist</t>
+          <t>President and CEO - Oklahoma Manufacturing Alliance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>$134K - $269K(Employer provided)</t>
-        </is>
-      </c>
+          <t>Schnake Turnbo Frank4.1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/investment-specialist-rsm-JV_KO0,21_KE22,25.htm?jl=1010071186146</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-ceo-oklahoma-manufacturing-alliance-schnake-turnbo-frank-JV_IC1137055_KO0,49_KE50,70.htm?jl=1010109776782</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,27 +839,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Product Manager</t>
+          <t>CEO in Training (CIT), Executive Director</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pennant Group3.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$120K - $204K(Employer provided)</t>
+          <t>$42K - $76K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-product-manager-edward-jones-JV_IC1133917_KO0,22_KE23,35.htm?jl=1010061670684</t>
+          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133685_KO0,38_KE39,52.htm?jl=1010088747434</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,27 +871,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Finance Expert - Fixed Income</t>
+          <t>Executive Director</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$45.00 - $100.00Per Hour(Employer provided)</t>
+          <t>$140K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/finance-expert-fixed-income-x-ai-JV_KO0,27_KE28,32.htm?jl=1010111363064</t>
+          <t>https://www.glassdoor.com/job-listing/executive-director-the-moran-company-JV_IC1136440_KO0,18_KE19,36.htm?jl=1010108424026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,27 +903,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Securities &amp; Commodities Specialist - Freelance AI Trainer Project</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Scion Staffing3.7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$8.00 - $65.00Per Hour(Employer provided)</t>
+          <t>$175K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/securities-commodities-specialist-freelance-ai-trainer-project-invisible-technologies-JV_IC1139977_KO0,62_KE63,85.htm?jl=1010082625711</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-scion-staffing-JV_IC1150480_KO0,23_KE24,38.htm?jl=1010092080553</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -943,27 +935,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Equity Strategist</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$145K - $173K(Employer provided)</t>
+          <t>$150K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-strategist-ubs-JV_KO0,17_KE18,21.htm?jl=1010109601778</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1126720_KO0,23_KE24,41.htm?jl=1010091874998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -975,27 +967,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VP, Alternative Investments Platform Management</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>LNG Holding</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$145K - $241K(Employer provided)</t>
+          <t>$150K - $220K(Employer provided)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/vp-alternative-investments-platform-management-lpl-financial-JV_IC1155108_KO0,46_KE47,60.htm?jl=1010102268301</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-lng-holding-JV_IC1128793_KO0,23_KE24,35.htm?jl=1010006337770</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,27 +999,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bloomberg Intelligence, Thematic Strategist</t>
+          <t>President and Chief Executive Officer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Confidential</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$215K - $285K(Employer provided)</t>
+          <t>$275K - $325K(Employer provided)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/bloomberg-intelligence-thematic-strategist-bloomberg-JV_IC1132348_KO0,42_KE43,52.htm?jl=1010072907857</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-chief-executive-officer-confidential-JV_KO0,37_KE38,50.htm?jl=1010043379708</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,27 +1031,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>US Biotech/Pharma - Associate</t>
+          <t>President &amp; Chief Commercial Officer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Check My Policy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$135K - $175K(Employer provided)</t>
+          <t>$150K - $185K(Employer provided)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/us-biotech-pharma-associate-deutsche-bank-JV_IC3735316_KO0,27_KE28,41.htm?jl=1009998379468</t>
+          <t>https://www.glassdoor.com/job-listing/president-chief-commercial-officer-check-my-policy-JV_IC1140171_KO0,34_KE35,50.htm?jl=1010094178300</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,27 +1063,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MVRM Valuation Risk Management – Rates - Vice President</t>
+          <t>CEO in Training (CIT), Executive Director</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pennant Group3.3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$125K - $198K(Employer provided)</t>
+          <t>$46K - $84K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/mvrm-valuation-risk-management-rates-vice-president-deutsche-bank-JV_IC3735316_KO0,51_KE52,65.htm?jl=1010084578104</t>
+          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133406_KO0,38_KE39,52.htm?jl=1010112336554</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,27 +1095,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>US Aerospace &amp; Defense - Analyst</t>
+          <t>Regional Executive Director - Chicagoland | World Relief</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Vanderbloemen Search Group3.1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$110K - $125K(Employer provided)</t>
+          <t>$120K - $130K(Employer provided)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/us-aerospace-defense-analyst-deutsche-bank-JV_IC3735316_KO0,28_KE29,42.htm?jl=1010016667567</t>
+          <t>https://www.glassdoor.com/job-listing/regional-executive-director-chicagoland-world-relief-vanderbloemen-search-group-JV_IC1128808_KO0,52_KE53,79.htm?jl=1010104739908</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,27 +1127,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Research Associate</t>
+          <t>Chief Executive Officer / Hospital Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ClearSky Health3.1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$135K - $175K(Employer provided)</t>
+          <t>$63K - $117K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/research-associate-deutsche-bank-JV_IC3735316_KO0,18_KE19,32.htm?jl=1010094143042</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-hospital-administrator-clearsky-health-JV_IC1154120_KO0,46_KE47,62.htm?jl=1010115284210</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,27 +1159,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate, Portfolio Manager / Derivatives Trader – Derivatives SMA (Option Overlays)</t>
+          <t>Louisiana Healthcare Connections Plan President &amp; CEO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Centene3.7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$105K - $140K(Employer provided)</t>
+          <t>$270K - $580K(Employer provided)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-portfolio-manager-derivatives-trader-derivatives-sma-option-overlays-blackrock-JV_IC1128808_KO0,78_KE79,88.htm?jl=1010053662882</t>
+          <t>https://www.glassdoor.com/job-listing/louisiana-healthcare-connections-plan-president-ceo-centene-JV_IC1150013_KO0,51_KE52,59.htm?jl=1010112808854</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,27 +1191,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate, US iShares Product Consulting</t>
+          <t>Director, CEO Communications</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Ochsner Health3.7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$110K - $150K(Employer provided)</t>
+          <t>$90K - $150K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-us-ishares-product-consulting-blackrock-JV_KO0,39_KE40,49.htm?jl=1010109682353</t>
+          <t>https://www.glassdoor.com/job-listing/director-ceo-communications-ochsner-health-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010105292126</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,27 +1223,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate - Hedge Fund Investor Relations</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>City of Arvin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$105K - $138K(Employer provided)</t>
+          <t>$180K - $210K(Employer provided)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-hedge-fund-investor-relations-blackrock-JV_KO0,39_KE40,49.htm?jl=1010111513024</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-arvin-ca-JV_IC1146556_KO0,12_KE13,29.htm?jl=1010112565997</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,27 +1255,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate, Investment Solutions/Portfolio Consulting</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>City of Tigard, Oregon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$116K - $155K(Employer provided)</t>
+          <t>$220K - $245K(Employer provided)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-investment-solutions-portfolio-consulting-blackrock-JV_KO0,51_KE52,61.htm?jl=1010109682583</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-tigard-oregon-JV_IC1165048_KO0,12_KE13,34.htm?jl=1010101155714</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,27 +1287,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DIRECTOR OF INVESTMENTS, Investment Office</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sausalito Art Festival3.8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$350K - $750K(Employer provided)</t>
+          <t>$275K(Employer provided)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/director-of-investments-investment-office-boston-university-school-of-law-JV_IC1154532_KO0,41_KE42,73.htm?jl=1010102711412</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-sausalito-art-festival-JV_IC1147411_KO0,12_KE13,35.htm?jl=1010015848250</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,27 +1319,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aladdin Client Transformations, Vice President (Delivery Lead)</t>
+          <t>City Manager - Annapolis, MD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Annapolis Market House (MD)3.8</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$148K - $195K(Employer provided)</t>
+          <t>$250K - $294K(Employer provided)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/aladdin-client-transformations-vice-president-delivery-lead-blackrock-JV_IC1132348_KO0,59_KE60,69.htm?jl=1010052138380</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-annapolis-md-annapolis-market-house-md-JV_IC1153523_KO0,25_KE26,51.htm?jl=1010023329394</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,27 +1351,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate, Private Equity Secondaries, Portfolio Management</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>County of Sonoma3.8</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$130K - $175K(Employer provided)</t>
+          <t>$274K(Employer provided)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-private-equity-secondaries-portfolio-management-ares-management-JV_KO0,57_KE58,73.htm?jl=1010082981654</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-county-of-sonoma-JV_IC1147520_KO0,12_KE13,29.htm?jl=1010107011390</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,23 +1383,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Equity Trading Analyst</t>
+          <t>President and General Manager, WPVI-TV</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>Walt Disney Company3.8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>$412K - $553K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/equity-trading-analyst-sei-investments-JV_IC1152660_KO0,22_KE23,38.htm?jl=1010077779964</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-general-manager-wpvi-tv-walt-disney-company-JV_IC1152672_KO0,37_KE38,57.htm?jl=1009865634435</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CFA</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1419,27 +1415,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Executive Director</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Brooksource3.8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$70K - $80K(Employer provided)</t>
+          <t>$163K - $173K(Employer provided)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
+          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-brooksource-JV_IC1152672_KO0,21_KE22,33.htm?jl=1010114706169</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1451,27 +1447,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Executive Assistant to the CEO</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Brooksource3.8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$55K(Employer provided)</t>
+          <t>$50.00 - $55.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-brooksource-JV_IC1154170_KO0,14_KE15,26.htm?jl=1010114754582</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1483,27 +1479,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>ML/AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Midwest Machine LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>$170K - $175K(Employer provided)</t>
+          <t>$80K - $120K(Employer provided)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
+          <t>https://www.glassdoor.com/job-listing/ml-ai-engineer-midwest-machine-llc-JV_IC1139740_KO0,14_KE15,34.htm?jl=1010109262064</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1515,27 +1511,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>President ANC</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Hershey Company3.6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$318K - $406K(Employer provided)</t>
+          <t>$124K - $165K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-anc-alutiiq-JV_IC1134201_KO0,13_KE14,21.htm?jl=1010071156640</t>
+          <t>https://www.glassdoor.com/job-listing/sr-data-scientist-the-hershey-company-JV_IC1139977_KO0,17_KE18,37.htm?jl=1009569149385</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1547,27 +1543,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>President &amp; CEO</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MIFAB3.5</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>$320K - $350K(Employer provided)</t>
+          <t>$70K - $80K(Employer provided)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-ceo-the-moran-company-JV_IC1154062_KO0,13_KE14,31.htm?jl=1010108349638</t>
+          <t>https://www.glassdoor.com/job-listing/ai-developer-mifab-JV_IC1128808_KO0,12_KE13,18.htm?jl=1010103162764</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1579,27 +1575,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chief of Staff to CEO</t>
+          <t>Associate Director, Data Science - Market Access</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sanofi4.0</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>$220K - $275K(Employer provided)</t>
+          <t>$149K - $215K(Employer provided)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-of-staff-to-ceo-iterative-health-JV_IC1154545_KO0,21_KE22,38.htm?jl=1009970363828</t>
+          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-market-access-sanofi-JV_IC1154545_KO0,45_KE46,52.htm?jl=1010050421211</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1611,27 +1607,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pueblo of Pojoaque Corporate Businesses CEO</t>
+          <t>Systems Engineer 3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Judge Group3.6</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>$225K(Employer provided)</t>
+          <t>$60.00 - $70.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/pueblo-of-pojoaque-corporate-businesses-ceo-pueblo-of-pojoaque-corporations-JV_IC1138171_KO0,43_KE44,75.htm?jl=1010074993847</t>
+          <t>https://www.glassdoor.com/job-listing/systems-engineer-3-the-judge-group-JV_IC1131233_KO0,18_KE19,34.htm?jl=1010088930529</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1643,27 +1639,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Senior Director, Enterprise Data Architecture and Analytics</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pattern Energy Group3.5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>$300K - $450K(Employer provided)</t>
+          <t>$174K - $216K(Employer provided)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-northwestern-medical-center-JV_IC1141798_KO0,23_KE24,51.htm?jl=1010086464392</t>
+          <t>https://www.glassdoor.com/job-listing/senior-director-enterprise-data-architecture-and-analytics-pattern-energy-group-JV_IC1147401_KO0,58_KE59,79.htm?jl=1009990778925</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1675,23 +1671,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Digital Assets Risk Manager - Crypto &amp; Blockchain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Fidelity Investments4.1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>$80K - $153K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-anson-regional-medical-service-JV_IC1138675_KO0,23_KE24,54.htm?jl=1010104525348</t>
+          <t>https://www.glassdoor.com/job-listing/digital-assets-risk-manager-crypto-blockchain-fidelity-investments-JV_IC1161600_KO0,45_KE46,66.htm?jl=1009950273910</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1703,27 +1703,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>AI and Automation Engineer (Business Analysis, Senior Analyst)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The MIL Corporation4.0</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>$275K - $280K(Employer provided)</t>
+          <t>$100K - $115K(Employer provided)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1136950_KO0,23_KE24,41.htm?jl=1010097248172</t>
+          <t>https://www.glassdoor.com/job-listing/ai-and-automation-engineer-business-analysis-senior-analyst-the-mil-corporation-JV_IC1155074_KO0,59_KE60,79.htm?jl=1010101966087</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1735,27 +1735,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>President &amp; Chief Commercial Officer</t>
+          <t>Senior Artificial Intelligence (AI) Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Amtelco3.9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>$150K - $185K(Employer provided)</t>
+          <t>$68K - $114K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-chief-commercial-officer-check-my-policy-JV_IC1140171_KO0,34_KE35,50.htm?jl=1010094178300</t>
+          <t>https://www.glassdoor.com/job-listing/senior-artificial-intelligence-ai-developer-amtelco-JV_IC3740374_KO0,43_KE44,51.htm?jl=1010109218562</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1767,27 +1767,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CEO in Training (CIT), Executive Director</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Neptune Technology Group3.8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>$42K - $76K(Glassdoor est.)</t>
+          <t>$114K - $155K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133685_KO0,38_KE39,52.htm?jl=1010088747434</t>
+          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-neptune-technology-group-JV_IC1155612_KO0,21_KE22,46.htm?jl=1010037988368</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1799,27 +1799,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>MedPro Group4.0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>$175K - $225K(Employer provided)</t>
+          <t>$48K - $80K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
+          <t>https://www.glassdoor.com/job-listing/ai-specialist-medpro-group-JV_IC1144939_KO0,13_KE14,26.htm?jl=1010112183170</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1831,27 +1831,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>AI Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Commonwealth Equipment Corp5.0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$200K(Employer provided)</t>
+          <t>$71K - $123K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-marathon-JV_IC1154115_KO0,12_KE13,29.htm?jl=1010103355662</t>
+          <t>https://www.glassdoor.com/job-listing/ai-specialist-commonwealth-equipment-corp-JV_IC1165586_KO0,13_KE14,41.htm?jl=1010101947687</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1863,23 +1863,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>President and CEO - Oklahoma Manufacturing Alliance</t>
+          <t>Digital Assets Risk Manager - Crypto &amp; Blockchain</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Fidelity Investments4.1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>$80K - $153K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-ceo-oklahoma-manufacturing-alliance-schnake-turnbo-frank-JV_IC1137055_KO0,49_KE50,70.htm?jl=1010109776782</t>
+          <t>https://www.glassdoor.com/job-listing/digital-assets-risk-manager-crypto-blockchain-fidelity-investments-JV_IC1147908_KO0,45_KE46,66.htm?jl=1009950273913</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1891,27 +1895,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Friant &amp; Associates2.6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>$150K - $175K(Employer provided)</t>
+          <t>$160K - $185K(Employer provided)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1126720_KO0,23_KE24,41.htm?jl=1010091874998</t>
+          <t>https://www.glassdoor.com/job-listing/ai-engineer-friant-associates-JV_IC1147404_KO0,11_KE12,29.htm?jl=1010037044723</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1923,27 +1927,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer</t>
+          <t>Marketing Data Systems &amp; Analytics Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>One Nevada Credit Union3.6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>$275K - $325K(Employer provided)</t>
+          <t>$67K - $94K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-chief-executive-officer-confidential-JV_KO0,37_KE38,50.htm?jl=1010043379708</t>
+          <t>https://www.glassdoor.com/job-listing/marketing-data-systems-analytics-specialist-one-nevada-credit-union-JV_IC1149603_KO0,43_KE44,67.htm?jl=1010110137715</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1955,27 +1959,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Executive Director</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Neptune Technology Group3.8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$140K - $150K(Employer provided)</t>
+          <t>$83K - $125K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-the-moran-company-JV_IC1136440_KO0,18_KE19,36.htm?jl=1010108424026</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-neptune-technology-group-JV_IC1155612_KO0,14_KE15,39.htm?jl=1010037988367</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1987,27 +1991,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CEO in Training (CIT), Executive Director</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CIA3.5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$46K - $84K(Glassdoor est.)</t>
+          <t>$75K - $157K(Employer provided)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133406_KO0,38_KE39,52.htm?jl=1010112336554</t>
+          <t>https://www.glassdoor.com/job-listing/data-engineer-cia-JV_IC1138213_KO0,13_KE14,17.htm?jl=1009964042992</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2019,27 +2023,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CEO - Interior Design Company</t>
+          <t>Data Scientist (In Person - Austin, TX)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tommbo.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$250K - $350K(Employer provided)</t>
+          <t>$135K - $170K(Employer provided)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-interior-design-company-redford-hearth-executive-search-healthcare-JV_IC1132348_KO0,27_KE28,70.htm?jl=1010077281914</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-in-person-austin-tx-tommbo-com-JV_IC1139761_KO0,34_KE35,45.htm?jl=1010046625687</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2051,27 +2055,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Software Engineer, Agentic Systems</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>InCommodities4.3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$150K - $220K(Employer provided)</t>
+          <t>$160K(Employer provided)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-lng-holding-JV_IC1128793_KO0,23_KE24,35.htm?jl=1010006337770</t>
+          <t>https://www.glassdoor.com/job-listing/software-engineer-agentic-systems-incommodities-JV_IC1139761_KO0,33_KE34,47.htm?jl=1010084207208</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2083,27 +2087,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Louisiana Healthcare Connections Plan President &amp; CEO</t>
+          <t>Computer Science Teacher</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Kūlia Academy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>$270K - $580K(Employer provided)</t>
+          <t>$80K - $90K(Employer provided)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/louisiana-healthcare-connections-plan-president-ceo-centene-JV_IC1150013_KO0,51_KE52,59.htm?jl=1010112808854</t>
+          <t>https://www.glassdoor.com/job-listing/computer-science-teacher-kūlia-academy-JV_IC1140656_KO0,24_KE25,38.htm?jl=1009966984742</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2115,27 +2119,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Director, CEO Communications</t>
+          <t>MRM Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Pacific Life3.4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>$90K - $150K(Glassdoor est.)</t>
+          <t>$152K - $186K(Employer provided)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/director-ceo-communications-ochsner-health-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010105292126</t>
+          <t>https://www.glassdoor.com/job-listing/mrm-senior-data-scientist-pacific-life-JV_IC1146837_KO0,25_KE26,38.htm?jl=1010094536797</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2147,27 +2151,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Acra Lending3.0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>$180K - $210K(Employer provided)</t>
+          <t>$135K - $145K(Employer provided)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-arvin-ca-JV_IC1146556_KO0,12_KE13,29.htm?jl=1010112565997</t>
+          <t>https://www.glassdoor.com/job-listing/data-engineer-acra-lending-JV_IC1146798_KO0,13_KE14,26.htm?jl=1009841415610</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2179,27 +2183,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Associate Director, Registry Data Analytics</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>American Academy of Dermatology3.9</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>$220K - $245K(Employer provided)</t>
+          <t>$159K - $183K(Employer provided)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-tigard-oregon-JV_IC1165048_KO0,12_KE13,34.htm?jl=1010101155714</t>
+          <t>https://www.glassdoor.com/job-listing/associate-director-registry-data-analytics-american-academy-of-dermatology-JV_IC1158097_KO0,42_KE43,74.htm?jl=1010115120315</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2211,27 +2215,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Associate Director, Data Science &amp; AI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CSL Plasma3.0</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>$275K(Employer provided)</t>
+          <t>$114K - $170K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-sausalito-art-festival-JV_IC1147411_KO0,12_KE13,35.htm?jl=1010015848250</t>
+          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-ai-csl-plasma-JV_IC1152620_KO0,34_KE35,45.htm?jl=1010110020399</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2243,27 +2247,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>City Manager - Annapolis, MD</t>
+          <t>Senior Director, Data Sciences and Advanced Analytics</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bristol Myers Squibb3.7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>$250K - $294K(Employer provided)</t>
+          <t>$232K - $315K(Employer provided)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-annapolis-md-annapolis-market-house-md-JV_IC1153523_KO0,25_KE26,51.htm?jl=1010023329394</t>
+          <t>https://www.glassdoor.com/job-listing/senior-director-data-sciences-and-advanced-analytics-bristol-myers-squibb-JV_IC1127179_KO0,52_KE53,73.htm?jl=1010025012657</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2275,27 +2279,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Senior AI Engineer – Data and AI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Fisher Investments3.7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>$274K(Employer provided)</t>
+          <t>$84K - $125K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-county-of-sonoma-JV_IC1147520_KO0,12_KE13,29.htm?jl=1010107011390</t>
+          <t>https://www.glassdoor.com/job-listing/senior-ai-engineer-data-and-ai-fisher-investments-JV_IC1140045_KO0,30_KE31,49.htm?jl=1010098255789</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2307,27 +2311,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>President and General Manager, WPVI-TV</t>
+          <t>Senior AI Engineer – Data and AI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Fisher Investments3.7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>$412K - $553K(Employer provided)</t>
+          <t>$125K - $165K(Employer provided)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-general-manager-wpvi-tv-walt-disney-company-JV_IC1152672_KO0,37_KE38,57.htm?jl=1009865634435</t>
+          <t>https://www.glassdoor.com/job-listing/senior-ai-engineer-data-and-ai-fisher-investments-JV_IC1150405_KO0,30_KE31,49.htm?jl=1010050420643</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2339,27 +2343,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Executive Business Partner, Office of the CEO</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Judge Group3.6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>$76.96 - $92.53Per Hour(Employer provided)</t>
+          <t>$130K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-business-partner-office-of-the-ceo-roblox-JV_IC1147406_KO0,44_KE45,51.htm?jl=1010090207481</t>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-the-judge-group-JV_IC1140494_KO0,14_KE15,30.htm?jl=1010106793793</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Data Science</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2371,22 +2375,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Financial Analyst III - FP Financial Services</t>
+          <t>MEP Project Manager</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Ettinger Engineering Associates3.6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>$33.37 - $47.97Per Hour(Employer provided)</t>
+          <t>$80K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/financial-analyst-iii-fp-financial-services-unc-health-JV_IC1138696_KO0,43_KE44,54.htm?jl=1010111806078</t>
+          <t>https://www.glassdoor.com/job-listing/mep-project-manager-ettinger-engineering-associates-JV_IC1132348_KO0,19_KE20,51.htm?jl=1010013627763</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2403,22 +2407,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Region President</t>
+          <t>Financial Analyst III - FP Financial Services</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>UNC Health3.8</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>$210K - $350K(Employer provided)</t>
+          <t>$33.37 - $47.97Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/region-president-sysco-JV_IC1146959_KO0,16_KE17,22.htm?jl=1010056940373</t>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-iii-fp-financial-services-unc-health-JV_IC1138696_KO0,43_KE44,54.htm?jl=1010111806078</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2435,22 +2439,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Transportation Clerk - SYGMA - FP - US</t>
+          <t>Region President</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sysco3.3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>$16.83 - $25.19Per Hour(Employer provided)</t>
+          <t>$210K - $350K(Employer provided)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/transportation-clerk-sygma-fp-us-sygma-network-JV_IC1147539_KO0,32_KE33,46.htm?jl=1010076661775</t>
+          <t>https://www.glassdoor.com/job-listing/region-president-sysco-JV_IC1146959_KO0,16_KE17,22.htm?jl=1010056940373</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2467,22 +2471,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Construction Quality Director</t>
+          <t>Supervisor, Production - FP - SSMG - US</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sysco3.3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>$130K - $241K(Employer provided)</t>
+          <t>$39K - $58K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/construction-quality-director-aecom-JV_IC1145778_KO0,29_KE30,35.htm?jl=1010002852559</t>
+          <t>https://www.glassdoor.com/job-listing/supervisor-production-fp-ssmg-us-sysco-JV_IC1154123_KO0,32_KE33,38.htm?jl=1010102656517</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2499,22 +2503,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FP and A Analyst Sr</t>
+          <t>Transportation Clerk - SYGMA - FP - US</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SYGMA Network3.0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>$77K - $118K(Employer provided)</t>
+          <t>$16.83 - $25.19Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/fp-and-a-analyst-sr-engie-JV_IC1140171_KO0,19_KE20,25.htm?jl=1010051644171</t>
+          <t>https://www.glassdoor.com/job-listing/transportation-clerk-sygma-fp-us-sygma-network-JV_IC1147539_KO0,32_KE33,46.htm?jl=1010076661775</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2531,22 +2535,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Specialist I, Pricing</t>
+          <t>Construction Quality Director</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AECOM3.7</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>$42K - $59K(Glassdoor est.)</t>
+          <t>$130K - $241K(Employer provided)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/specialist-i-pricing-qxo-JV_IC1140029_KO0,20_KE21,24.htm?jl=1010076339628</t>
+          <t>https://www.glassdoor.com/job-listing/construction-quality-director-aecom-JV_IC1145778_KO0,29_KE30,35.htm?jl=1010002852559</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2563,22 +2567,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Scientist, Study Manager</t>
+          <t>FP and A Analyst Sr</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>ENGIE4.0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>$117K - $184K(Employer provided)</t>
+          <t>$77K - $118K(Employer provided)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-scientist-study-manager-merck-JV_IC1147311_KO0,30_KE31,36.htm?jl=1010069167075</t>
+          <t>https://www.glassdoor.com/job-listing/fp-and-a-analyst-sr-engie-JV_IC1140171_KO0,19_KE20,25.htm?jl=1010051644171</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2595,22 +2599,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Clinical Scientist</t>
+          <t>Specialist I, Pricing</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>QXO3.7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>$115K - $181K(Employer provided)</t>
+          <t>$42K - $59K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-clinical-scientist-merck-JV_IC1147311_KO0,25_KE26,31.htm?jl=1009970109525</t>
+          <t>https://www.glassdoor.com/job-listing/specialist-i-pricing-qxo-JV_IC1140029_KO0,20_KE21,24.htm?jl=1010076339628</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2627,18 +2631,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dishwasher FP</t>
+          <t>Senior Scientist, Study Manager</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Merck4.1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>$117K - $184K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/dishwasher-fp-arcis-golf-JV_KO0,13_KE14,24.htm?jl=1010053677954</t>
+          <t>https://www.glassdoor.com/job-listing/senior-scientist-study-manager-merck-JV_IC1147311_KO0,30_KE31,36.htm?jl=1010069167075</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2655,22 +2663,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Senior Clinical Scientist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Merck4.1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>$100K - $120K(Employer provided)</t>
+          <t>$115K - $181K(Employer provided)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/social-media-manager-paramount-JV_KO0,20_KE21,30.htm?jl=1010111288466</t>
+          <t>https://www.glassdoor.com/job-listing/senior-clinical-scientist-merck-JV_IC1147311_KO0,25_KE26,31.htm?jl=1009970109525</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2687,22 +2695,18 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Royalty Analyst (Peanuts Worldwide)</t>
+          <t>Dishwasher FP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>$60K - $70K(Employer provided)</t>
-        </is>
-      </c>
+          <t>Arcis Golf3.3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/royalty-analyst-peanuts-worldwide-sony-electronics-JV_KO0,33_KE34,50.htm?jl=1010086845696</t>
+          <t>https://www.glassdoor.com/job-listing/dishwasher-fp-arcis-golf-JV_KO0,13_KE14,24.htm?jl=1010053677954</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2719,22 +2723,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aseptic Production Training Instructor</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Paramount3.7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>$46K - $78K(Glassdoor est.)</t>
+          <t>$100K - $120K(Employer provided)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/aseptic-production-training-instructor-novo-nordisk-JV_IC1138946_KO0,38_KE39,51.htm?jl=1010106837668</t>
+          <t>https://www.glassdoor.com/job-listing/social-media-manager-paramount-JV_KO0,20_KE21,30.htm?jl=1010111288466</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2751,22 +2755,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Technical Acquisition and Contracts Specialist</t>
+          <t>Royalty Analyst (Peanuts Worldwide)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Sony Electronics3.9</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>$151K - $227K(Employer provided)</t>
+          <t>$60K - $70K(Employer provided)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/technical-acquisition-and-contracts-specialist-the-aerospace-corporation-JV_IC1130353_KO0,46_KE47,72.htm?jl=1010079037925</t>
+          <t>https://www.glassdoor.com/job-listing/royalty-analyst-peanuts-worldwide-sony-electronics-JV_KO0,33_KE34,50.htm?jl=1010086845696</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2783,22 +2787,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Maintenance Tech</t>
+          <t>Member Services Representative</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>$40K - $56K(Glassdoor est.)</t>
+          <t>$28K - $34K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/maintenance-tech-planet-fitness-JV_IC1151076_KO0,16_KE17,31.htm?jl=1010087433721</t>
+          <t>https://www.glassdoor.com/job-listing/member-services-representative-planet-fitness-JV_IC1141423_KO0,30_KE31,45.htm?jl=1010112842947</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2815,22 +2819,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Planet Fitness Team Member</t>
+          <t>Aseptic Production Training Instructor</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Novo Nordisk3.9</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>$33K - $47K(Glassdoor est.)</t>
+          <t>$46K - $78K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-team-member-planet-fitness-JV_IC1146121_KO0,26_KE27,41.htm?jl=1009789931023</t>
+          <t>https://www.glassdoor.com/job-listing/aseptic-production-training-instructor-novo-nordisk-JV_IC1138946_KO0,38_KE39,51.htm?jl=1010106837668</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2847,22 +2851,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Member Services Representative- St. Joseph, MO, Planet Fitness</t>
+          <t>Technical Acquisition and Contracts Specialist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The Aerospace Corporation3.5</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>$36K - $47K(Glassdoor est.)</t>
+          <t>$151K - $227K(Employer provided)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/member-services-representative-st-joseph-mo-planet-fitness-planet-fitness-JV_IC1131187_KO0,58_KE59,73.htm?jl=1009990771575</t>
+          <t>https://www.glassdoor.com/job-listing/technical-acquisition-and-contracts-specialist-the-aerospace-corporation-JV_IC1130353_KO0,46_KE47,72.htm?jl=1010079037925</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2879,18 +2883,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Planet Fitness</t>
+          <t>Maintenance Tech</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Planet Fitness3.3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>$40K - $56K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140422_KO0,14_KE15,29.htm?jl=1010063289184</t>
+          <t>https://www.glassdoor.com/job-listing/maintenance-tech-planet-fitness-JV_IC1151076_KO0,16_KE17,31.htm?jl=1010087433721</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2907,22 +2915,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>planet fitness Member Services Representative</t>
+          <t>Planet Fitness Team Member</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>$38K - $53K(Glassdoor est.)</t>
+          <t>$33K - $47K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-member-services-representative-planet-fitness-JV_IC1151049_KO0,45_KE46,60.htm?jl=1010106825729</t>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-team-member-planet-fitness-JV_IC1146121_KO0,26_KE27,41.htm?jl=1009789931023</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2939,18 +2947,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Planet Fitness</t>
+          <t>Member Services Representative- St. Joseph, MO, Planet Fitness</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>Planet Fitness3.3</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>$36K - $47K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140320_KO0,14_KE15,29.htm?jl=1010053177095</t>
+          <t>https://www.glassdoor.com/job-listing/member-services-representative-st-joseph-mo-planet-fitness-planet-fitness-JV_IC1131187_KO0,58_KE59,73.htm?jl=1009990771575</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2967,22 +2979,18 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CLUB - Overnight Member Services Rep</t>
+          <t>Planet Fitness</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>$27K - $33K(Glassdoor est.)</t>
-        </is>
-      </c>
+          <t>Planet Fitness3.3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/club-overnight-member-services-rep-planet-fitness-JV_IC1140000_KO0,34_KE35,49.htm?jl=1010031133814</t>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140422_KO0,14_KE15,29.htm?jl=1010063289184</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2999,22 +3007,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Member Services Representative- Morning Opener</t>
+          <t>planet fitness Member Services Representative</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>$32K - $42K(Glassdoor est.)</t>
+          <t>$38K - $53K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/member-services-representative-morning-opener-planet-fitness-JV_IC1130886_KO0,45_KE46,60.htm?jl=1010101171715</t>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-member-services-representative-planet-fitness-JV_IC1151049_KO0,45_KE46,60.htm?jl=1010106825729</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3031,22 +3039,18 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Club Manager</t>
+          <t>Planet Fitness</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>$40K - $53K(Glassdoor est.)</t>
-        </is>
-      </c>
+          <t>Planet Fitness3.3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/club-manager-planet-fitness-JV_IC1141333_KO0,12_KE13,27.htm?jl=1010105150250</t>
+          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140320_KO0,14_KE15,29.htm?jl=1010053177095</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3063,22 +3067,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Part-Time Member Services Representative</t>
+          <t>CLUB - Overnight Member Services Rep</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>$26K - $35K(Glassdoor est.)</t>
+          <t>$27K - $33K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/part-time-member-services-representative-planet-fitness-JV_IC1143111_KO0,40_KE41,55.htm?jl=1010083348473</t>
+          <t>https://www.glassdoor.com/job-listing/club-overnight-member-services-rep-planet-fitness-JV_IC1140000_KO0,34_KE35,49.htm?jl=1010031133814</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3095,22 +3099,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Member Services Representative</t>
+          <t>Member Services Representative- Morning Opener</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>$27K - $35K(Glassdoor est.)</t>
+          <t>$32K - $42K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/member-services-representative-planet-fitness-JV_IC1149904_KO0,30_KE31,45.htm?jl=1010093033515</t>
+          <t>https://www.glassdoor.com/job-listing/member-services-representative-morning-opener-planet-fitness-JV_IC1130886_KO0,45_KE46,60.htm?jl=1010101171715</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3127,22 +3131,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Overnight Member Services</t>
+          <t>Club Manager</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>$33K - $44K(Glassdoor est.)</t>
+          <t>$40K - $53K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/overnight-member-services-planet-fitness-JV_IC1133904_KO0,25_KE26,40.htm?jl=1010074948979</t>
+          <t>https://www.glassdoor.com/job-listing/club-manager-planet-fitness-JV_IC1141333_KO0,12_KE13,27.htm?jl=1010105150250</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3159,22 +3163,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CLUB - Assistant Club Manager</t>
+          <t>Part-Time Member Services Representative</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>$34K - $47K(Glassdoor est.)</t>
+          <t>$26K - $35K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/club-assistant-club-manager-planet-fitness-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010052052649</t>
+          <t>https://www.glassdoor.com/job-listing/part-time-member-services-representative-planet-fitness-JV_IC1143111_KO0,40_KE41,55.htm?jl=1010083348473</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3191,22 +3195,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Overnight Member Service Rep</t>
+          <t>Overnight Member Services</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>$12.00Per Hour(Employer provided)</t>
+          <t>$33K - $44K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/overnight-member-service-rep-planet-fitness-JV_IC1139716_KO0,28_KE29,43.htm?jl=1010083348519</t>
+          <t>https://www.glassdoor.com/job-listing/overnight-member-services-planet-fitness-JV_IC1133904_KO0,25_KE26,40.htm?jl=1010074948979</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3223,22 +3227,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Specialist, Sexual and Reproductive Health and Rights</t>
+          <t>CLUB - Assistant Club Manager</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>$59K - $107K(Employer provided)</t>
+          <t>$34K - $47K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/specialist-sexual-and-reproductive-health-and-rights-international-rescue-committee-JV_KO0,52_KE53,83.htm?jl=1010111119629</t>
+          <t>https://www.glassdoor.com/job-listing/club-assistant-club-manager-planet-fitness-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010052052649</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3255,22 +3259,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Research Analyst III-(IAC)</t>
+          <t>Overnight Member Service Rep</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Planet Fitness3.3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>$71K - $111K(Glassdoor est.)</t>
+          <t>$12.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/research-analyst-iii-iac-people-technology-processes-JV_IC1154429_KO0,24_KE25,52.htm?jl=1009627655799</t>
+          <t>https://www.glassdoor.com/job-listing/overnight-member-service-rep-planet-fitness-JV_IC1139716_KO0,28_KE29,43.htm?jl=1010083348519</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3287,22 +3291,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Research Scientist-(IAC)</t>
+          <t>Specialist, Sexual and Reproductive Health and Rights</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>International Rescue Committee3.8</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>$111K - $173K(Glassdoor est.)</t>
+          <t>$59K - $107K(Employer provided)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/research-scientist-iac-people-technology-processes-JV_IC1154429_KO0,22_KE23,50.htm?jl=1009627655806</t>
+          <t>https://www.glassdoor.com/job-listing/specialist-sexual-and-reproductive-health-and-rights-international-rescue-committee-JV_KO0,52_KE53,83.htm?jl=1010111119629</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/Glassdoor_Jobs_2026-04-28.xlsx
+++ b/Glassdoor_Jobs_2026-04-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,27 +463,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Executive Director</t>
+          <t>Behavior Analyst (BCBA)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Addiction Recovery Coalition of New Hampshire</t>
+          <t>Soar Autism Center4.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$70K - $80K(Employer provided)</t>
+          <t>$86K - $114K(Employer provided)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
+          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1133897_KO0,21_KE22,40.htm?jl=1010038424820</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,27 +495,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Executive Assistant to the CEO</t>
+          <t>Behavior Analyst (BCBA)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Automotive Reinsurance Concepts</t>
+          <t>Soar Autism Center4.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>$55K(Employer provided)</t>
+          <t>$81K - $104K(Employer provided)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
+          <t>https://www.glassdoor.com/job-listing/behavior-analyst-bcba-soar-autism-center-JV_IC1148170_KO0,21_KE22,40.htm?jl=1010100922250</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -527,27 +527,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>President ANC</t>
+          <t>Hybrid Behavior Analyst (BCBA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alutiiq3.5</t>
+          <t>Soar Autism Center4.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>$318K - $406K(Employer provided)</t>
+          <t>$86K - $114K(Employer provided)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-anc-alutiiq-JV_IC1134201_KO0,13_KE14,21.htm?jl=1010071156640</t>
+          <t>https://www.glassdoor.com/job-listing/hybrid-behavior-analyst-bcba-soar-autism-center-JV_IC1133888_KO0,28_KE29,47.htm?jl=1010054611224</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -559,27 +559,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>President &amp; CEO</t>
+          <t>Job Cost Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Moran Company2.0</t>
+          <t>Vee-Jay Cement Contracting4.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>$320K - $350K(Employer provided)</t>
+          <t>$57K - $82K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-ceo-the-moran-company-JV_IC1154062_KO0,13_KE14,31.htm?jl=1010108349638</t>
+          <t>https://www.glassdoor.com/job-listing/job-cost-analyst-vee-jay-cement-contracting-JV_IC1131270_KO0,16_KE17,43.htm?jl=1010114961842</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Senior Sales Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Moran Company2.0</t>
+          <t>Breakthru Beverage Group3.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>$170K - $175K(Employer provided)</t>
+          <t>$68K - $99K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
+          <t>https://www.glassdoor.com/job-listing/senior-sales-analyst-breakthru-beverage-group-JV_IC1155147_KO0,20_KE21,45.htm?jl=1010114667197</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,27 +623,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chief of Staff to CEO</t>
+          <t>Business Analyst 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Iterative Health4.2</t>
+          <t>inSync Staffing4.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>$220K - $275K(Employer provided)</t>
+          <t>$34.66 - $36.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-of-staff-to-ceo-iterative-health-JV_IC1154545_KO0,21_KE22,38.htm?jl=1009970363828</t>
+          <t>https://www.glassdoor.com/job-listing/business-analyst-1-insync-staffing-JV_IC1151576_KO0,18_KE19,34.htm?jl=1010114536750</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,27 +655,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pueblo of Pojoaque Corporate Businesses CEO</t>
+          <t>Junior Financial Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pueblo of Pojoaque Corporations</t>
+          <t>GL Staffing Services3.2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>$225K(Employer provided)</t>
+          <t>$70K - $75K(Employer provided)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/pueblo-of-pojoaque-corporate-businesses-ceo-pueblo-of-pojoaque-corporations-JV_IC1138171_KO0,43_KE44,75.htm?jl=1010074993847</t>
+          <t>https://www.glassdoor.com/job-listing/junior-financial-analyst-gl-staffing-services-JV_IC1154160_KO0,24_KE25,45.htm?jl=1010115041405</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -687,27 +687,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Business Analyst I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Moran Company2.0</t>
+          <t>PHP Agency3.9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>$275K - $280K(Employer provided)</t>
+          <t>$53K - $70K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1136950_KO0,23_KE24,41.htm?jl=1010097248172</t>
+          <t>https://www.glassdoor.com/job-listing/business-analyst-i-php-agency-JV_IC1139977_KO0,18_KE19,29.htm?jl=1010115251725</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,23 +719,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Lead Quantitative Analyst (Charlotte, NC (Hybrid) or Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Anson Regional Medical Service</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>Brighthouse Financial4.1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>$160K - $210K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-anson-regional-medical-service-JV_IC1138675_KO0,23_KE24,54.htm?jl=1010104525348</t>
+          <t>https://www.glassdoor.com/job-listing/lead-quantitative-analyst-charlotte-nc-hybrid-or-remote-brighthouse-financial-JV_IC1138644_KO0,55_KE56,77.htm?jl=1010114527699</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -747,27 +751,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Chemical Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northwestern Medical Center3.5</t>
+          <t>Materion3.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>$300K - $450K(Employer provided)</t>
+          <t>$53K - $70K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-northwestern-medical-center-JV_IC1141798_KO0,23_KE24,51.htm?jl=1010086464392</t>
+          <t>https://www.glassdoor.com/job-listing/chemical-analyst-materion-JV_IC1145796_KO0,16_KE17,25.htm?jl=1010114458569</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -779,27 +783,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Accounting Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pennsylvania Coalition of Public Charter Schools</t>
+          <t>TalentBurst4.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>$175K - $225K(Employer provided)</t>
+          <t>$28.00 - $32.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
+          <t>https://www.glassdoor.com/job-listing/accounting-analyst-talentburst-JV_IC1138922_KO0,18_KE19,30.htm?jl=1010114789828</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -811,23 +815,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>President and CEO - Oklahoma Manufacturing Alliance</t>
+          <t>Financial Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Schnake Turnbo Frank4.1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>Hydro4.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>$63K - $96K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-ceo-oklahoma-manufacturing-alliance-schnake-turnbo-frank-JV_IC1137055_KO0,49_KE50,70.htm?jl=1010109776782</t>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-hydro-JV_IC1146170_KO0,17_KE18,23.htm?jl=1010108517953</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -839,27 +847,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CEO in Training (CIT), Executive Director</t>
+          <t>Analyst / Associate, Infrastructure and Energy Debt Advisory</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pennant Group3.3</t>
+          <t>Macquarie Group3.7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$42K - $76K(Glassdoor est.)</t>
+          <t>$110K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133685_KO0,38_KE39,52.htm?jl=1010088747434</t>
+          <t>https://www.glassdoor.com/job-listing/analyst-associate-infrastructure-and-energy-debt-advisory-macquarie-group-JV_IC1132348_KO0,57_KE58,73.htm?jl=1010114916735</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -871,27 +879,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Executive Director</t>
+          <t>Sr. Financial Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Moran Company2.0</t>
+          <t>Safecor Health2.2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$140K - $150K(Employer provided)</t>
+          <t>$70K - $87K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/executive-director-the-moran-company-JV_IC1136440_KO0,18_KE19,36.htm?jl=1010108424026</t>
+          <t>https://www.glassdoor.com/job-listing/sr-financial-analyst-safecor-health-JV_IC1145845_KO0,20_KE21,35.htm?jl=1010093412811</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -903,27 +911,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Sourcing Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scion Staffing3.7</t>
+          <t>DuBois Chemicals3.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$175K - $200K(Employer provided)</t>
+          <t>$59K - $75K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-scion-staffing-JV_IC1150480_KO0,23_KE24,38.htm?jl=1010092080553</t>
+          <t>https://www.glassdoor.com/job-listing/sourcing-analyst-dubois-chemicals-JV_IC1163270_KO0,16_KE17,33.htm?jl=1009996189526</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -935,27 +943,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Sales Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Moran Company2.0</t>
+          <t>Victaulic3.7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$150K - $175K(Employer provided)</t>
+          <t>$57K - $86K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1126720_KO0,23_KE24,41.htm?jl=1010091874998</t>
+          <t>https://www.glassdoor.com/job-listing/sales-analyst-victaulic-JV_IC1151932_KO0,13_KE14,23.htm?jl=1010083969774</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -967,27 +975,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Marketing &amp; Communication Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LNG Holding</t>
+          <t>Visions In Education3.9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$150K - $220K(Employer provided)</t>
+          <t>$6,472 - $9,616(Employer provided)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-lng-holding-JV_IC1128793_KO0,23_KE24,35.htm?jl=1010006337770</t>
+          <t>https://www.glassdoor.com/job-listing/marketing-communication-analyst-visions-in-education-JV_IC1163941_KO0,31_KE32,52.htm?jl=1010115052665</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -999,27 +1007,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>President and Chief Executive Officer</t>
+          <t>Sales Tax Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Confidential</t>
+          <t>Pleasant Valley Corporation3.8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$275K - $325K(Employer provided)</t>
+          <t>$51K - $68K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-chief-executive-officer-confidential-JV_KO0,37_KE38,50.htm?jl=1010043379708</t>
+          <t>https://www.glassdoor.com/job-listing/sales-tax-analyst-pleasant-valley-corporation-JV_IC1145799_KO0,17_KE18,45.htm?jl=1010073039141</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1031,27 +1039,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>President &amp; Chief Commercial Officer</t>
+          <t>Power BI Data Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Check My Policy</t>
+          <t>Worth and Company3.6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$150K - $185K(Employer provided)</t>
+          <t>$60K - $70K(Employer provided)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-chief-commercial-officer-check-my-policy-JV_IC1140171_KO0,34_KE35,50.htm?jl=1010094178300</t>
+          <t>https://www.glassdoor.com/job-listing/power-bi-data-analyst-worth-and-company-JV_IC1152675_KO0,21_KE22,39.htm?jl=1010110843211</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1063,27 +1071,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CEO in Training (CIT), Executive Director</t>
+          <t>Finance Systems Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pennant Group3.3</t>
+          <t>System One3.8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$46K - $84K(Glassdoor est.)</t>
+          <t>$53.00 - $70.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133406_KO0,38_KE39,52.htm?jl=1010112336554</t>
+          <t>https://www.glassdoor.com/job-listing/finance-systems-analyst-system-one-JV_IC1150442_KO0,23_KE24,34.htm?jl=1010115273847</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1095,27 +1103,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Regional Executive Director - Chicagoland | World Relief</t>
+          <t>Service &amp; Sales Operations Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vanderbloemen Search Group3.1</t>
+          <t>Pitco Frialator LLC2.3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$120K - $130K(Employer provided)</t>
+          <t>$57K - $81K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/regional-executive-director-chicagoland-world-relief-vanderbloemen-search-group-JV_IC1128808_KO0,52_KE53,79.htm?jl=1010104739908</t>
+          <t>https://www.glassdoor.com/job-listing/service-sales-operations-analyst-pitco-nh-JV_IC1147785_KO0,32_KE33,41.htm?jl=1010063149721</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1127,27 +1135,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chief Executive Officer / Hospital Administrator</t>
+          <t>Data Visualization Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ClearSky Health3.1</t>
+          <t>Shaw Industries3.7</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$63K - $117K(Glassdoor est.)</t>
+          <t>$65K - $107K(Employer provided)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-hospital-administrator-clearsky-health-JV_IC1154120_KO0,46_KE47,62.htm?jl=1010115284210</t>
+          <t>https://www.glassdoor.com/job-listing/data-visualization-analyst-shaw-industries-JV_IC1155803_KO0,26_KE27,42.htm?jl=1010094277077</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1159,27 +1167,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Louisiana Healthcare Connections Plan President &amp; CEO</t>
+          <t>Intelligence Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Centene3.7</t>
+          <t>Leidos3.9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$270K - $580K(Employer provided)</t>
+          <t>$59K - $107K(Employer provided)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/louisiana-healthcare-connections-plan-president-ceo-centene-JV_IC1150013_KO0,51_KE52,59.htm?jl=1010112808854</t>
+          <t>https://www.glassdoor.com/job-listing/intelligence-analyst-leidos-JV_IC1147652_KO0,20_KE21,27.htm?jl=1010114963762</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1191,27 +1199,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Director, CEO Communications</t>
+          <t>Sales Operations Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ochsner Health3.7</t>
+          <t>Visa Lighting An Oldenburg Group Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$90K - $150K(Glassdoor est.)</t>
+          <t>$65K - $85K(Employer provided)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/director-ceo-communications-ochsner-health-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010105292126</t>
+          <t>https://www.glassdoor.com/job-listing/sales-operations-analyst-visa-lighting-an-oldenburg-group-company-JV_IC1133579_KO0,24_KE25,65.htm?jl=1010074838658</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1223,27 +1231,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Sales and Marketing Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>City of Arvin</t>
+          <t>GSC Enterprises3.9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$180K - $210K(Employer provided)</t>
+          <t>$60K - $70K(Employer provided)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-arvin-ca-JV_IC1146556_KO0,12_KE13,29.htm?jl=1010112565997</t>
+          <t>https://www.glassdoor.com/job-listing/sales-and-marketing-analyst-gsc-enterprises-JV_IC1140540_KO0,27_KE28,43.htm?jl=1010109888516</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1255,27 +1263,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Financial Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>City of Tigard, Oregon</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>$220K - $245K(Employer provided)</t>
-        </is>
-      </c>
+          <t>Flavorseal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-tigard-oregon-JV_IC1165048_KO0,12_KE13,34.htm?jl=1010101155714</t>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-flavorseal-JV_IC1145763_KO0,17_KE18,28.htm?jl=1010098928013</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1287,27 +1291,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>QA Lab Analyst- Analytical</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sausalito Art Festival3.8</t>
+          <t>Mayer Brothers2.6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$275K(Employer provided)</t>
+          <t>$20.00Per Hour(Employer provided)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-sausalito-art-festival-JV_IC1147411_KO0,12_KE13,35.htm?jl=1010015848250</t>
+          <t>https://www.glassdoor.com/job-listing/qa-lab-analyst-analytical-mayer-brothers-JV_IC1158943_KO0,25_KE26,40.htm?jl=1010108261024</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1319,27 +1323,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>City Manager - Annapolis, MD</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Annapolis Market House (MD)3.8</t>
+          <t>Vaco3.7</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$250K - $294K(Employer provided)</t>
+          <t>$130K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-annapolis-md-annapolis-market-house-md-JV_IC1153523_KO0,25_KE26,51.htm?jl=1010023329394</t>
+          <t>https://www.glassdoor.com/job-listing/senior-business-analyst-vaco-JV_IC1126819_KO0,23_KE24,28.htm?jl=1010109933425</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1351,27 +1355,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>City Manager</t>
+          <t>Accounts Payable &amp; Accounts Receivable Analyst – Manufacturing</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>County of Sonoma3.8</t>
+          <t>Inceed4.1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$274K(Employer provided)</t>
+          <t>$60K - $64K(Employer provided)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/city-manager-county-of-sonoma-JV_IC1147520_KO0,12_KE13,29.htm?jl=1010107011390</t>
+          <t>https://www.glassdoor.com/job-listing/accounts-payable-accounts-receivable-analyst-manufacturing-inceed-JV_IC1140171_KO0,58_KE59,65.htm?jl=1010115127802</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1383,27 +1387,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>President and General Manager, WPVI-TV</t>
+          <t>Client Support Center Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Walt Disney Company3.8</t>
+          <t>athenahealth4.1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$412K - $553K(Employer provided)</t>
+          <t>$33K - $55K(Employer provided)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/president-and-general-manager-wpvi-tv-walt-disney-company-JV_IC1152672_KO0,37_KE38,57.htm?jl=1009865634435</t>
+          <t>https://www.glassdoor.com/job-listing/client-support-center-analyst-athenahealth-JV_IC1135503_KO0,29_KE30,42.htm?jl=1010100458393</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1415,27 +1419,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AVP, Investment Strategy and Derivatives</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Brooksource3.8</t>
+          <t>Unum3.5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$163K - $173K(Employer provided)</t>
+          <t>$134K - $274K(Employer provided)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-brooksource-JV_IC1152672_KO0,21_KE22,33.htm?jl=1010114706169</t>
+          <t>https://www.glassdoor.com/job-listing/avp-investment-strategy-and-derivatives-unum-JV_IC1144251_KO0,39_KE40,44.htm?jl=1010074853461</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1447,27 +1451,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Intermediate Quantitative Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brooksource3.8</t>
+          <t>Allstate3.4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$50.00 - $55.00Per Hour(Employer provided)</t>
+          <t>$124K - $165K(Employer provided)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-brooksource-JV_IC1154170_KO0,14_KE15,26.htm?jl=1010114754582</t>
+          <t>https://www.glassdoor.com/job-listing/intermediate-quantitative-analyst-allstate-JV_IC1128808_KO0,33_KE34,42.htm?jl=1010111214997</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1479,27 +1483,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ML/AI Engineer</t>
+          <t>Investment Specialist</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Midwest Machine LLC</t>
+          <t>RSM3.6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>$80K - $120K(Employer provided)</t>
+          <t>$134K - $269K(Employer provided)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ml-ai-engineer-midwest-machine-llc-JV_IC1139740_KO0,14_KE15,34.htm?jl=1010109262064</t>
+          <t>https://www.glassdoor.com/job-listing/investment-specialist-rsm-JV_KO0,21_KE22,25.htm?jl=1010071186146</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1511,27 +1515,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>VP, Alternative Investments Platform Management</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Hershey Company3.6</t>
+          <t>LPL Financial3.4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$124K - $165K(Glassdoor est.)</t>
+          <t>$145K - $241K(Employer provided)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/sr-data-scientist-the-hershey-company-JV_IC1139977_KO0,17_KE18,37.htm?jl=1009569149385</t>
+          <t>https://www.glassdoor.com/job-listing/vp-alternative-investments-platform-management-lpl-financial-JV_IC1155108_KO0,46_KE47,60.htm?jl=1010102268301</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1543,27 +1547,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Bloomberg Intelligence, Thematic Strategist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MIFAB3.5</t>
+          <t>Bloomberg4.0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>$70K - $80K(Employer provided)</t>
+          <t>$215K - $285K(Employer provided)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-developer-mifab-JV_IC1128808_KO0,12_KE13,18.htm?jl=1010103162764</t>
+          <t>https://www.glassdoor.com/job-listing/bloomberg-intelligence-thematic-strategist-bloomberg-JV_IC1132348_KO0,42_KE43,52.htm?jl=1010072907857</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1575,27 +1579,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Director, Data Science - Market Access</t>
+          <t>US Biotech/Pharma - Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sanofi4.0</t>
+          <t>Deutsche Bank3.8</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>$149K - $215K(Employer provided)</t>
+          <t>$135K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-market-access-sanofi-JV_IC1154545_KO0,45_KE46,52.htm?jl=1010050421211</t>
+          <t>https://www.glassdoor.com/job-listing/us-biotech-pharma-associate-deutsche-bank-JV_IC3735316_KO0,27_KE28,41.htm?jl=1009998379468</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1607,27 +1611,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Systems Engineer 3</t>
+          <t>US Aerospace &amp; Defense - Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Judge Group3.6</t>
+          <t>Deutsche Bank3.8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>$60.00 - $70.00Per Hour(Employer provided)</t>
+          <t>$110K - $125K(Employer provided)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/systems-engineer-3-the-judge-group-JV_IC1131233_KO0,18_KE19,34.htm?jl=1010088930529</t>
+          <t>https://www.glassdoor.com/job-listing/us-aerospace-defense-analyst-deutsche-bank-JV_IC3735316_KO0,28_KE29,42.htm?jl=1010016667567</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1639,27 +1643,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Director, Enterprise Data Architecture and Analytics</t>
+          <t>Research Associate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pattern Energy Group3.5</t>
+          <t>Deutsche Bank3.8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>$174K - $216K(Employer provided)</t>
+          <t>$135K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-director-enterprise-data-architecture-and-analytics-pattern-energy-group-JV_IC1147401_KO0,58_KE59,79.htm?jl=1009990778925</t>
+          <t>https://www.glassdoor.com/job-listing/research-associate-deutsche-bank-JV_IC3735316_KO0,18_KE19,32.htm?jl=1010048276472</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1671,27 +1675,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Digital Assets Risk Manager - Crypto &amp; Blockchain</t>
+          <t>Associate, Equity Investment Risk</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity Investments4.1</t>
+          <t>BlackRock3.8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>$80K - $153K(Employer provided)</t>
+          <t>$116K - $155K(Employer provided)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/digital-assets-risk-manager-crypto-blockchain-fidelity-investments-JV_IC1161600_KO0,45_KE46,66.htm?jl=1009950273910</t>
+          <t>https://www.glassdoor.com/job-listing/associate-equity-investment-risk-blackrock-JV_IC1147401_KO0,32_KE33,42.htm?jl=1010042879484</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1703,27 +1707,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI and Automation Engineer (Business Analysis, Senior Analyst)</t>
+          <t>DIRECTOR OF INVESTMENTS, Investment Office</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The MIL Corporation4.0</t>
+          <t>Boston University School of Law</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>$100K - $115K(Employer provided)</t>
+          <t>$350K - $750K(Employer provided)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-and-automation-engineer-business-analysis-senior-analyst-the-mil-corporation-JV_IC1155074_KO0,59_KE60,79.htm?jl=1010101966087</t>
+          <t>https://www.glassdoor.com/job-listing/director-of-investments-investment-office-boston-university-school-of-law-JV_IC1154532_KO0,41_KE42,73.htm?jl=1010102711412</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1735,27 +1739,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Artificial Intelligence (AI) Developer</t>
+          <t>Associate - Pension &amp; Inv Mgmt Oversight</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amtelco3.9</t>
+          <t>MetLife3.7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>$68K - $114K(Glassdoor est.)</t>
+          <t>$117K - $136K(Employer provided)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-artificial-intelligence-ai-developer-amtelco-JV_IC3740374_KO0,43_KE44,51.htm?jl=1010109218562</t>
+          <t>https://www.glassdoor.com/job-listing/associate-pension-inv-mgmt-oversight-metlife-JV_IC1127044_KO0,36_KE37,44.htm?jl=1010108324603</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1767,27 +1771,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Teacher Education - Affiliate Faculty (CFA-No Salary Appointment)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Neptune Technology Group3.8</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>$114K - $155K(Glassdoor est.)</t>
-        </is>
-      </c>
+          <t>Brigham Young University (BYU)4.6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-neptune-technology-group-JV_IC1155612_KO0,21_KE22,46.htm?jl=1010037988368</t>
+          <t>https://www.glassdoor.com/job-listing/teacher-education-affiliate-faculty-cfa-no-salary-appointment-brigham-young-university-byu-JV_IC1128247_KO0,61_KE62,90.htm?jl=1009975256241</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1799,27 +1799,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Fundamental Data Researcher</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MedPro Group4.0</t>
+          <t>Point724.0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>$48K - $80K(Glassdoor est.)</t>
+          <t>$150K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-specialist-medpro-group-JV_IC1144939_KO0,13_KE14,26.htm?jl=1010112183170</t>
+          <t>https://www.glassdoor.com/job-listing/fundamental-data-researcher-point72-JV_IC1132348_KO0,27_KE28,35.htm?jl=1009613833864</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1831,27 +1831,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Specialist</t>
+          <t>Trader/Quant Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Commonwealth Equipment Corp5.0</t>
+          <t>Point724.0</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$71K - $123K(Glassdoor est.)</t>
+          <t>$150K(Employer provided)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-specialist-commonwealth-equipment-corp-JV_IC1165586_KO0,13_KE14,41.htm?jl=1010101947687</t>
+          <t>https://www.glassdoor.com/job-listing/trader-quant-analyst-point72-JV_IC1131609_KO0,20_KE21,28.htm?jl=1009998192667</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1863,27 +1863,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Digital Assets Risk Manager - Crypto &amp; Blockchain</t>
+          <t>US Macro Trader</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fidelity Investments4.1</t>
+          <t>Wellington Management3.6</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>$80K - $153K(Employer provided)</t>
+          <t>$120K - $225K(Employer provided)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/digital-assets-risk-manager-crypto-blockchain-fidelity-investments-JV_IC1147908_KO0,45_KE46,66.htm?jl=1009950273913</t>
+          <t>https://www.glassdoor.com/job-listing/us-macro-trader-wellington-management-JV_IC1154532_KO0,15_KE16,37.htm?jl=1010086862367</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1895,27 +1895,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Associate, Private Climate Investing</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Friant &amp; Associates2.6</t>
+          <t>Wellington Management3.6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>$160K - $185K(Employer provided)</t>
+          <t>$90K - $180K(Employer provided)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/ai-engineer-friant-associates-JV_IC1147404_KO0,11_KE12,29.htm?jl=1010037044723</t>
+          <t>https://www.glassdoor.com/job-listing/associate-private-climate-investing-wellington-management-JV_KO0,35_KE36,57.htm?jl=1010039177866</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1927,27 +1927,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Marketing Data Systems &amp; Analytics Specialist</t>
+          <t>US Equity Trader</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>One Nevada Credit Union3.6</t>
+          <t>Wellington Management3.6</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>$67K - $94K(Glassdoor est.)</t>
+          <t>$120K - $225K(Employer provided)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/marketing-data-systems-analytics-specialist-one-nevada-credit-union-JV_IC1149603_KO0,43_KE44,67.htm?jl=1010110137715</t>
+          <t>https://www.glassdoor.com/job-listing/us-equity-trader-wellington-management-JV_IC1154532_KO0,16_KE17,38.htm?jl=1009938829673</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1959,27 +1959,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Principal, ALM &amp; Portfolio Manager</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Neptune Technology Group3.8</t>
+          <t>Apollo Global Management4.0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$83K - $125K(Glassdoor est.)</t>
+          <t>$300K(Employer provided)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-neptune-technology-group-JV_IC1155612_KO0,14_KE15,39.htm?jl=1010037988367</t>
+          <t>https://www.glassdoor.com/job-listing/principal-alm-portfolio-manager-apollo-global-management-JV_IC1146779_KO0,31_KE32,56.htm?jl=1010084152847</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1991,27 +1991,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Institutional Portfolios Investment Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CIA3.5</t>
+          <t>CAPTRUST Financial Advisors4.1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$75K - $157K(Employer provided)</t>
+          <t>$51K - $85K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-engineer-cia-JV_IC1138213_KO0,13_KE14,17.htm?jl=1009964042992</t>
+          <t>https://www.glassdoor.com/job-listing/institutional-portfolios-investment-associate-captrust-financial-advisors-JV_IC1138960_KO0,45_KE46,73.htm?jl=1010014203206</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2023,27 +2023,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist (In Person - Austin, TX)</t>
+          <t>Relationship Manager, Portfolio Management</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tommbo.com</t>
+          <t>Glenmede4.0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$135K - $170K(Employer provided)</t>
+          <t>$125K - $275K(Employer provided)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-in-person-austin-tx-tommbo-com-JV_IC1139761_KO0,34_KE35,45.htm?jl=1010046625687</t>
+          <t>https://www.glassdoor.com/job-listing/relationship-manager-portfolio-management-glenmede-JV_IC1126766_KO0,41_KE42,50.htm?jl=1009789988735</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2055,27 +2055,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer, Agentic Systems</t>
+          <t>Corporate Bond Trader</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>InCommodities4.3</t>
+          <t>Securian Financial3.6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$160K(Employer provided)</t>
+          <t>$92K - $203K(Employer provided)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/software-engineer-agentic-systems-incommodities-JV_IC1139761_KO0,33_KE34,47.htm?jl=1010084207208</t>
+          <t>https://www.glassdoor.com/job-listing/corporate-bond-trader-securian-financial-JV_IC1142575_KO0,21_KE22,40.htm?jl=1010069104372</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2087,27 +2087,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Computer Science Teacher</t>
+          <t>Quantitative Risk Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kūlia Academy</t>
+          <t>CoBank3.0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>$80K - $90K(Employer provided)</t>
+          <t>$99K - $121K(Employer provided)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/computer-science-teacher-kūlia-academy-JV_IC1140656_KO0,24_KE25,38.htm?jl=1009966984742</t>
+          <t>https://www.glassdoor.com/job-listing/quantitative-risk-analyst-cobank-JV_IC1164302_KO0,25_KE26,32.htm?jl=1009970735558</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2119,27 +2119,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MRM Senior Data Scientist</t>
+          <t>Adjunct CFA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pacific Life3.4</t>
+          <t>Jacksonville University3.5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>$152K - $186K(Employer provided)</t>
+          <t>$83K - $145K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/mrm-senior-data-scientist-pacific-life-JV_IC1146837_KO0,25_KE26,38.htm?jl=1010094536797</t>
+          <t>https://www.glassdoor.com/job-listing/adjunct-cfa-jacksonville-university-JV_IC1154093_KO0,11_KE12,35.htm?jl=1009814248819</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2151,27 +2151,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Model Risk Manager</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acra Lending3.0</t>
+          <t>Revolut4.0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>$135K - $145K(Employer provided)</t>
+          <t>$162K - $180K(Employer provided)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-engineer-acra-lending-JV_IC1146798_KO0,13_KE14,26.htm?jl=1009841415610</t>
+          <t>https://www.glassdoor.com/job-listing/model-risk-manager-revolut-JV_KO0,18_KE19,26.htm?jl=1010106554700</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2183,27 +2183,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Director, Registry Data Analytics</t>
+          <t>Financial Risk Manager</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Academy of Dermatology3.9</t>
+          <t>Revolut4.0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>$159K - $183K(Employer provided)</t>
+          <t>$162K - $180K(Employer provided)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-director-registry-data-analytics-american-academy-of-dermatology-JV_IC1158097_KO0,42_KE43,74.htm?jl=1010115120315</t>
+          <t>https://www.glassdoor.com/job-listing/financial-risk-manager-revolut-JV_KO0,22_KE23,30.htm?jl=1010062140091</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2215,27 +2215,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Director, Data Science &amp; AI</t>
+          <t>Associate, Capital Markets</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CSL Plasma3.0</t>
+          <t>TCW3.1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>$114K - $170K(Glassdoor est.)</t>
+          <t>$130K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-ai-csl-plasma-JV_IC1152620_KO0,34_KE35,45.htm?jl=1010110020399</t>
+          <t>https://www.glassdoor.com/job-listing/associate-capital-markets-tcw-JV_IC1146821_KO0,25_KE26,29.htm?jl=1010005173867</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2247,27 +2247,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Director, Data Sciences and Advanced Analytics</t>
+          <t>Fund Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb3.7</t>
+          <t>Expa2.9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>$232K - $315K(Employer provided)</t>
+          <t>$140K - $190K(Employer provided)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-director-data-sciences-and-advanced-analytics-bristol-myers-squibb-JV_IC1127179_KO0,52_KE53,73.htm?jl=1010025012657</t>
+          <t>https://www.glassdoor.com/job-listing/fund-analyst-expa-JV_KO0,12_KE13,17.htm?jl=1010047997937</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2279,27 +2279,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Data and AI</t>
+          <t>Model Validation Expert</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fisher Investments3.7</t>
+          <t>American AgCredit3.6</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>$84K - $125K(Glassdoor est.)</t>
+          <t>$110K - $199K(Employer provided)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-ai-engineer-data-and-ai-fisher-investments-JV_IC1140045_KO0,30_KE31,49.htm?jl=1010098255789</t>
+          <t>https://www.glassdoor.com/job-listing/model-validation-expert-american-agcredit-JV_KO0,23_KE24,41.htm?jl=1010097471429</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2311,27 +2311,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Data and AI</t>
+          <t>Research Associate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fisher Investments3.7</t>
+          <t>Green Street3.7</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>$125K - $165K(Employer provided)</t>
+          <t>$80K - $110K(Employer provided)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-ai-engineer-data-and-ai-fisher-investments-JV_IC1150405_KO0,30_KE31,49.htm?jl=1010050420643</t>
+          <t>https://www.glassdoor.com/job-listing/research-associate-green-street-JV_IC1146837_KO0,18_KE19,31.htm?jl=1010064827475</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2343,27 +2343,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Performance Analyst (entry level)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The Judge Group3.6</t>
+          <t>Prime Buchholz3.5</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>$130K - $150K(Employer provided)</t>
+          <t>$57K - $70K(Employer provided)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/data-scientist-the-judge-group-JV_IC1140494_KO0,14_KE15,30.htm?jl=1010106793793</t>
+          <t>https://www.glassdoor.com/job-listing/performance-analyst-entry-level-prime-buchholz-JV_IC1147753_KO0,31_KE32,46.htm?jl=1010103448948</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Data Science</t>
+          <t>CFA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2375,27 +2375,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MEP Project Manager</t>
+          <t>Executive Director</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ettinger Engineering Associates3.6</t>
+          <t>Addiction Recovery Coalition of New Hampshire</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>$80K - $150K(Employer provided)</t>
+          <t>$70K - $80K(Employer provided)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/mep-project-manager-ettinger-engineering-associates-JV_IC1132348_KO0,19_KE20,51.htm?jl=1010013627763</t>
+          <t>https://www.glassdoor.com/job-listing/executive-director-addiction-recovery-coalition-of-new-hampshire-JV_IC1147909_KO0,18_KE19,64.htm?jl=1010013592537</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2407,27 +2407,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Financial Analyst III - FP Financial Services</t>
+          <t>Executive Assistant to the CEO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>UNC Health3.8</t>
+          <t>Automotive Reinsurance Concepts</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>$33.37 - $47.97Per Hour(Employer provided)</t>
+          <t>$55K(Employer provided)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/financial-analyst-iii-fp-financial-services-unc-health-JV_IC1138696_KO0,43_KE44,54.htm?jl=1010111806078</t>
+          <t>https://www.glassdoor.com/job-listing/executive-assistant-to-the-ceo-automotive-reinsurance-concepts-JV_IC1130512_KO0,30_KE31,62.htm?jl=1010113074205</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2439,27 +2439,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Region President</t>
+          <t>President ANC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sysco3.3</t>
+          <t>Alutiiq3.5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>$210K - $350K(Employer provided)</t>
+          <t>$318K - $406K(Employer provided)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/region-president-sysco-JV_IC1146959_KO0,16_KE17,22.htm?jl=1010056940373</t>
+          <t>https://www.glassdoor.com/job-listing/president-anc-alutiiq-JV_IC1134201_KO0,13_KE14,21.htm?jl=1010071156640</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2471,27 +2471,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Supervisor, Production - FP - SSMG - US</t>
+          <t>President</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sysco3.3</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>$39K - $58K(Glassdoor est.)</t>
+          <t>$170K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/supervisor-production-fp-ssmg-us-sysco-JV_IC1154123_KO0,32_KE33,38.htm?jl=1010102656517</t>
+          <t>https://www.glassdoor.com/job-listing/president-the-moran-company-JV_IC1154293_KO0,9_KE10,27.htm?jl=1010086883488</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2503,27 +2503,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Transportation Clerk - SYGMA - FP - US</t>
+          <t>President &amp; CEO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SYGMA Network3.0</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>$16.83 - $25.19Per Hour(Employer provided)</t>
+          <t>$320K - $350K(Employer provided)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/transportation-clerk-sygma-fp-us-sygma-network-JV_IC1147539_KO0,32_KE33,46.htm?jl=1010076661775</t>
+          <t>https://www.glassdoor.com/job-listing/president-ceo-the-moran-company-JV_IC1154062_KO0,13_KE14,31.htm?jl=1010108349638</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2535,27 +2535,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Construction Quality Director</t>
+          <t>Chief of Staff to CEO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AECOM3.7</t>
+          <t>Iterative Health4.2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>$130K - $241K(Employer provided)</t>
+          <t>$220K - $275K(Employer provided)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/construction-quality-director-aecom-JV_IC1145778_KO0,29_KE30,35.htm?jl=1010002852559</t>
+          <t>https://www.glassdoor.com/job-listing/chief-of-staff-to-ceo-iterative-health-JV_IC1154545_KO0,21_KE22,38.htm?jl=1009970363828</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2567,27 +2567,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FP and A Analyst Sr</t>
+          <t>Pueblo of Pojoaque Corporate Businesses CEO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ENGIE4.0</t>
+          <t>Pueblo of Pojoaque Corporations</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>$77K - $118K(Employer provided)</t>
+          <t>$225K(Employer provided)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/fp-and-a-analyst-sr-engie-JV_IC1140171_KO0,19_KE20,25.htm?jl=1010051644171</t>
+          <t>https://www.glassdoor.com/job-listing/pueblo-of-pojoaque-corporate-businesses-ceo-pueblo-of-pojoaque-corporations-JV_IC1138171_KO0,43_KE44,75.htm?jl=1010074993847</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2599,27 +2599,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Specialist I, Pricing</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>QXO3.7</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>$42K - $59K(Glassdoor est.)</t>
-        </is>
-      </c>
+          <t>Anson Regional Medical Service</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/specialist-i-pricing-qxo-JV_IC1140029_KO0,20_KE21,24.htm?jl=1010076339628</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-anson-regional-medical-service-JV_IC1138675_KO0,23_KE24,54.htm?jl=1010104525348</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2631,27 +2627,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Scientist, Study Manager</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Merck4.1</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>$117K - $184K(Employer provided)</t>
+          <t>$275K - $280K(Employer provided)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-scientist-study-manager-merck-JV_IC1147311_KO0,30_KE31,36.htm?jl=1010069167075</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1136950_KO0,23_KE24,41.htm?jl=1010097248172</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2663,27 +2659,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Clinical Scientist</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Merck4.1</t>
+          <t>Pennsylvania Coalition of Public Charter Schools</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>$115K - $181K(Employer provided)</t>
+          <t>$175K - $225K(Employer provided)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/senior-clinical-scientist-merck-JV_IC1147311_KO0,25_KE26,31.htm?jl=1009970109525</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-pennsylvania-coalition-of-public-charter-schools-JV_IC1152597_KO0,23_KE24,72.htm?jl=1010110681394</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2695,23 +2691,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dishwasher FP</t>
+          <t>President and Chief Executive Officer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Arcis Golf3.3</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>$275K - $325K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/dishwasher-fp-arcis-golf-JV_KO0,13_KE14,24.htm?jl=1010053677954</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-chief-executive-officer-confidential-JV_KO0,37_KE38,50.htm?jl=1010043379708</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2723,27 +2723,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Social Media Manager</t>
+          <t>Executive Director</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Paramount3.7</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>$100K - $120K(Employer provided)</t>
+          <t>$140K - $150K(Employer provided)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/social-media-manager-paramount-JV_KO0,20_KE21,30.htm?jl=1010111288466</t>
+          <t>https://www.glassdoor.com/job-listing/executive-director-the-moran-company-JV_IC1136440_KO0,18_KE19,36.htm?jl=1010108424026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2755,27 +2755,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Royalty Analyst (Peanuts Worldwide)</t>
+          <t>President and CEO - Oklahoma Manufacturing Alliance</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sony Electronics3.9</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>$60K - $70K(Employer provided)</t>
-        </is>
-      </c>
+          <t>Schnake Turnbo Frank4.1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/royalty-analyst-peanuts-worldwide-sony-electronics-JV_KO0,33_KE34,50.htm?jl=1010086845696</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-ceo-oklahoma-manufacturing-alliance-schnake-turnbo-frank-JV_IC1137055_KO0,49_KE50,70.htm?jl=1010109776782</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2787,27 +2783,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Member Services Representative</t>
+          <t>President &amp; Chief Commercial Officer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Check My Policy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>$28K - $34K(Glassdoor est.)</t>
+          <t>$150K - $185K(Employer provided)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/member-services-representative-planet-fitness-JV_IC1141423_KO0,30_KE31,45.htm?jl=1010112842947</t>
+          <t>https://www.glassdoor.com/job-listing/president-chief-commercial-officer-check-my-policy-JV_IC1140171_KO0,34_KE35,50.htm?jl=1010094178300</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2819,27 +2815,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aseptic Production Training Instructor</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Novo Nordisk3.9</t>
+          <t>Scion Staffing3.7</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>$46K - $78K(Glassdoor est.)</t>
+          <t>$175K - $200K(Employer provided)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/aseptic-production-training-instructor-novo-nordisk-JV_IC1138946_KO0,38_KE39,51.htm?jl=1010106837668</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-scion-staffing-JV_IC1150480_KO0,23_KE24,38.htm?jl=1010092080553</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2851,27 +2847,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technical Acquisition and Contracts Specialist</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Aerospace Corporation3.5</t>
+          <t>The Moran Company2.0</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>$151K - $227K(Employer provided)</t>
+          <t>$150K - $175K(Employer provided)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/technical-acquisition-and-contracts-specialist-the-aerospace-corporation-JV_IC1130353_KO0,46_KE47,72.htm?jl=1010079037925</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-the-moran-company-JV_IC1126720_KO0,23_KE24,41.htm?jl=1010091874998</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2883,27 +2879,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maintenance Tech</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Northwestern Medical Center3.5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>$40K - $56K(Glassdoor est.)</t>
+          <t>$300K - $450K(Employer provided)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/maintenance-tech-planet-fitness-JV_IC1151076_KO0,16_KE17,31.htm?jl=1010087433721</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-northwestern-medical-center-JV_IC1141798_KO0,23_KE24,51.htm?jl=1010086464392</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2915,27 +2911,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Planet Fitness Team Member</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>LNG Holding</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>$33K - $47K(Glassdoor est.)</t>
+          <t>$150K - $220K(Employer provided)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-team-member-planet-fitness-JV_IC1146121_KO0,26_KE27,41.htm?jl=1009789931023</t>
+          <t>https://www.glassdoor.com/job-listing/chief-executive-officer-lng-holding-JV_IC1128793_KO0,23_KE24,35.htm?jl=1010006337770</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2947,27 +2943,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Member Services Representative- St. Joseph, MO, Planet Fitness</t>
+          <t>CEO - Interior Design Company</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Redford Hearth</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>$36K - $47K(Glassdoor est.)</t>
+          <t>$250K - $350K(Employer provided)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/member-services-representative-st-joseph-mo-planet-fitness-planet-fitness-JV_IC1131187_KO0,58_KE59,73.htm?jl=1009990771575</t>
+          <t>https://www.glassdoor.com/job-listing/ceo-interior-design-company-redford-hearth-executive-search-healthcare-JV_IC1132348_KO0,27_KE28,70.htm?jl=1010077281914</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2979,23 +2975,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Planet Fitness</t>
+          <t>CEO in Training (CIT), Executive Director</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Pennant Group3.3</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>$42K - $76K(Glassdoor est.)</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140422_KO0,14_KE15,29.htm?jl=1010063289184</t>
+          <t>https://www.glassdoor.com/job-listing/ceo-in-training-cit-executive-director-pennant-group-JV_IC1133685_KO0,38_KE39,52.htm?jl=1010088747434</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3007,27 +3007,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>planet fitness Member Services Representative</t>
+          <t>Regional Executive Director - Chicagoland | World Relief</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Vanderbloemen Search Group3.1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>$38K - $53K(Glassdoor est.)</t>
+          <t>$120K - $130K(Employer provided)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-member-services-representative-planet-fitness-JV_IC1151049_KO0,45_KE46,60.htm?jl=1010106825729</t>
+          <t>https://www.glassdoor.com/job-listing/regional-executive-director-chicagoland-world-relief-vanderbloemen-search-group-JV_IC1128808_KO0,52_KE53,79.htm?jl=1010104739908</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3039,23 +3039,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Planet Fitness</t>
+          <t>Louisiana Healthcare Connections Plan President &amp; CEO</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Centene3.7</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>$270K - $580K(Employer provided)</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/planet-fitness-planet-fitness-JV_IC1140320_KO0,14_KE15,29.htm?jl=1010053177095</t>
+          <t>https://www.glassdoor.com/job-listing/louisiana-healthcare-connections-plan-president-ceo-centene-JV_IC1150013_KO0,51_KE52,59.htm?jl=1010112808854</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3067,27 +3071,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CLUB - Overnight Member Services Rep</t>
+          <t>Director, CEO Communications</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Ochsner Health3.7</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>$27K - $33K(Glassdoor est.)</t>
+          <t>$90K - $150K(Glassdoor est.)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/club-overnight-member-services-rep-planet-fitness-JV_IC1140000_KO0,34_KE35,49.htm?jl=1010031133814</t>
+          <t>https://www.glassdoor.com/job-listing/director-ceo-communications-ochsner-health-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010105292126</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3099,27 +3103,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Member Services Representative- Morning Opener</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>City of Arvin</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>$32K - $42K(Glassdoor est.)</t>
+          <t>$180K - $210K(Employer provided)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/member-services-representative-morning-opener-planet-fitness-JV_IC1130886_KO0,45_KE46,60.htm?jl=1010101171715</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-arvin-ca-JV_IC1146556_KO0,12_KE13,29.htm?jl=1010112565997</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3131,27 +3135,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Club Manager</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>City of Tigard, Oregon</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>$40K - $53K(Glassdoor est.)</t>
+          <t>$220K - $245K(Employer provided)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/club-manager-planet-fitness-JV_IC1141333_KO0,12_KE13,27.htm?jl=1010105150250</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-city-of-tigard-oregon-JV_IC1165048_KO0,12_KE13,34.htm?jl=1010101155714</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3163,27 +3167,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Part-Time Member Services Representative</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Sausalito Art Festival3.8</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>$26K - $35K(Glassdoor est.)</t>
+          <t>$275K(Employer provided)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/part-time-member-services-representative-planet-fitness-JV_IC1143111_KO0,40_KE41,55.htm?jl=1010083348473</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-sausalito-art-festival-JV_IC1147411_KO0,12_KE13,35.htm?jl=1010015848250</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3195,27 +3199,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Overnight Member Services</t>
+          <t>City Manager - Annapolis, MD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Annapolis Market House (MD)3.8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>$33K - $44K(Glassdoor est.)</t>
+          <t>$250K - $294K(Employer provided)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/overnight-member-services-planet-fitness-JV_IC1133904_KO0,25_KE26,40.htm?jl=1010074948979</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-annapolis-md-annapolis-market-house-md-JV_IC1153523_KO0,25_KE26,51.htm?jl=1010023329394</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3227,27 +3231,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CLUB - Assistant Club Manager</t>
+          <t>City Manager</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>County of Sonoma3.8</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>$34K - $47K(Glassdoor est.)</t>
+          <t>$274K(Employer provided)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/club-assistant-club-manager-planet-fitness-JV_IC1150035_KO0,27_KE28,42.htm?jl=1010052052649</t>
+          <t>https://www.glassdoor.com/job-listing/city-manager-county-of-sonoma-JV_IC1147520_KO0,12_KE13,29.htm?jl=1010107011390</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3259,27 +3263,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Overnight Member Service Rep</t>
+          <t>President and General Manager, WPVI-TV</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Planet Fitness3.3</t>
+          <t>Walt Disney Company3.8</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>$12.00Per Hour(Employer provided)</t>
+          <t>$412K - $553K(Employer provided)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.com/job-listing/overnight-member-service-rep-planet-fitness-JV_IC1139716_KO0,28_KE29,43.htm?jl=1010083348519</t>
+          <t>https://www.glassdoor.com/job-listing/president-and-general-manager-wpvi-tv-walt-disney-company-JV_IC1152672_KO0,37_KE38,57.htm?jl=1009865634435</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FP&amp;A</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3291,30 +3295,1926 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Executive Business Partner, Office of the CEO</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Roblox3.8</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>$76.96 - $92.53Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/executive-business-partner-office-of-the-ceo-roblox-JV_IC1147406_KO0,44_KE45,51.htm?jl=1010090207481</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Bioinformatics Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agendia3.2</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>$80K - $85K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/bioinformatics-analyst-agendia-JV_KO0,22_KE23,30.htm?jl=1010110968052</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Gen AI Engineering Analyst - Vice President</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Citi3.6</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>$114K - $171K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/gen-ai-engineering-analyst-vice-president-citi-JV_IC1154093_KO0,41_KE42,46.htm?jl=1010114737667</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Brooksource3.8</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>$163K - $173K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-brooksource-JV_IC1152672_KO0,21_KE22,33.htm?jl=1010114706169</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Brooksource3.8</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>$50.00 - $55.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-brooksource-JV_IC1154170_KO0,14_KE15,26.htm?jl=1010114754582</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Glidewell Dental</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>$122K - $160K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/machine-learning-engineer-ii-glidewell-dental-JV_IC1146798_KO0,28_KE29,45.htm?jl=1009940212594</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MIFAB3.5</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>$70K - $80K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-developer-mifab-JV_IC1128808_KO0,12_KE13,18.htm?jl=1010103162764</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Associate Director, Data Science - Market Access</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sanofi4.0</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>$149K - $215K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/associate-director-data-science-market-access-sanofi-JV_IC1154545_KO0,45_KE46,52.htm?jl=1010050421211</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Sr. Exploitation Specialist/Data Scientist (TS/SCI)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Culmen International4.3</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>$117K - $195K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/sr-exploitation-specialist-data-scientist-ts-sci-culmen-international-JV_IC1154170_KO0,48_KE49,69.htm?jl=1010041116784</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AI Program Manager III</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Hyve Solutions2.7</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>$78K - $101K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-program-manager-iii-hyve-solutions-JV_IC1155193_KO0,22_KE23,37.htm?jl=1010035266428</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Data Product Lead</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mariner Finance3.7</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>$100K - $139K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-data-product-lead-mariner-finance-JV_IC1151049_KO0,24_KE25,40.htm?jl=1010081192082</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Friant &amp; Associates2.6</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>$160K - $185K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-engineer-friant-associates-JV_IC1147404_KO0,11_KE12,29.htm?jl=1010037044723</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Computer Science Teacher</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Kūlia Academy</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>$80K - $90K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/computer-science-teacher-kūlia-academy-JV_IC1140656_KO0,24_KE25,38.htm?jl=1009966984742</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Staff Data Scientist</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Penske Truck Leasing3.4</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>$145K - $191K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/staff-data-scientist-penske-truck-leasing-JV_IC1145766_KO0,20_KE21,41.htm?jl=1010083044600</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Lab Data Scientist</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GEVEKO Markings USA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>$75K - $80K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/lab-data-scientist-geveko-markings-usa-JV_IC1155838_KO0,18_KE19,38.htm?jl=1010104506793</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Director, Commercial Data Science - Hampton, NJ</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Celldex3.9</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>$177K - $229K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/director-commercial-data-science-hampton-nj-celldex-JV_IC1126790_KO0,43_KE44,51.htm?jl=1010072517837</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>The Hershey Company3.6</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>$124K - $165K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/sr-data-scientist-the-hershey-company-JV_IC1139977_KO0,17_KE18,37.htm?jl=1009569149385</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Lead Developer, Finance Technology</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>The J.M. Smucker Co.3.4</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>$98K - $152K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/lead-developer-finance-technology-the-jm-smucker-co-JV_IC1146360_KO0,33_KE34,51.htm?jl=1010097676555</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Scientist (In Person - Austin, TX)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Tommbo.com</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>$135K - $170K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/data-scientist-in-person-austin-tx-tommbo-com-JV_IC1139761_KO0,34_KE35,45.htm?jl=1010046625687</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Technical target analyst</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CIA3.5</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>$70K - $185K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/technical-target-analyst-cia-JV_IC1138213_KO0,24_KE25,28.htm?jl=1009964046918</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ML/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Midwest Machine LLC</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>$80K - $120K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ml-ai-engineer-midwest-machine-llc-JV_IC1139740_KO0,14_KE15,34.htm?jl=1010109262064</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>AI Specialist</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MedPro Group4.0</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>$48K - $80K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-specialist-medpro-group-JV_IC1144939_KO0,13_KE14,26.htm?jl=1010112183170</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; Network Analyst</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Outerlink Global Solutions</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/infrastructure-network-analyst-outerlink-global-solutions-JV_IC1150108_KO0,30_KE31,57.htm?jl=1010109233580</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Aircraft Performance Engineer I</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>RocketRoute4.0</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>$75K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/aircraft-performance-engineer-i-rocketroute-JV_IC1164306_KO0,31_KE32,43.htm?jl=1010103160521</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Systems Engineer 3</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>The Judge Group3.6</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>$60.00 - $70.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/systems-engineer-3-the-judge-group-JV_IC1131233_KO0,18_KE19,34.htm?jl=1010088930529</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Snowflake Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Victaulic3.7</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>$75K - $96K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/snowflake-solutions-engineer-victaulic-JV_IC1151932_KO0,28_KE29,38.htm?jl=1010094601086</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer – Data and AI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Fisher Investments3.7</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>$125K - $165K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-ai-engineer-data-and-ai-fisher-investments-JV_IC1150405_KO0,30_KE31,49.htm?jl=1010050420643</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Takeda Pharmaceuticals3.9</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>$162K - $260K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-data-scientist-takeda-pharmaceuticals-JV_IC1154532_KO0,21_KE22,44.htm?jl=1010080328224</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Lead Machine Learning Engineer, Ad Platforms</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Disney Entertainment and ESPN Product &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>$172K - $241K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/lead-machine-learning-engineer-ad-platforms-disney-entertainment-and-espn-product-technology-JV_IC1146873_KO0,43_KE44,92.htm?jl=1010018402983</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Confidential Posting</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>$130K - $180K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/full-stack-software-engineer-confidential-posting-JV_IC1147401_KO0,28_KE29,49.htm?jl=1009576404400</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>AI Specialist</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Commonwealth Equipment Corp5.0</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>$71K - $123K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/ai-specialist-commonwealth-equipment-corp-JV_IC1165586_KO0,13_KE14,41.htm?jl=1010101947687</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Data Science</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Resident I-FP</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Mount Sinai South Nassau3.2</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>$38.98Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/resident-i-fp-mount-sinai-south-nassau-JV_IC1132356_KO0,13_KE14,38.htm?jl=1010114755936</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Financial Analyst III - FP Financial Services</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UNC Health3.8</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>$33.37 - $47.97Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/financial-analyst-iii-fp-financial-services-unc-health-JV_IC1138696_KO0,43_KE44,54.htm?jl=1010111806078</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FP and A Analyst Sr</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ENGIE4.0</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>$77K - $118K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/fp-and-a-analyst-sr-engie-JV_IC1140171_KO0,19_KE20,25.htm?jl=1010051644171</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Scientist, Study Manager</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Merck4.1</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>$117K - $184K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-scientist-study-manager-merck-JV_IC1147311_KO0,30_KE31,36.htm?jl=1010069167075</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Dishwasher FP</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Arcis Golf3.3</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/dishwasher-fp-arcis-golf-JV_KO0,13_KE14,24.htm?jl=1010053677954</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Social Media Manager</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Paramount3.7</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>$100K - $120K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/social-media-manager-paramount-JV_KO0,20_KE21,30.htm?jl=1010111288466</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Royalty Analyst (Peanuts Worldwide)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Sony Electronics3.9</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>$60K - $70K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/royalty-analyst-peanuts-worldwide-sony-electronics-JV_KO0,33_KE34,50.htm?jl=1010086845696</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>Specialist, Sexual and Reproductive Health and Rights</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>International Rescue Committee3.8</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>$59K - $107K(Employer provided)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>https://www.glassdoor.com/job-listing/specialist-sexual-and-reproductive-health-and-rights-international-rescue-committee-JV_KO0,52_KE53,83.htm?jl=1010111119629</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>FP&amp;A</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Assistant Project Manager (MEP Design)</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DLB Associates3.6</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>$83K - $104K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/assistant-project-manager-mep-design-dlb-associates-JV_KO0,36_KE37,51.htm?jl=1010097073085</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Project Manager</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DLB Associates3.6</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>$105K - $131K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/project-manager-dlb-associates-JV_KO0,15_KE16,30.htm?jl=1010054623437</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Sr. FP &amp; A Analyst</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Beacon Bank</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>$56K - $102K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/sr-fpa-analyst-beacon-bank-JV_IC1154532_KO0,14_KE15,26.htm?jl=1010102037846</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CL22808: Para/FP/LAP - Westgate</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Kennewick School District3.9</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>$20.86 - $24.27Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/cl22808-para-fp-lap-westgate-kennewick-school-district-JV_IC1150324_KO0,28_KE29,54.htm?jl=1009989599106</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Product GRC SME</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Vanta3.3</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>$171K - $201K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/product-grc-sme-vanta-JV_KO0,15_KE16,21.htm?jl=1009877790257</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer (Scala 2/3 FP, Elasticsearch, Spark) - Remote US</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Revvity3.8</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>$119K - $142K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/senior-software-development-engineer-scala-23-fp-elasticsearch-spark-remote-us-revvity-JV_IC1154532_KO0,78_KE79,86.htm?jl=1010025279652</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Sales Specialist (Full-Time) - FP</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>rag &amp; bone2.9</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/sales-specialist-full-time-fp-rag-bone-JV_IC1147931_KO0,29_KE30,38.htm?jl=1009831903829</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>(FP) - Summer Program Instructor</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Boys &amp; Girls Clubs of America3.7</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>$18.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/fp-summer-program-instructor-boys-girls-clubs-of-america-JV_IC1155583_KO0,28_KE29,56.htm?jl=1010079406618</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Hazard Mitigation Specialist</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Witt O'Brien's3.7</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>$53K - $79K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/hazard-mitigation-specialist-witt-o-brien-s-JV_IC1140171_KO0,28_KE29,43.htm?jl=1009879107306</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>FP &amp; A Analyst I - WA</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Clearwater Paper3.4</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>$55K - $83K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/fpa-analyst-i-wa-clearwater-paper-JV_IC1150554_KO0,16_KE17,33.htm?jl=1010081022030</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Training Curriculum and Content Developer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Fieldpiece Instruments3.6</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>$100K - $120K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/training-curriculum-and-content-developer-fieldpiece-instruments-JV_IC1146843_KO0,41_KE42,64.htm?jl=1010031129094</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>FP &amp; A Analyst II</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>AgReliant Genetics2.9</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>$62K - $83K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/fpa-analyst-ii-agreliant-genetics-JV_IC1145044_KO0,14_KE15,33.htm?jl=1010082245684</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Program Support Analyst I</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>PROJECTXYZ4.1</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>$50K - $75K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/program-support-analyst-i-projectxyz-JV_IC1127653_KO0,25_KE26,36.htm?jl=1010110954665</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Paraplanner, Centralized Services</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Blue Trust4.2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/paraplanner-centralized-services-blue-trust-JV_IC1155582_KO0,32_KE33,43.htm?jl=1010109699168</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>FP &amp; A Analyst</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BMH Equipment2.3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>$75K - $85K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/fpa-analyst-bmh-equipment-JV_IC1134732_KO0,11_KE12,25.htm?jl=1010111086320</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Communications Coordinator, Foreign Policy (Job ID: 2026-3837)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Brookings Institution4.0</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>$59K - $64K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/communications-coordinator-foreign-policy-job-id-2026-3837-brookings-institution-JV_IC1138213_KO0,58_KE59,80.htm?jl=1010079866634</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Manager, FP &amp;A</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Azurity Pharmaceuticals3.2</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>$111K - $149K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/manager-fpa-azurity-pharmaceuticals-JV_IC1155583_KO0,11_KE12,35.htm?jl=1008094393295</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Anti-Terrorism/Force Protection (AT/FP) Specialist</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>MacDonald-Bedford, LLC3.2</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/anti-terrorism-force-protection-at-fp-specialist-macdonald-bedford-llc-JV_IC3757296_KO0,48_KE49,70.htm?jl=1010061304027</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>FP &amp; A Specialist</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Applus+3.4</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/fpa-specialist-applus-JV_IC1134737_KO0,14_KE15,21.htm?jl=1010045244886</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Assistant Loan Processor/Receptionist</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>F.P. Mortgage4.1</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>$44K - $63K(Glassdoor est.)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/assistant-loan-processor-receptionist-fp-mortgage-JV_IC1146906_KO0,37_KE38,49.htm?jl=1009049347113</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Customer Success Associate</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>FpAlpha, inc.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>$65K(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/customer-success-associate-fpalpha-inc-JV_KO0,26_KE27,38.htm?jl=1010108366728</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Resident Tech Assistant</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Front Porch3.6</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>$23.18 - $25.00Per Hour(Employer provided)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/resident-tech-assistant-front-porch-JV_IC1147473_KO0,23_KE24,35.htm?jl=1010099727483</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>FP&amp;A</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
